--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1787,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>1300.0</v>
+        <v>1303.0</v>
       </c>
       <c r="G62" t="n">
         <v>91.0</v>
@@ -1813,7 +1813,7 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>220.0</v>
+        <v>221.0</v>
       </c>
       <c r="G63" t="n">
         <v>25.0</v>
@@ -1839,7 +1839,7 @@
         <v>40</v>
       </c>
       <c r="F64" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G64" t="n">
         <v>8.0</v>
@@ -1891,7 +1891,7 @@
         <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G66" t="n">
         <v>10.0</v>
@@ -1943,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
       <c r="G68" t="n">
         <v>4.0</v>
@@ -2151,7 +2151,7 @@
         <v>40</v>
       </c>
       <c r="F76" t="n">
-        <v>210.0</v>
+        <v>209.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2229,7 +2229,7 @@
         <v>40</v>
       </c>
       <c r="F79" t="n">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -3144,10 +3144,10 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>51.0</v>
+        <v>53.0</v>
       </c>
       <c r="F19" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G19" t="n">
         <v>62.0</v>
@@ -3213,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="E22" t="n">
-        <v>64.0</v>
+        <v>67.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -3522,7 +3522,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>2096.0</v>
+        <v>2107.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3568,7 +3568,7 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3614,7 +3614,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>145.0</v>
+        <v>156.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>348.0</v>
+        <v>353.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>712.0</v>
+        <v>719.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3683,7 +3683,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3187.0</v>
+        <v>3190.0</v>
       </c>
       <c r="F14" t="n">
         <v>1.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>534.0</v>
+        <v>535.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8708.0</v>
+        <v>8722.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2632.0</v>
+        <v>2636.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3959,7 +3959,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>4492.0</v>
+        <v>4517.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3982,7 +3982,7 @@
         <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>481.0</v>
+        <v>482.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4005,7 +4005,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>5151.0</v>
+        <v>5171.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>9962.0</v>
+        <v>9981.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4650.0</v>
+        <v>4663.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>
@@ -4074,7 +4074,7 @@
         <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>1211.0</v>
+        <v>1212.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4097,7 +4097,7 @@
         <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -409,7 +409,7 @@
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -1871,7 +1871,7 @@
         <v>1.0</v>
       </c>
       <c r="H65" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="66">
@@ -1949,7 +1949,7 @@
         <v>4.0</v>
       </c>
       <c r="H68" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="69">
@@ -2229,7 +2229,7 @@
         <v>40</v>
       </c>
       <c r="F79" t="n">
-        <v>405.0</v>
+        <v>406.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -3075,7 +3075,7 @@
         <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F16" t="n">
         <v>4.0</v>
@@ -3150,7 +3150,7 @@
         <v>20.0</v>
       </c>
       <c r="G19" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="20">
@@ -3407,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>664.0</v>
+        <v>666.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>719.0</v>
+        <v>720.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3821,7 +3821,7 @@
         <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>2543.0</v>
+        <v>2553.0</v>
       </c>
       <c r="F20" t="n">
         <v>2.0</v>
@@ -3844,7 +3844,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>1592.0</v>
+        <v>1594.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2636.0</v>
+        <v>2637.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>9981.0</v>
+        <v>9986.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -721,7 +721,7 @@
         <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -1293,7 +1293,7 @@
         <v>40</v>
       </c>
       <c r="F43" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1345,7 +1345,7 @@
         <v>39</v>
       </c>
       <c r="F45" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -1371,7 +1371,7 @@
         <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1527,7 +1527,7 @@
         <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>43.0</v>
+        <v>47.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1579,7 +1579,7 @@
         <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1637,7 +1637,7 @@
         <v>2.0</v>
       </c>
       <c r="H56" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="57">
@@ -1689,7 +1689,7 @@
         <v>0.0</v>
       </c>
       <c r="H58" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="59">
@@ -1787,13 +1787,13 @@
         <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>1303.0</v>
+        <v>1306.0</v>
       </c>
       <c r="G62" t="n">
         <v>91.0</v>
       </c>
       <c r="H62" t="n">
-        <v>655.0</v>
+        <v>657.0</v>
       </c>
     </row>
     <row r="63">
@@ -1813,7 +1813,7 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="G63" t="n">
         <v>25.0</v>
@@ -1839,7 +1839,7 @@
         <v>40</v>
       </c>
       <c r="F64" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G64" t="n">
         <v>8.0</v>
@@ -1865,7 +1865,7 @@
         <v>38</v>
       </c>
       <c r="F65" t="n">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="G65" t="n">
         <v>1.0</v>
@@ -1891,13 +1891,13 @@
         <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
       <c r="G66" t="n">
         <v>10.0</v>
       </c>
       <c r="H66" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="67">
@@ -1917,7 +1917,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="G67" t="n">
         <v>4.0</v>
@@ -1943,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G68" t="n">
         <v>4.0</v>
@@ -1972,7 +1972,7 @@
         <v>169.0</v>
       </c>
       <c r="G69" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="H69" t="n">
         <v>46.0</v>
@@ -2125,7 +2125,7 @@
         <v>39</v>
       </c>
       <c r="F75" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G75" t="n">
         <v>2.0</v>
@@ -2151,7 +2151,7 @@
         <v>40</v>
       </c>
       <c r="F76" t="n">
-        <v>209.0</v>
+        <v>212.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2177,7 +2177,7 @@
         <v>38</v>
       </c>
       <c r="F77" t="n">
-        <v>179.0</v>
+        <v>180.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
@@ -2203,7 +2203,7 @@
         <v>39</v>
       </c>
       <c r="F78" t="n">
-        <v>225.0</v>
+        <v>226.0</v>
       </c>
       <c r="G78" t="n">
         <v>3.0</v>
@@ -2521,7 +2521,7 @@
         <v>1.0</v>
       </c>
       <c r="H90" t="n">
-        <v>99.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="91">
@@ -2541,13 +2541,13 @@
         <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>31.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="92">
@@ -2599,7 +2599,7 @@
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="94">
@@ -3006,13 +3006,13 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>53.0</v>
+        <v>61.0</v>
       </c>
       <c r="F13" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G13" t="n">
-        <v>203.0</v>
+        <v>208.0</v>
       </c>
     </row>
     <row r="14">
@@ -3035,7 +3035,7 @@
         <v>35.0</v>
       </c>
       <c r="G14" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="15">
@@ -3078,7 +3078,7 @@
         <v>11.0</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -3144,10 +3144,10 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>53.0</v>
+        <v>57.0</v>
       </c>
       <c r="F19" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G19" t="n">
         <v>63.0</v>
@@ -3282,7 +3282,7 @@
         <v>29</v>
       </c>
       <c r="E25" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F25" t="n">
         <v>4.0</v>
@@ -3305,13 +3305,13 @@
         <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>132.0</v>
+        <v>141.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>34.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="27">
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>78.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="28">
@@ -3351,7 +3351,7 @@
         <v>37</v>
       </c>
       <c r="E28" t="n">
-        <v>97.0</v>
+        <v>103.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3430,7 +3430,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>294.0</v>
+        <v>310.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>666.0</v>
+        <v>672.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3522,7 +3522,7 @@
         <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>2107.0</v>
+        <v>2109.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3545,7 +3545,7 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>31.0</v>
+        <v>39.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -3614,7 +3614,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>156.0</v>
+        <v>159.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3637,7 +3637,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>353.0</v>
+        <v>363.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>720.0</v>
+        <v>765.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3683,7 +3683,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3190.0</v>
+        <v>3213.0</v>
       </c>
       <c r="F14" t="n">
         <v>1.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>535.0</v>
+        <v>541.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3729,7 +3729,7 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>120.0</v>
+        <v>122.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -3752,7 +3752,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>240.0</v>
+        <v>267.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3821,7 +3821,7 @@
         <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>2553.0</v>
+        <v>2568.0</v>
       </c>
       <c r="F20" t="n">
         <v>2.0</v>
@@ -3844,13 +3844,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>1594.0</v>
+        <v>1597.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="22">
@@ -3890,7 +3890,7 @@
         <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="F23" t="n">
         <v>2.0</v>
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8722.0</v>
+        <v>8727.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2637.0</v>
+        <v>2691.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4005,7 +4005,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>5171.0</v>
+        <v>5200.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>9986.0</v>
+        <v>10055.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4663.0</v>
+        <v>4704.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>
@@ -4074,7 +4074,7 @@
         <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>1212.0</v>
+        <v>1218.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4097,7 +4097,7 @@
         <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -4120,13 +4120,13 @@
         <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>383.0</v>
+        <v>395.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="34">
@@ -4149,7 +4149,7 @@
         <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>41.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="35">
@@ -4166,7 +4166,7 @@
         <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>3008.0</v>
+        <v>3025.0</v>
       </c>
       <c r="F35" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -643,7 +643,7 @@
         <v>39</v>
       </c>
       <c r="F18" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G18" t="n">
         <v>2.0</v>
@@ -1787,13 +1787,13 @@
         <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>1306.0</v>
+        <v>1308.0</v>
       </c>
       <c r="G62" t="n">
         <v>91.0</v>
       </c>
       <c r="H62" t="n">
-        <v>657.0</v>
+        <v>658.0</v>
       </c>
     </row>
     <row r="63">
@@ -3035,7 +3035,7 @@
         <v>35.0</v>
       </c>
       <c r="G14" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="15">
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>92.0</v>
+        <v>95.0</v>
       </c>
     </row>
     <row r="28">
@@ -3351,7 +3351,7 @@
         <v>37</v>
       </c>
       <c r="E28" t="n">
-        <v>103.0</v>
+        <v>105.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>765.0</v>
+        <v>776.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3683,7 +3683,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3213.0</v>
+        <v>3215.0</v>
       </c>
       <c r="F14" t="n">
         <v>1.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>541.0</v>
+        <v>546.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8727.0</v>
+        <v>8733.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3959,7 +3959,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>4517.0</v>
+        <v>4522.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4704.0</v>
+        <v>4717.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1345,7 +1345,7 @@
         <v>39</v>
       </c>
       <c r="F45" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G45" t="n">
         <v>0.0</v>
@@ -2125,7 +2125,7 @@
         <v>39</v>
       </c>
       <c r="F75" t="n">
-        <v>153.0</v>
+        <v>152.0</v>
       </c>
       <c r="G75" t="n">
         <v>2.0</v>
@@ -2203,7 +2203,7 @@
         <v>39</v>
       </c>
       <c r="F78" t="n">
-        <v>226.0</v>
+        <v>227.0</v>
       </c>
       <c r="G78" t="n">
         <v>3.0</v>
@@ -3190,7 +3190,7 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="F21" t="n">
         <v>8.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>776.0</v>
+        <v>777.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>546.0</v>
+        <v>547.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4005,7 +4005,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>5200.0</v>
+        <v>5237.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10055.0</v>
+        <v>10062.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4717.0</v>
+        <v>4719.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -435,7 +435,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -1527,7 +1527,7 @@
         <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -2983,7 +2983,7 @@
         <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="F12" t="n">
         <v>2.0</v>
@@ -3351,7 +3351,7 @@
         <v>37</v>
       </c>
       <c r="E28" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3827,7 +3827,7 @@
         <v>2.0</v>
       </c>
       <c r="G20" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="21">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -617,7 +617,7 @@
         <v>38</v>
       </c>
       <c r="F17" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -1059,7 +1059,7 @@
         <v>40</v>
       </c>
       <c r="F34" t="n">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1943,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>118.0</v>
+        <v>120.0</v>
       </c>
       <c r="G68" t="n">
         <v>4.0</v>
@@ -2776,7 +2776,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F3" t="n">
         <v>3.0</v>
@@ -3006,7 +3006,7 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>61.0</v>
+        <v>66.0</v>
       </c>
       <c r="F13" t="n">
         <v>51.0</v>
@@ -3213,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="E22" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>95.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="28">
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>777.0</v>
+        <v>780.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3729,7 +3729,7 @@
         <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -3959,7 +3959,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>4522.0</v>
+        <v>4524.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10062.0</v>
+        <v>10077.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1917,13 +1917,13 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>127.0</v>
+        <v>128.0</v>
       </c>
       <c r="G67" t="n">
         <v>4.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="68">
@@ -2229,7 +2229,7 @@
         <v>40</v>
       </c>
       <c r="F79" t="n">
-        <v>406.0</v>
+        <v>407.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2547,7 +2547,7 @@
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>43.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="92">
@@ -3305,7 +3305,7 @@
         <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>141.0</v>
+        <v>142.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="28">
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>780.0</v>
+        <v>781.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3752,7 +3752,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2691.0</v>
+        <v>2700.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10077.0</v>
+        <v>10079.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -435,7 +435,7 @@
         <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -1371,7 +1371,7 @@
         <v>40</v>
       </c>
       <c r="F46" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G46" t="n">
         <v>0.0</v>
@@ -1527,7 +1527,7 @@
         <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G52" t="n">
         <v>4.0</v>
@@ -1605,7 +1605,7 @@
         <v>38</v>
       </c>
       <c r="F55" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G55" t="n">
         <v>3.0</v>
@@ -1637,7 +1637,7 @@
         <v>2.0</v>
       </c>
       <c r="H56" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="57">
@@ -1787,13 +1787,13 @@
         <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>1308.0</v>
+        <v>1309.0</v>
       </c>
       <c r="G62" t="n">
         <v>91.0</v>
       </c>
       <c r="H62" t="n">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
     </row>
     <row r="63">
@@ -1813,7 +1813,7 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>222.0</v>
+        <v>223.0</v>
       </c>
       <c r="G63" t="n">
         <v>25.0</v>
@@ -1943,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>120.0</v>
+        <v>122.0</v>
       </c>
       <c r="G68" t="n">
         <v>4.0</v>
@@ -2521,7 +2521,7 @@
         <v>1.0</v>
       </c>
       <c r="H90" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="91">
@@ -2541,13 +2541,13 @@
         <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>46.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="92">
@@ -2599,7 +2599,7 @@
         <v>0.0</v>
       </c>
       <c r="H93" t="n">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="94">
@@ -2983,13 +2983,13 @@
         <v>17</v>
       </c>
       <c r="E12" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F12" t="n">
         <v>2.0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -3006,7 +3006,7 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>66.0</v>
+        <v>69.0</v>
       </c>
       <c r="F13" t="n">
         <v>51.0</v>
@@ -3029,7 +3029,7 @@
         <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="F14" t="n">
         <v>35.0</v>
@@ -3144,7 +3144,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="F19" t="n">
         <v>21.0</v>
@@ -3305,13 +3305,13 @@
         <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>142.0</v>
+        <v>144.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="27">
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>781.0</v>
+        <v>782.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>547.0</v>
+        <v>549.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3752,7 +3752,7 @@
         <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>268.0</v>
+        <v>270.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8733.0</v>
+        <v>8735.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2700.0</v>
+        <v>2707.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4719.0</v>
+        <v>4726.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>
@@ -4074,7 +4074,7 @@
         <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>1218.0</v>
+        <v>1220.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4120,7 +4120,7 @@
         <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>395.0</v>
+        <v>397.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
@@ -4166,7 +4166,7 @@
         <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>3025.0</v>
+        <v>3034.0</v>
       </c>
       <c r="F35" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2547,7 +2547,7 @@
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="92">
@@ -2671,7 +2671,7 @@
         <v>39</v>
       </c>
       <c r="F96" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G96" t="n">
         <v>3.0</v>
@@ -3262,7 +3262,7 @@
         <v>1.0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3305,7 +3305,7 @@
         <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>98.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="28">
@@ -3637,7 +3637,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>363.0</v>
+        <v>365.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>782.0</v>
+        <v>786.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3683,7 +3683,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3215.0</v>
+        <v>3216.0</v>
       </c>
       <c r="F14" t="n">
         <v>1.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10079.0</v>
+        <v>10089.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4726.0</v>
+        <v>4729.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1579,7 +1579,7 @@
         <v>40</v>
       </c>
       <c r="F54" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1793,7 +1793,7 @@
         <v>91.0</v>
       </c>
       <c r="H62" t="n">
-        <v>659.0</v>
+        <v>660.0</v>
       </c>
     </row>
     <row r="63">
@@ -1891,7 +1891,7 @@
         <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="G66" t="n">
         <v>10.0</v>
@@ -1917,7 +1917,7 @@
         <v>40</v>
       </c>
       <c r="F67" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G67" t="n">
         <v>4.0</v>
@@ -1949,7 +1949,7 @@
         <v>4.0</v>
       </c>
       <c r="H68" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="69">
@@ -2547,7 +2547,7 @@
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>55.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="92">
@@ -2776,7 +2776,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F3" t="n">
         <v>3.0</v>
@@ -2986,7 +2986,7 @@
         <v>16.0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G12" t="n">
         <v>1.0</v>
@@ -3006,10 +3006,10 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>69.0</v>
+        <v>72.0</v>
       </c>
       <c r="F13" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G13" t="n">
         <v>208.0</v>
@@ -3545,7 +3545,7 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>39.0</v>
+        <v>50.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -4005,7 +4005,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>5237.0</v>
+        <v>5273.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10089.0</v>
+        <v>10110.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4074,7 +4074,7 @@
         <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>1220.0</v>
+        <v>1222.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -3012,7 +3012,7 @@
         <v>52.0</v>
       </c>
       <c r="G13" t="n">
-        <v>208.0</v>
+        <v>210.0</v>
       </c>
     </row>
     <row r="14">
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="28">
@@ -3407,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3430,7 +3430,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>310.0</v>
+        <v>312.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>672.0</v>
+        <v>688.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3476,7 +3476,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>117.0</v>
+        <v>122.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3499,7 +3499,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>212.0</v>
+        <v>216.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3821,13 +3821,13 @@
         <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>2568.0</v>
+        <v>2613.0</v>
       </c>
       <c r="F20" t="n">
         <v>2.0</v>
       </c>
       <c r="G20" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
     </row>
     <row r="21">
@@ -3844,7 +3844,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>1597.0</v>
+        <v>1601.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>786.0</v>
+        <v>791.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>549.0</v>
+        <v>550.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10110.0</v>
+        <v>10117.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1637,7 +1637,7 @@
         <v>2.0</v>
       </c>
       <c r="H56" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="57">
@@ -1793,7 +1793,7 @@
         <v>91.0</v>
       </c>
       <c r="H62" t="n">
-        <v>660.0</v>
+        <v>662.0</v>
       </c>
     </row>
     <row r="63">
@@ -1897,7 +1897,7 @@
         <v>10.0</v>
       </c>
       <c r="H66" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="67">
@@ -1943,7 +1943,7 @@
         <v>38</v>
       </c>
       <c r="F68" t="n">
-        <v>122.0</v>
+        <v>124.0</v>
       </c>
       <c r="G68" t="n">
         <v>4.0</v>
@@ -2151,7 +2151,7 @@
         <v>40</v>
       </c>
       <c r="F76" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2822,7 +2822,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F5" t="n">
         <v>2.0</v>
@@ -3012,7 +3012,7 @@
         <v>52.0</v>
       </c>
       <c r="G13" t="n">
-        <v>210.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="14">
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8735.0</v>
+        <v>8739.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2707.0</v>
+        <v>2712.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3959,7 +3959,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>4524.0</v>
+        <v>4526.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -4005,7 +4005,7 @@
         <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>5273.0</v>
+        <v>5278.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -383,7 +383,7 @@
         <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -1556,10 +1556,10 @@
         <v>38.0</v>
       </c>
       <c r="G53" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H53" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="54">
@@ -2521,7 +2521,7 @@
         <v>1.0</v>
       </c>
       <c r="H90" t="n">
-        <v>105.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="91">
@@ -2541,13 +2541,13 @@
         <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>64.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="92">
@@ -2937,7 +2937,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -2986,7 +2986,7 @@
         <v>16.0</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G12" t="n">
         <v>1.0</v>
@@ -3006,10 +3006,10 @@
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>72.0</v>
+        <v>85.0</v>
       </c>
       <c r="F13" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G13" t="n">
         <v>212.0</v>
@@ -3029,7 +3029,7 @@
         <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="F14" t="n">
         <v>35.0</v>
@@ -3213,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="E22" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -3305,7 +3305,7 @@
         <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3453,7 +3453,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>688.0</v>
+        <v>683.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>791.0</v>
+        <v>794.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3683,7 +3683,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3216.0</v>
+        <v>3221.0</v>
       </c>
       <c r="F14" t="n">
         <v>1.0</v>
@@ -3827,7 +3827,7 @@
         <v>2.0</v>
       </c>
       <c r="G20" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="21">
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2712.0</v>
+        <v>2714.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10117.0</v>
+        <v>10118.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4729.0</v>
+        <v>4731.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>
@@ -4120,7 +4120,7 @@
         <v>31</v>
       </c>
       <c r="E33" t="n">
-        <v>397.0</v>
+        <v>403.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
@@ -4166,7 +4166,7 @@
         <v>37</v>
       </c>
       <c r="E35" t="n">
-        <v>3034.0</v>
+        <v>3041.0</v>
       </c>
       <c r="F35" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1787,13 +1787,13 @@
         <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>1309.0</v>
+        <v>1311.0</v>
       </c>
       <c r="G62" t="n">
         <v>91.0</v>
       </c>
       <c r="H62" t="n">
-        <v>662.0</v>
+        <v>663.0</v>
       </c>
     </row>
     <row r="63">
@@ -1813,7 +1813,7 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>223.0</v>
+        <v>224.0</v>
       </c>
       <c r="G63" t="n">
         <v>25.0</v>
@@ -1891,7 +1891,7 @@
         <v>39</v>
       </c>
       <c r="F66" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G66" t="n">
         <v>10.0</v>
@@ -2547,7 +2547,7 @@
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="92">
@@ -3334,7 +3334,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="28">
@@ -3637,7 +3637,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>365.0</v>
+        <v>366.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3660,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>794.0</v>
+        <v>823.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3706,7 +3706,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>550.0</v>
+        <v>555.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3913,7 +3913,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8739.0</v>
+        <v>8742.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3936,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2714.0</v>
+        <v>2719.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3982,7 +3982,7 @@
         <v>23</v>
       </c>
       <c r="E27" t="n">
-        <v>482.0</v>
+        <v>483.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4028,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10118.0</v>
+        <v>10138.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4051,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4731.0</v>
+        <v>4736.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>
@@ -4097,7 +4097,7 @@
         <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -4149,7 +4149,7 @@
         <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="35">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="41">
   <si>
     <t>Area</t>
   </si>
@@ -1813,7 +1813,7 @@
         <v>39</v>
       </c>
       <c r="F63" t="n">
-        <v>224.0</v>
+        <v>227.0</v>
       </c>
       <c r="G63" t="n">
         <v>25.0</v>
@@ -2541,13 +2541,13 @@
         <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
       </c>
       <c r="H91" t="n">
-        <v>73.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="92">
@@ -2816,16 +2816,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -2839,16 +2839,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -2865,13 +2865,13 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -2885,10 +2885,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
         <v>1.0</v>
@@ -2911,13 +2911,13 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -2934,10 +2934,10 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -2957,13 +2957,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -2974,22 +2974,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="F12" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -3003,16 +3003,16 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
-        <v>85.0</v>
+        <v>16.0</v>
       </c>
       <c r="F13" t="n">
-        <v>53.0</v>
+        <v>6.0</v>
       </c>
       <c r="G13" t="n">
-        <v>212.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="14">
@@ -3026,16 +3026,16 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>33.0</v>
+        <v>86.0</v>
       </c>
       <c r="F14" t="n">
-        <v>35.0</v>
+        <v>53.0</v>
       </c>
       <c r="G14" t="n">
-        <v>16.0</v>
+        <v>212.0</v>
       </c>
     </row>
     <row r="15">
@@ -3049,16 +3049,16 @@
         <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="16">
@@ -3072,16 +3072,16 @@
         <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="F16" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="17">
@@ -3092,19 +3092,19 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="F17" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G17" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -3118,16 +3118,16 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="19">
@@ -3141,16 +3141,16 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>58.0</v>
+        <v>17.0</v>
       </c>
       <c r="F19" t="n">
-        <v>21.0</v>
+        <v>6.0</v>
       </c>
       <c r="G19" t="n">
-        <v>63.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="20">
@@ -3161,19 +3161,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>6.0</v>
+        <v>58.0</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0</v>
+        <v>21.0</v>
       </c>
       <c r="G20" t="n">
-        <v>16.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="21">
@@ -3187,16 +3187,16 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" t="n">
-        <v>26.0</v>
+        <v>6.0</v>
       </c>
       <c r="F21" t="n">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="G21" t="n">
-        <v>38.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="22">
@@ -3207,19 +3207,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E22" t="n">
-        <v>69.0</v>
+        <v>26.0</v>
       </c>
       <c r="F22" t="n">
-        <v>18.0</v>
+        <v>8.0</v>
       </c>
       <c r="G22" t="n">
-        <v>29.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="23">
@@ -3233,16 +3233,16 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>15.0</v>
+        <v>69.0</v>
       </c>
       <c r="F23" t="n">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="24">
@@ -3256,13 +3256,13 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
@@ -3279,16 +3279,16 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="F25" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" t="n">
-        <v>64.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3299,19 +3299,19 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E26" t="n">
-        <v>147.0</v>
+        <v>11.0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G26" t="n">
-        <v>43.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="27">
@@ -3325,16 +3325,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0</v>
+        <v>147.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>104.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="28">
@@ -3348,15 +3348,38 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>104.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
         <v>37</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E29" t="n">
         <v>106.0</v>
       </c>
-      <c r="F28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="F29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3407,7 +3430,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>19.0</v>
+        <v>24.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3453,7 +3476,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>683.0</v>
+        <v>687.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3476,7 +3499,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>122.0</v>
+        <v>134.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3499,7 +3522,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>216.0</v>
+        <v>220.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3637,7 +3660,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>366.0</v>
+        <v>367.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3683,7 +3706,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3221.0</v>
+        <v>3222.0</v>
       </c>
       <c r="F14" t="n">
         <v>1.0</v>
@@ -3706,7 +3729,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="n">
-        <v>555.0</v>
+        <v>556.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3821,7 +3844,7 @@
         <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>2613.0</v>
+        <v>2644.0</v>
       </c>
       <c r="F20" t="n">
         <v>2.0</v>
@@ -3844,7 +3867,7 @@
         <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>1601.0</v>
+        <v>1603.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3890,7 +3913,7 @@
         <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>293.0</v>
+        <v>296.0</v>
       </c>
       <c r="F23" t="n">
         <v>2.0</v>
@@ -3913,7 +3936,7 @@
         <v>34</v>
       </c>
       <c r="E24" t="n">
-        <v>8742.0</v>
+        <v>8748.0</v>
       </c>
       <c r="F24" t="n">
         <v>18.0</v>
@@ -3936,7 +3959,7 @@
         <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>2719.0</v>
+        <v>2721.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3959,7 +3982,7 @@
         <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>4526.0</v>
+        <v>4527.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -4028,7 +4051,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>10138.0</v>
+        <v>10150.0</v>
       </c>
       <c r="F29" t="n">
         <v>3.0</v>
@@ -4051,7 +4074,7 @@
         <v>27</v>
       </c>
       <c r="E30" t="n">
-        <v>4736.0</v>
+        <v>4737.0</v>
       </c>
       <c r="F30" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -4212,7 +4212,7 @@
         <v>32</v>
       </c>
       <c r="E36" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="37">
   <si>
     <t>Area</t>
   </si>
@@ -85,15 +85,9 @@
     <t>Lodi</t>
   </si>
   <si>
-    <t>Milano</t>
-  </si>
-  <si>
     <t>Pavia</t>
   </si>
   <si>
-    <t>Varese</t>
-  </si>
-  <si>
     <t>Alessandria</t>
   </si>
   <si>
@@ -101,12 +95,6 @@
   </si>
   <si>
     <t>Cuneo</t>
-  </si>
-  <si>
-    <t>Novara</t>
-  </si>
-  <si>
-    <t>Vercelli</t>
   </si>
   <si>
     <t>Lucca</t>
@@ -224,7 +212,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>5.0</v>
@@ -250,7 +238,7 @@
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
         <v>1.0</v>
@@ -276,7 +264,7 @@
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -302,10 +290,10 @@
         <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -328,10 +316,10 @@
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -354,10 +342,10 @@
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -380,10 +368,10 @@
         <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -406,10 +394,10 @@
         <v>18</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -432,10 +420,10 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
-        <v>50.0</v>
+        <v>43.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -458,10 +446,10 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -484,16 +472,16 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13">
@@ -510,10 +498,10 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0</v>
+        <v>34.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -536,10 +524,10 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -562,10 +550,10 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0</v>
+        <v>24.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -588,10 +576,10 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>12.0</v>
+        <v>70.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -614,7 +602,7 @@
         <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
         <v>21.0</v>
@@ -640,7 +628,7 @@
         <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
         <v>26.0</v>
@@ -666,7 +654,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
         <v>15.0</v>
@@ -692,10 +680,10 @@
         <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F20" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -718,10 +706,10 @@
         <v>22</v>
       </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F21" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -744,16 +732,16 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F22" t="n">
-        <v>8.0</v>
+        <v>15.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="23">
@@ -770,16 +758,16 @@
         <v>23</v>
       </c>
       <c r="E23" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>6.0</v>
+        <v>46.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -796,16 +784,16 @@
         <v>23</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F24" t="n">
-        <v>8.0</v>
+        <v>50.0</v>
       </c>
       <c r="G24" t="n">
         <v>0.0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="25">
@@ -816,16 +804,16 @@
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0</v>
+        <v>13.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -842,16 +830,16 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>4.0</v>
+        <v>22.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -868,16 +856,16 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" t="s">
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0</v>
+        <v>40.0</v>
       </c>
       <c r="G27" t="n">
         <v>0.0</v>
@@ -894,16 +882,16 @@
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0</v>
+        <v>19.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -923,13 +911,13 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F29" t="n">
-        <v>3.0</v>
+        <v>40.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -949,13 +937,13 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F30" t="n">
-        <v>5.0</v>
+        <v>52.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -978,10 +966,10 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F31" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1001,16 +989,16 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1027,16 +1015,16 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F33" t="n">
-        <v>41.0</v>
+        <v>29.0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1050,16 +1038,16 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F34" t="n">
-        <v>54.0</v>
+        <v>6.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1076,16 +1064,16 @@
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>18.0</v>
+        <v>13.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1102,19 +1090,19 @@
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F36" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1128,19 +1116,19 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F37" t="n">
-        <v>29.0</v>
+        <v>2.0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1154,16 +1142,16 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1177,25 +1165,25 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F39" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="40">
@@ -1203,19 +1191,19 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F40" t="n">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1229,19 +1217,19 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D41" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F41" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1255,25 +1243,25 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F42" t="n">
-        <v>2.0</v>
+        <v>50.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="43">
@@ -1281,25 +1269,25 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F43" t="n">
-        <v>13.0</v>
+        <v>41.0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="44">
@@ -1307,25 +1295,25 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F44" t="n">
-        <v>6.0</v>
+        <v>89.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="45">
@@ -1333,25 +1321,25 @@
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F45" t="n">
-        <v>13.0</v>
+        <v>31.0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="46">
@@ -1359,25 +1347,25 @@
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F46" t="n">
-        <v>25.0</v>
+        <v>41.0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="47">
@@ -1385,25 +1373,25 @@
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F47" t="n">
-        <v>2.0</v>
+        <v>80.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="48">
@@ -1411,25 +1399,25 @@
         <v>8</v>
       </c>
       <c r="B48" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F48" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
         <v>0.0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="49">
@@ -1443,19 +1431,19 @@
         <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F49" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1469,13 +1457,13 @@
         <v>11</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F50" t="n">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -1495,13 +1483,13 @@
         <v>11</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F51" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1518,22 +1506,22 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>49.0</v>
+        <v>1311.0</v>
       </c>
       <c r="G52" t="n">
-        <v>4.0</v>
+        <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>62.0</v>
+        <v>663.0</v>
       </c>
     </row>
     <row r="53">
@@ -1544,22 +1532,22 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>38.0</v>
+        <v>228.0</v>
       </c>
       <c r="G53" t="n">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
       <c r="H53" t="n">
-        <v>29.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="54">
@@ -1570,22 +1558,22 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F54" t="n">
-        <v>81.0</v>
+        <v>249.0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H54" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="55">
@@ -1596,22 +1584,22 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>39.0</v>
+        <v>67.0</v>
       </c>
       <c r="G55" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H55" t="n">
-        <v>142.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="56">
@@ -1622,22 +1610,22 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>47.0</v>
+        <v>117.0</v>
       </c>
       <c r="G56" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="H56" t="n">
-        <v>27.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="57">
@@ -1648,22 +1636,22 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E57" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>112.0</v>
+        <v>129.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H57" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="58">
@@ -1674,22 +1662,22 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0</v>
+        <v>124.0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H58" t="n">
-        <v>3.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="59">
@@ -1700,22 +1688,22 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E59" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>3.0</v>
+        <v>169.0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="60">
@@ -1726,22 +1714,22 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>7.0</v>
+        <v>92.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="61">
@@ -1752,22 +1740,22 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F61" t="n">
-        <v>4.0</v>
+        <v>42.0</v>
       </c>
       <c r="G61" t="n">
         <v>0.0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="62">
@@ -1778,22 +1766,22 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>1311.0</v>
+        <v>78.0</v>
       </c>
       <c r="G62" t="n">
-        <v>91.0</v>
+        <v>0.0</v>
       </c>
       <c r="H62" t="n">
-        <v>663.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="63">
@@ -1804,22 +1792,22 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F63" t="n">
-        <v>227.0</v>
+        <v>128.0</v>
       </c>
       <c r="G63" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="H63" t="n">
-        <v>62.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="64">
@@ -1830,22 +1818,22 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" t="s">
         <v>34</v>
       </c>
-      <c r="E64" t="s">
-        <v>40</v>
-      </c>
       <c r="F64" t="n">
-        <v>249.0</v>
+        <v>164.0</v>
       </c>
       <c r="G64" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H64" t="n">
-        <v>14.0</v>
+        <v>305.0</v>
       </c>
     </row>
     <row r="65">
@@ -1856,22 +1844,22 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" t="s">
         <v>35</v>
       </c>
-      <c r="E65" t="s">
-        <v>38</v>
-      </c>
       <c r="F65" t="n">
-        <v>67.0</v>
+        <v>199.0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H65" t="n">
-        <v>6.0</v>
+        <v>142.0</v>
       </c>
     </row>
     <row r="66">
@@ -1882,22 +1870,22 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>117.0</v>
+        <v>350.0</v>
       </c>
       <c r="G66" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H66" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="67">
@@ -1908,22 +1896,22 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F67" t="n">
-        <v>129.0</v>
+        <v>123.0</v>
       </c>
       <c r="G67" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H67" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="68">
@@ -1934,22 +1922,22 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F68" t="n">
-        <v>124.0</v>
+        <v>80.0</v>
       </c>
       <c r="G68" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="H68" t="n">
-        <v>99.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="69">
@@ -1960,22 +1948,22 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>169.0</v>
+        <v>61.0</v>
       </c>
       <c r="G69" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="H69" t="n">
-        <v>46.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1986,22 +1974,22 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F70" t="n">
-        <v>92.0</v>
+        <v>8.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -2012,22 +2000,22 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F71" t="n">
-        <v>9.0</v>
+        <v>31.0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H71" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2038,16 +2026,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F72" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2064,22 +2052,22 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
-        <v>5.0</v>
+        <v>43.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="74">
@@ -2090,22 +2078,22 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>74.0</v>
+        <v>38.0</v>
       </c>
       <c r="G74" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>126.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="75">
@@ -2116,22 +2104,22 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F75" t="n">
-        <v>152.0</v>
+        <v>24.0</v>
       </c>
       <c r="G75" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -2142,22 +2130,22 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F76" t="n">
-        <v>213.0</v>
+        <v>0.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="77">
@@ -2168,22 +2156,22 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E77" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n">
-        <v>180.0</v>
+        <v>0.0</v>
       </c>
       <c r="G77" t="n">
         <v>0.0</v>
       </c>
       <c r="H77" t="n">
-        <v>305.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="78">
@@ -2194,22 +2182,22 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E78" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F78" t="n">
-        <v>227.0</v>
+        <v>24.0</v>
       </c>
       <c r="G78" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H78" t="n">
-        <v>142.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -2220,22 +2208,22 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E79" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n">
-        <v>407.0</v>
+        <v>133.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H79" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2246,463 +2234,21 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E80" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>123.0</v>
+        <v>35.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
       </c>
       <c r="H80" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>8</v>
-      </c>
-      <c r="B81" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D81" t="s">
-        <v>27</v>
-      </c>
-      <c r="E81" t="s">
-        <v>39</v>
-      </c>
-      <c r="F81" t="n">
-        <v>79.0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" t="s">
-        <v>14</v>
-      </c>
-      <c r="D82" t="s">
-        <v>27</v>
-      </c>
-      <c r="E82" t="s">
-        <v>40</v>
-      </c>
-      <c r="F82" t="n">
-        <v>61.0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>8</v>
-      </c>
-      <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-      <c r="D83" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83" t="s">
-        <v>38</v>
-      </c>
-      <c r="F83" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>8</v>
-      </c>
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" t="s">
-        <v>14</v>
-      </c>
-      <c r="D84" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84" t="s">
-        <v>39</v>
-      </c>
-      <c r="F84" t="n">
-        <v>31.0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>8</v>
-      </c>
-      <c r="B85" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" t="s">
-        <v>14</v>
-      </c>
-      <c r="D85" t="s">
-        <v>28</v>
-      </c>
-      <c r="E85" t="s">
-        <v>40</v>
-      </c>
-      <c r="F85" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>8</v>
-      </c>
-      <c r="B86" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" t="s">
-        <v>14</v>
-      </c>
-      <c r="D86" t="s">
-        <v>29</v>
-      </c>
-      <c r="E86" t="s">
-        <v>38</v>
-      </c>
-      <c r="F86" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>8</v>
-      </c>
-      <c r="B87" t="s">
-        <v>10</v>
-      </c>
-      <c r="C87" t="s">
-        <v>14</v>
-      </c>
-      <c r="D87" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" t="s">
-        <v>39</v>
-      </c>
-      <c r="F87" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>8</v>
-      </c>
-      <c r="B88" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" t="s">
-        <v>14</v>
-      </c>
-      <c r="D88" t="s">
-        <v>29</v>
-      </c>
-      <c r="E88" t="s">
-        <v>40</v>
-      </c>
-      <c r="F88" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>8</v>
-      </c>
-      <c r="B89" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" t="s">
-        <v>14</v>
-      </c>
-      <c r="D89" t="s">
-        <v>30</v>
-      </c>
-      <c r="E89" t="s">
-        <v>38</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>8</v>
-      </c>
-      <c r="B90" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" t="s">
-        <v>31</v>
-      </c>
-      <c r="E90" t="s">
-        <v>38</v>
-      </c>
-      <c r="F90" t="n">
-        <v>43.0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>109.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>8</v>
-      </c>
-      <c r="B91" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" t="s">
-        <v>31</v>
-      </c>
-      <c r="E91" t="s">
-        <v>39</v>
-      </c>
-      <c r="F91" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>82.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>8</v>
-      </c>
-      <c r="B92" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92" t="s">
-        <v>31</v>
-      </c>
-      <c r="E92" t="s">
-        <v>40</v>
-      </c>
-      <c r="F92" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>8</v>
-      </c>
-      <c r="B93" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93" t="s">
-        <v>36</v>
-      </c>
-      <c r="E93" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>8</v>
-      </c>
-      <c r="B94" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94" t="s">
-        <v>36</v>
-      </c>
-      <c r="E94" t="s">
-        <v>39</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>29.0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>8</v>
-      </c>
-      <c r="B95" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95" t="s">
-        <v>37</v>
-      </c>
-      <c r="E95" t="s">
-        <v>38</v>
-      </c>
-      <c r="F95" t="n">
-        <v>24.0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>8</v>
-      </c>
-      <c r="B96" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" t="s">
-        <v>15</v>
-      </c>
-      <c r="D96" t="s">
-        <v>37</v>
-      </c>
-      <c r="E96" t="s">
-        <v>39</v>
-      </c>
-      <c r="F96" t="n">
-        <v>133.0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>8</v>
-      </c>
-      <c r="B97" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" t="s">
-        <v>15</v>
-      </c>
-      <c r="D97" t="s">
-        <v>37</v>
-      </c>
-      <c r="E97" t="s">
-        <v>40</v>
-      </c>
-      <c r="F97" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H97" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2750,13 +2296,13 @@
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F2" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2773,16 +2319,16 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -2793,16 +2339,16 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -2816,16 +2362,16 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F5" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -2839,19 +2385,19 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="7">
@@ -2862,16 +2408,16 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -2885,16 +2431,16 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F8" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -2914,10 +2460,10 @@
         <v>26</v>
       </c>
       <c r="E9" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="F9" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -2928,22 +2474,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="F10" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -2951,22 +2497,22 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>6.0</v>
+        <v>97.0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0</v>
+        <v>59.0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0</v>
+        <v>218.0</v>
       </c>
     </row>
     <row r="12">
@@ -2974,22 +2520,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0</v>
+        <v>37.0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="13">
@@ -3003,13 +2549,13 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="F13" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" t="n">
         <v>1.0</v>
@@ -3026,16 +2572,16 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>86.0</v>
+        <v>12.0</v>
       </c>
       <c r="F14" t="n">
-        <v>53.0</v>
+        <v>5.0</v>
       </c>
       <c r="G14" t="n">
-        <v>212.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -3046,19 +2592,19 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>33.0</v>
+        <v>14.0</v>
       </c>
       <c r="F15" t="n">
-        <v>35.0</v>
+        <v>4.0</v>
       </c>
       <c r="G15" t="n">
-        <v>16.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="16">
@@ -3069,16 +2615,16 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G16" t="n">
         <v>1.0</v>
@@ -3092,19 +2638,19 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>11.0</v>
+        <v>60.0</v>
       </c>
       <c r="F17" t="n">
-        <v>5.0</v>
+        <v>22.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="18">
@@ -3115,19 +2661,19 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>14.0</v>
+        <v>19.0</v>
       </c>
       <c r="F18" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="G18" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -3138,19 +2684,19 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>17.0</v>
+        <v>58.0</v>
       </c>
       <c r="F19" t="n">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="20">
@@ -3161,19 +2707,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>58.0</v>
+        <v>15.0</v>
       </c>
       <c r="F20" t="n">
-        <v>21.0</v>
+        <v>4.0</v>
       </c>
       <c r="G20" t="n">
-        <v>63.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -3184,19 +2730,19 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -3207,19 +2753,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>26.0</v>
+        <v>147.0</v>
       </c>
       <c r="F22" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>38.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="23">
@@ -3230,19 +2776,19 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>69.0</v>
+        <v>0.0</v>
       </c>
       <c r="F23" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>29.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="24">
@@ -3253,133 +2799,18 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>15.0</v>
+        <v>106.0</v>
       </c>
       <c r="F24" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" t="n">
-        <v>11.0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>64.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" t="n">
-        <v>147.0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>43.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>104.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>37</v>
-      </c>
-      <c r="E29" t="n">
-        <v>106.0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G29" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3453,7 +2884,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>312.0</v>
+        <v>332.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3476,7 +2907,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>687.0</v>
+        <v>662.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3499,7 +2930,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>134.0</v>
+        <v>239.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3522,7 +2953,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>220.0</v>
+        <v>555.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3568,7 +2999,7 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>50.0</v>
+        <v>19.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -3591,13 +3022,13 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>95.0</v>
+        <v>977.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="10">
@@ -3608,19 +3039,19 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>53.0</v>
+        <v>1052.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="11">
@@ -3631,13 +3062,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>159.0</v>
+        <v>808.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3660,10 +3091,10 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>367.0</v>
+        <v>3223.0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -3677,13 +3108,13 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>823.0</v>
+        <v>270.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3700,16 +3131,16 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>3222.0</v>
+        <v>126.0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -3720,16 +3151,16 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>556.0</v>
+        <v>258.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3743,22 +3174,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>123.0</v>
+        <v>2669.0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="17">
@@ -3766,22 +3197,22 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>270.0</v>
+        <v>1499.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="18">
@@ -3789,22 +3220,22 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E18" t="n">
-        <v>126.0</v>
+        <v>0.0</v>
       </c>
       <c r="F18" t="n">
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
@@ -3818,13 +3249,13 @@
         <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>49.0</v>
+        <v>516.0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" t="n">
         <v>0.0</v>
@@ -3838,19 +3269,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>2644.0</v>
+        <v>8748.0</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="G20" t="n">
-        <v>37.0</v>
+        <v>182.0</v>
       </c>
     </row>
     <row r="21">
@@ -3861,19 +3292,19 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>1603.0</v>
+        <v>2721.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>39.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -3884,19 +3315,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0</v>
+        <v>4527.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="23">
@@ -3907,19 +3338,19 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>296.0</v>
+        <v>3286.0</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="24">
@@ -3930,19 +3361,19 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>8748.0</v>
+        <v>8973.0</v>
       </c>
       <c r="F24" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="G24" t="n">
-        <v>182.0</v>
+        <v>220.0</v>
       </c>
     </row>
     <row r="25">
@@ -3953,19 +3384,19 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>2721.0</v>
+        <v>4739.0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" t="n">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="26">
@@ -3976,19 +3407,19 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4527.0</v>
+        <v>1222.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -3999,19 +3430,19 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>483.0</v>
+        <v>403.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="28">
@@ -4022,19 +3453,19 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E28" t="n">
-        <v>5278.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>113.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="29">
@@ -4045,19 +3476,19 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>10150.0</v>
+        <v>3041.0</v>
       </c>
       <c r="F29" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>222.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -4068,156 +3499,18 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>4737.0</v>
+        <v>19.0</v>
       </c>
       <c r="F30" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" t="s">
-        <v>28</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1222.0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" t="n">
-        <v>148.0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="D33" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" t="n">
-        <v>403.0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>46.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35" t="n">
-        <v>3041.0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G36" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1307,13 +1307,13 @@
         <v>36</v>
       </c>
       <c r="F44" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
       </c>
       <c r="H44" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="45">
@@ -1671,7 +1671,7 @@
         <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G58" t="n">
         <v>4.0</v>
@@ -2483,10 +2483,10 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F10" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G10" t="n">
         <v>1.0</v>
@@ -2506,7 +2506,7 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>97.0</v>
+        <v>100.0</v>
       </c>
       <c r="F11" t="n">
         <v>59.0</v>
@@ -3022,7 +3022,7 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>977.0</v>
+        <v>986.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>808.0</v>
+        <v>809.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4527.0</v>
+        <v>4529.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3344,7 +3344,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3286.0</v>
+        <v>3290.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2087,13 +2087,13 @@
         <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>82.0</v>
+        <v>88.0</v>
       </c>
     </row>
     <row r="75">
@@ -2145,7 +2145,7 @@
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="77">
@@ -2759,7 +2759,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>147.0</v>
+        <v>150.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -2788,7 +2788,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>104.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="24">
@@ -2805,7 +2805,7 @@
         <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>106.0</v>
+        <v>109.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>809.0</v>
+        <v>814.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>3223.0</v>
+        <v>3228.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3114,7 +3114,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>270.0</v>
+        <v>272.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4739.0</v>
+        <v>4766.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1222.0</v>
+        <v>1225.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3436,7 +3436,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>403.0</v>
+        <v>406.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -3482,7 +3482,7 @@
         <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>3041.0</v>
+        <v>3046.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1365,7 +1365,7 @@
         <v>2.0</v>
       </c>
       <c r="H46" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="47">
@@ -1547,7 +1547,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" t="n">
-        <v>62.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="54">
@@ -1593,7 +1593,7 @@
         <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1619,7 +1619,7 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -1645,7 +1645,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1879,7 +1879,7 @@
         <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>350.0</v>
+        <v>352.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -2716,7 +2716,7 @@
         <v>15.0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G20" t="n">
         <v>0.0</v>
@@ -2805,7 +2805,7 @@
         <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>1052.0</v>
+        <v>1054.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3281,7 +3281,7 @@
         <v>18.0</v>
       </c>
       <c r="G20" t="n">
-        <v>182.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="21">
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2721.0</v>
+        <v>2733.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>8973.0</v>
+        <v>8979.0</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4766.0</v>
+        <v>4769.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1515,13 +1515,13 @@
         <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>1311.0</v>
+        <v>1314.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>663.0</v>
+        <v>666.0</v>
       </c>
     </row>
     <row r="53">
@@ -1619,7 +1619,7 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>118.0</v>
+        <v>120.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -1697,7 +1697,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>169.0</v>
+        <v>170.0</v>
       </c>
       <c r="G59" t="n">
         <v>13.0</v>
@@ -1723,7 +1723,7 @@
         <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2759,7 +2759,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>814.0</v>
+        <v>815.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3275,7 +3275,7 @@
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>8748.0</v>
+        <v>8751.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2733.0</v>
+        <v>2734.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2512,7 +2512,7 @@
         <v>59.0</v>
       </c>
       <c r="G11" t="n">
-        <v>218.0</v>
+        <v>219.0</v>
       </c>
     </row>
     <row r="12">
@@ -3189,7 +3189,7 @@
         <v>2.0</v>
       </c>
       <c r="G16" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="17">
@@ -3436,7 +3436,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>406.0</v>
+        <v>407.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -969,7 +969,7 @@
         <v>34</v>
       </c>
       <c r="F31" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1593,7 +1593,7 @@
         <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -2460,7 +2460,7 @@
         <v>26</v>
       </c>
       <c r="E9" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="F9" t="n">
         <v>1.0</v>
@@ -2999,7 +2999,7 @@
         <v>22</v>
       </c>
       <c r="E8" t="n">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -3022,7 +3022,7 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>986.0</v>
+        <v>988.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>1054.0</v>
+        <v>1058.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>3228.0</v>
+        <v>3229.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2734.0</v>
+        <v>2747.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3344,7 +3344,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3290.0</v>
+        <v>3304.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4769.0</v>
+        <v>4775.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1225.0</v>
+        <v>1227.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -501,7 +501,7 @@
         <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -761,7 +761,7 @@
         <v>35</v>
       </c>
       <c r="F23" t="n">
-        <v>46.0</v>
+        <v>45.0</v>
       </c>
       <c r="G23" t="n">
         <v>1.0</v>
@@ -1261,7 +1261,7 @@
         <v>4.0</v>
       </c>
       <c r="H42" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
     </row>
     <row r="43">
@@ -1625,7 +1625,7 @@
         <v>10.0</v>
       </c>
       <c r="H56" t="n">
-        <v>20.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="57">
@@ -2391,7 +2391,7 @@
         <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -2486,7 +2486,7 @@
         <v>18.0</v>
       </c>
       <c r="F10" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G10" t="n">
         <v>1.0</v>
@@ -2506,10 +2506,10 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>100.0</v>
+        <v>113.0</v>
       </c>
       <c r="F11" t="n">
-        <v>59.0</v>
+        <v>61.0</v>
       </c>
       <c r="G11" t="n">
         <v>219.0</v>
@@ -2529,7 +2529,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>31.0</v>
+        <v>35.0</v>
       </c>
       <c r="F12" t="n">
         <v>37.0</v>
@@ -2575,7 +2575,7 @@
         <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F14" t="n">
         <v>5.0</v>
@@ -2644,7 +2644,7 @@
         <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>60.0</v>
+        <v>62.0</v>
       </c>
       <c r="F17" t="n">
         <v>22.0</v>
@@ -2861,7 +2861,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>24.0</v>
+        <v>37.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -2930,7 +2930,7 @@
         <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>239.0</v>
+        <v>242.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -2953,7 +2953,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>555.0</v>
+        <v>564.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>815.0</v>
+        <v>817.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3183,7 +3183,7 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>2669.0</v>
+        <v>2670.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3206,7 +3206,7 @@
         <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>1499.0</v>
+        <v>1500.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3252,7 +3252,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>516.0</v>
+        <v>521.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2747.0</v>
+        <v>2752.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4529.0</v>
+        <v>4532.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4775.0</v>
+        <v>4776.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -839,7 +839,7 @@
         <v>35</v>
       </c>
       <c r="F26" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -891,7 +891,7 @@
         <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -998,7 +998,7 @@
         <v>22.0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -1261,7 +1261,7 @@
         <v>4.0</v>
       </c>
       <c r="H42" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="43">
@@ -1281,7 +1281,7 @@
         <v>35</v>
       </c>
       <c r="F43" t="n">
-        <v>41.0</v>
+        <v>43.0</v>
       </c>
       <c r="G43" t="n">
         <v>2.0</v>
@@ -1339,7 +1339,7 @@
         <v>3.0</v>
       </c>
       <c r="H45" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="46">
@@ -1515,13 +1515,13 @@
         <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>1314.0</v>
+        <v>1318.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>666.0</v>
+        <v>669.0</v>
       </c>
     </row>
     <row r="53">
@@ -1593,7 +1593,7 @@
         <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G55" t="n">
         <v>1.0</v>
@@ -1619,13 +1619,13 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
       </c>
       <c r="H56" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="57">
@@ -1645,7 +1645,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1677,7 +1677,7 @@
         <v>4.0</v>
       </c>
       <c r="H58" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="59">
@@ -1697,7 +1697,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>170.0</v>
+        <v>171.0</v>
       </c>
       <c r="G59" t="n">
         <v>13.0</v>
@@ -1723,7 +1723,7 @@
         <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1905,7 +1905,7 @@
         <v>34</v>
       </c>
       <c r="F67" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -2087,13 +2087,13 @@
         <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>39.0</v>
+        <v>42.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>88.0</v>
+        <v>96.0</v>
       </c>
     </row>
     <row r="75">
@@ -2506,13 +2506,13 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>113.0</v>
+        <v>118.0</v>
       </c>
       <c r="F11" t="n">
-        <v>61.0</v>
+        <v>67.0</v>
       </c>
       <c r="G11" t="n">
-        <v>219.0</v>
+        <v>223.0</v>
       </c>
     </row>
     <row r="12">
@@ -2529,7 +2529,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>35.0</v>
+        <v>37.0</v>
       </c>
       <c r="F12" t="n">
         <v>37.0</v>
@@ -2644,13 +2644,13 @@
         <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>62.0</v>
+        <v>64.0</v>
       </c>
       <c r="F17" t="n">
         <v>22.0</v>
       </c>
       <c r="G17" t="n">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
     </row>
     <row r="18">
@@ -2690,10 +2690,10 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G19" t="n">
         <v>29.0</v>
@@ -2788,7 +2788,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>110.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="24">
@@ -2805,7 +2805,7 @@
         <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -2861,7 +2861,7 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -2884,7 +2884,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>332.0</v>
+        <v>337.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -2907,7 +2907,7 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>662.0</v>
+        <v>666.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -2953,7 +2953,7 @@
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>564.0</v>
+        <v>566.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3022,7 +3022,7 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>988.0</v>
+        <v>990.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>1058.0</v>
+        <v>1061.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>817.0</v>
+        <v>829.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>3229.0</v>
+        <v>3240.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3114,7 +3114,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3160,7 +3160,7 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>258.0</v>
+        <v>261.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3183,7 +3183,7 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>2670.0</v>
+        <v>2692.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3212,7 +3212,7 @@
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="18">
@@ -3252,7 +3252,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>521.0</v>
+        <v>522.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -3275,7 +3275,7 @@
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>8751.0</v>
+        <v>8759.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2752.0</v>
+        <v>2772.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4532.0</v>
+        <v>4539.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3344,7 +3344,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3304.0</v>
+        <v>3315.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>8979.0</v>
+        <v>8986.0</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4776.0</v>
+        <v>4792.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1227.0</v>
+        <v>1238.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3482,7 +3482,7 @@
         <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>3046.0</v>
+        <v>3048.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2087,13 +2087,13 @@
         <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>96.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="75">
@@ -2690,7 +2690,7 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="F19" t="n">
         <v>15.0</v>
@@ -2759,7 +2759,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>8986.0</v>
+        <v>8992.0</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -3505,7 +3505,7 @@
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1284,7 +1284,7 @@
         <v>43.0</v>
       </c>
       <c r="G43" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H43" t="n">
         <v>29.0</v>
@@ -1515,7 +1515,7 @@
         <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>1318.0</v>
+        <v>1320.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
@@ -1645,7 +1645,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -2087,13 +2087,13 @@
         <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>101.0</v>
+        <v>107.0</v>
       </c>
     </row>
     <row r="75">
@@ -2759,7 +2759,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>153.0</v>
+        <v>154.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -2788,7 +2788,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>116.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="24">
@@ -2805,7 +2805,7 @@
         <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>113.0</v>
+        <v>115.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>3240.0</v>
+        <v>3242.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3275,7 +3275,7 @@
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>8759.0</v>
+        <v>8768.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2772.0</v>
+        <v>2774.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4539.0</v>
+        <v>4541.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1238.0</v>
+        <v>1240.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3436,7 +3436,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>407.0</v>
+        <v>409.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2759,7 +2759,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -2884,7 +2884,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>337.0</v>
+        <v>346.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3137,7 +3137,7 @@
         <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -891,7 +891,7 @@
         <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1697,10 +1697,10 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G59" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="H59" t="n">
         <v>46.0</v>
@@ -1853,7 +1853,7 @@
         <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>199.0</v>
+        <v>200.0</v>
       </c>
       <c r="G65" t="n">
         <v>3.0</v>
@@ -1879,7 +1879,7 @@
         <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>352.0</v>
+        <v>354.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -1957,7 +1957,7 @@
         <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>61.0</v>
+        <v>66.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -2644,13 +2644,13 @@
         <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>64.0</v>
+        <v>69.0</v>
       </c>
       <c r="F17" t="n">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="G17" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="18">
@@ -2719,7 +2719,7 @@
         <v>6.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21">
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>1061.0</v>
+        <v>1069.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>829.0</v>
+        <v>833.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2774.0</v>
+        <v>2777.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>8992.0</v>
+        <v>8999.0</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4792.0</v>
+        <v>4796.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1240.0</v>
+        <v>1241.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1255,7 +1255,7 @@
         <v>34</v>
       </c>
       <c r="F42" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1645,7 +1645,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1723,7 +1723,7 @@
         <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>94.0</v>
+        <v>96.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2716,7 +2716,7 @@
         <v>15.0</v>
       </c>
       <c r="F20" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G20" t="n">
         <v>1.0</v>
@@ -2739,7 +2739,7 @@
         <v>1.0</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -3022,7 +3022,7 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>990.0</v>
+        <v>996.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>833.0</v>
+        <v>835.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4541.0</v>
+        <v>4542.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3344,7 +3344,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3315.0</v>
+        <v>3316.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>8999.0</v>
+        <v>9000.0</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4796.0</v>
+        <v>4800.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -995,10 +995,10 @@
         <v>35</v>
       </c>
       <c r="F32" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" t="n">
         <v>0.0</v>
@@ -2087,13 +2087,13 @@
         <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>107.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="75">
@@ -2644,7 +2644,7 @@
         <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="F17" t="n">
         <v>18.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>835.0</v>
+        <v>846.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3275,7 +3275,7 @@
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>8768.0</v>
+        <v>8771.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2777.0</v>
+        <v>2781.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4542.0</v>
+        <v>4544.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4800.0</v>
+        <v>4802.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1241.0</v>
+        <v>1242.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3436,7 +3436,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>409.0</v>
+        <v>410.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -3482,7 +3482,7 @@
         <v>33</v>
       </c>
       <c r="E29" t="n">
-        <v>3048.0</v>
+        <v>3050.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1515,13 +1515,13 @@
         <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>1320.0</v>
+        <v>1322.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>669.0</v>
+        <v>670.0</v>
       </c>
     </row>
     <row r="53">
@@ -1567,7 +1567,7 @@
         <v>36</v>
       </c>
       <c r="F54" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G54" t="n">
         <v>8.0</v>
@@ -1671,7 +1671,7 @@
         <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G58" t="n">
         <v>4.0</v>
@@ -2736,10 +2736,10 @@
         <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G21" t="n">
         <v>0.0</v>
@@ -2788,7 +2788,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>118.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="24">
@@ -2805,7 +2805,7 @@
         <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>115.0</v>
+        <v>119.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3045,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>1069.0</v>
+        <v>1074.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3275,7 +3275,7 @@
         <v>30</v>
       </c>
       <c r="E20" t="n">
-        <v>8771.0</v>
+        <v>8773.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>2781.0</v>
+        <v>2784.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3321,7 +3321,7 @@
         <v>21</v>
       </c>
       <c r="E22" t="n">
-        <v>4544.0</v>
+        <v>4545.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3367,7 +3367,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>9000.0</v>
+        <v>9011.0</v>
       </c>
       <c r="F24" t="n">
         <v>3.0</v>
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4802.0</v>
+        <v>4803.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1242.0</v>
+        <v>1244.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1307,7 +1307,7 @@
         <v>36</v>
       </c>
       <c r="F44" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1677,7 +1677,7 @@
         <v>4.0</v>
       </c>
       <c r="H58" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="59">
@@ -2483,10 +2483,10 @@
         <v>17</v>
       </c>
       <c r="E10" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="F10" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G10" t="n">
         <v>1.0</v>
@@ -2509,7 +2509,7 @@
         <v>118.0</v>
       </c>
       <c r="F11" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="G11" t="n">
         <v>223.0</v>
@@ -2532,7 +2532,7 @@
         <v>37.0</v>
       </c>
       <c r="F12" t="n">
-        <v>37.0</v>
+        <v>39.0</v>
       </c>
       <c r="G12" t="n">
         <v>15.0</v>
@@ -2578,7 +2578,7 @@
         <v>13.0</v>
       </c>
       <c r="F14" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -2759,7 +2759,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>156.0</v>
+        <v>159.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3068,7 +3068,7 @@
         <v>25</v>
       </c>
       <c r="E11" t="n">
-        <v>846.0</v>
+        <v>847.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3091,7 +3091,7 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>3242.0</v>
+        <v>3246.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3327,7 +3327,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="23">
@@ -3390,7 +3390,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>4803.0</v>
+        <v>4806.0</v>
       </c>
       <c r="F25" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="37">
   <si>
     <t>Area</t>
   </si>
@@ -1099,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="F36" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -2087,13 +2087,13 @@
         <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>48.0</v>
+        <v>50.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="75">
@@ -2474,22 +2474,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>19.0</v>
+        <v>1.0</v>
       </c>
       <c r="F10" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -2503,16 +2503,16 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>118.0</v>
+        <v>19.0</v>
       </c>
       <c r="F11" t="n">
-        <v>68.0</v>
+        <v>11.0</v>
       </c>
       <c r="G11" t="n">
-        <v>223.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="12">
@@ -2526,16 +2526,16 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>37.0</v>
+        <v>118.0</v>
       </c>
       <c r="F12" t="n">
-        <v>39.0</v>
+        <v>68.0</v>
       </c>
       <c r="G12" t="n">
-        <v>15.0</v>
+        <v>223.0</v>
       </c>
     </row>
     <row r="13">
@@ -2549,16 +2549,16 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0</v>
+        <v>39.0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="14">
@@ -2572,16 +2572,16 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15">
@@ -2592,19 +2592,19 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E15" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G15" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -2618,16 +2618,16 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>17.0</v>
+        <v>14.0</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="17">
@@ -2641,16 +2641,16 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>70.0</v>
+        <v>17.0</v>
       </c>
       <c r="F17" t="n">
-        <v>18.0</v>
+        <v>6.0</v>
       </c>
       <c r="G17" t="n">
-        <v>69.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -2661,19 +2661,19 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>19.0</v>
+        <v>70.0</v>
       </c>
       <c r="F18" t="n">
-        <v>7.0</v>
+        <v>18.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="19">
@@ -2684,19 +2684,19 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>60.0</v>
+        <v>19.0</v>
       </c>
       <c r="F19" t="n">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
       <c r="G19" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -2710,16 +2710,16 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="F20" t="n">
         <v>15.0</v>
       </c>
-      <c r="F20" t="n">
-        <v>7.0</v>
-      </c>
       <c r="G20" t="n">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="21">
@@ -2733,16 +2733,16 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
       <c r="F21" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="22">
@@ -2753,19 +2753,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" t="n">
-        <v>159.0</v>
+        <v>3.0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G22" t="n">
-        <v>43.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -2779,16 +2779,16 @@
         <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0</v>
+        <v>159.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>124.0</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="24">
@@ -2802,15 +2802,38 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>124.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
         <v>33</v>
       </c>
-      <c r="E24" t="n">
-        <v>119.0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="E25" t="n">
+        <v>123.0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G25" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3114,7 +3137,7 @@
         <v>27</v>
       </c>
       <c r="E13" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="38">
   <si>
     <t>Area</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>II</t>
+  </si>
+  <si>
+    <t>III</t>
   </si>
   <si>
     <t>Emilia romagna</t>
@@ -206,13 +209,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>5.0</v>
@@ -232,13 +235,13 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
         <v>1.0</v>
@@ -258,13 +261,13 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -284,13 +287,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
         <v>9.0</v>
@@ -310,13 +313,13 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="n">
         <v>7.0</v>
@@ -336,13 +339,13 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n">
         <v>7.0</v>
@@ -362,13 +365,13 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="n">
         <v>7.0</v>
@@ -388,13 +391,13 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
         <v>8.0</v>
@@ -414,13 +417,13 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
         <v>43.0</v>
@@ -440,13 +443,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
         <v>10.0</v>
@@ -466,13 +469,13 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" t="n">
         <v>9.0</v>
@@ -492,16 +495,16 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -518,13 +521,13 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
         <v>6.0</v>
@@ -544,13 +547,13 @@
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
         <v>24.0</v>
@@ -570,13 +573,13 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F16" t="n">
         <v>70.0</v>
@@ -596,13 +599,13 @@
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F17" t="n">
         <v>21.0</v>
@@ -622,13 +625,13 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18" t="n">
         <v>26.0</v>
@@ -648,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
         <v>15.0</v>
@@ -674,13 +677,13 @@
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>1.0</v>
@@ -700,13 +703,13 @@
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F21" t="n">
         <v>1.0</v>
@@ -726,13 +729,13 @@
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F22" t="n">
         <v>15.0</v>
@@ -752,13 +755,13 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F23" t="n">
         <v>45.0</v>
@@ -778,13 +781,13 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
         <v>50.0</v>
@@ -804,13 +807,13 @@
         <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
         <v>13.0</v>
@@ -830,13 +833,13 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
         <v>23.0</v>
@@ -856,13 +859,13 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F27" t="n">
         <v>40.0</v>
@@ -882,13 +885,13 @@
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F28" t="n">
         <v>21.0</v>
@@ -908,13 +911,13 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F29" t="n">
         <v>40.0</v>
@@ -934,13 +937,13 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
         <v>52.0</v>
@@ -960,13 +963,13 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F31" t="n">
         <v>19.0</v>
@@ -986,13 +989,13 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" t="n">
         <v>23.0</v>
@@ -1012,13 +1015,13 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F33" t="n">
         <v>29.0</v>
@@ -1038,13 +1041,13 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F34" t="n">
         <v>6.0</v>
@@ -1064,13 +1067,13 @@
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F35" t="n">
         <v>13.0</v>
@@ -1090,13 +1093,13 @@
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F36" t="n">
         <v>26.0</v>
@@ -1116,13 +1119,13 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F37" t="n">
         <v>2.0</v>
@@ -1142,13 +1145,13 @@
         <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" t="n">
         <v>1.0</v>
@@ -1168,13 +1171,13 @@
         <v>10</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F39" t="n">
         <v>5.0</v>
@@ -1194,13 +1197,13 @@
         <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F40" t="n">
         <v>9.0</v>
@@ -1220,13 +1223,13 @@
         <v>10</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F41" t="n">
         <v>5.0</v>
@@ -1246,13 +1249,13 @@
         <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F42" t="n">
         <v>51.0</v>
@@ -1272,13 +1275,13 @@
         <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F43" t="n">
         <v>43.0</v>
@@ -1298,13 +1301,13 @@
         <v>10</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F44" t="n">
         <v>91.0</v>
@@ -1324,13 +1327,13 @@
         <v>10</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F45" t="n">
         <v>31.0</v>
@@ -1350,13 +1353,13 @@
         <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F46" t="n">
         <v>41.0</v>
@@ -1376,16 +1379,16 @@
         <v>10</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F47" t="n">
-        <v>80.0</v>
+        <v>82.0</v>
       </c>
       <c r="G47" t="n">
         <v>0.0</v>
@@ -1402,13 +1405,13 @@
         <v>10</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
@@ -1428,13 +1431,13 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F49" t="n">
         <v>4.0</v>
@@ -1454,13 +1457,13 @@
         <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F50" t="n">
         <v>13.0</v>
@@ -1480,13 +1483,13 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F51" t="n">
         <v>16.0</v>
@@ -1506,16 +1509,16 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1322.0</v>
+        <v>1324.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
@@ -1532,13 +1535,13 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53" t="n">
         <v>228.0</v>
@@ -1558,13 +1561,13 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F54" t="n">
         <v>250.0</v>
@@ -1584,13 +1587,13 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F55" t="n">
         <v>70.0</v>
@@ -1610,16 +1613,16 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -1636,16 +1639,16 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1662,22 +1665,22 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>126.0</v>
+        <v>125.0</v>
       </c>
       <c r="G58" t="n">
         <v>4.0</v>
       </c>
       <c r="H58" t="n">
-        <v>102.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="59">
@@ -1688,13 +1691,13 @@
         <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
         <v>172.0</v>
@@ -1714,13 +1717,13 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F60" t="n">
         <v>96.0</v>
@@ -1740,13 +1743,13 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F61" t="n">
         <v>42.0</v>
@@ -1766,13 +1769,13 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
         <v>78.0</v>
@@ -1792,13 +1795,13 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F63" t="n">
         <v>128.0</v>
@@ -1818,22 +1821,22 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>164.0</v>
+        <v>140.0</v>
       </c>
       <c r="G64" t="n">
         <v>0.0</v>
       </c>
       <c r="H64" t="n">
-        <v>305.0</v>
+        <v>244.0</v>
       </c>
     </row>
     <row r="65">
@@ -1844,22 +1847,22 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>200.0</v>
+        <v>169.0</v>
       </c>
       <c r="G65" t="n">
         <v>3.0</v>
       </c>
       <c r="H65" t="n">
-        <v>142.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="66">
@@ -1870,22 +1873,22 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>354.0</v>
+        <v>308.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
       </c>
       <c r="H66" t="n">
-        <v>19.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="67">
@@ -1896,16 +1899,16 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F67" t="n">
-        <v>124.0</v>
+        <v>120.0</v>
       </c>
       <c r="G67" t="n">
         <v>0.0</v>
@@ -1922,19 +1925,19 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>80.0</v>
+        <v>62.0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
         <v>6.0</v>
@@ -1948,16 +1951,16 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F69" t="n">
-        <v>66.0</v>
+        <v>56.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -1974,16 +1977,16 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F70" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2000,19 +2003,19 @@
         <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>31.0</v>
+        <v>11.0</v>
       </c>
       <c r="G71" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2026,16 +2029,16 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F72" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
@@ -2052,13 +2055,13 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
         <v>43.0</v>
@@ -2078,13 +2081,13 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
         <v>50.0</v>
@@ -2104,13 +2107,13 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F75" t="n">
         <v>24.0</v>
@@ -2130,13 +2133,13 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F76" t="n">
         <v>0.0</v>
@@ -2156,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
         <v>0.0</v>
@@ -2182,13 +2185,13 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F78" t="n">
         <v>24.0</v>
@@ -2208,13 +2211,13 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F79" t="n">
         <v>133.0</v>
@@ -2234,13 +2237,13 @@
         <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F80" t="n">
         <v>35.0</v>
@@ -2249,6 +2252,266 @@
         <v>0.0</v>
       </c>
       <c r="H80" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" t="s">
+        <v>35</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>8</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" t="s">
+        <v>35</v>
+      </c>
+      <c r="F82" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>61.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" t="s">
+        <v>36</v>
+      </c>
+      <c r="F83" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>18.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>8</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" t="s">
+        <v>37</v>
+      </c>
+      <c r="F84" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>8</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" t="s">
+        <v>26</v>
+      </c>
+      <c r="E85" t="s">
+        <v>35</v>
+      </c>
+      <c r="F85" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>8</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" t="s">
+        <v>36</v>
+      </c>
+      <c r="F86" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>8</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" t="s">
+        <v>26</v>
+      </c>
+      <c r="E87" t="s">
+        <v>37</v>
+      </c>
+      <c r="F87" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" t="s">
+        <v>27</v>
+      </c>
+      <c r="E88" t="s">
+        <v>35</v>
+      </c>
+      <c r="F88" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" t="s">
+        <v>36</v>
+      </c>
+      <c r="F89" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>27</v>
+      </c>
+      <c r="E90" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H90" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2293,10 +2556,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>4.0</v>
@@ -2316,19 +2579,19 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -2339,10 +2602,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
         <v>10.0</v>
@@ -2362,10 +2625,10 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
         <v>0.0</v>
@@ -2385,10 +2648,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>2.0</v>
@@ -2408,10 +2671,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
         <v>6.0</v>
@@ -2431,10 +2694,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
         <v>4.0</v>
@@ -2454,10 +2717,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
         <v>7.0</v>
@@ -2477,10 +2740,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
         <v>1.0</v>
@@ -2500,10 +2763,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
         <v>19.0</v>
@@ -2523,10 +2786,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E12" t="n">
         <v>118.0</v>
@@ -2535,7 +2798,7 @@
         <v>68.0</v>
       </c>
       <c r="G12" t="n">
-        <v>223.0</v>
+        <v>224.0</v>
       </c>
     </row>
     <row r="13">
@@ -2546,19 +2809,19 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="F13" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G13" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="14">
@@ -2569,10 +2832,10 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
         <v>0.0</v>
@@ -2592,10 +2855,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
         <v>13.0</v>
@@ -2615,10 +2878,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
         <v>14.0</v>
@@ -2638,10 +2901,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
         <v>17.0</v>
@@ -2661,13 +2924,13 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>70.0</v>
+        <v>69.0</v>
       </c>
       <c r="F18" t="n">
         <v>18.0</v>
@@ -2684,10 +2947,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E19" t="n">
         <v>19.0</v>
@@ -2707,19 +2970,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>60.0</v>
+        <v>43.0</v>
       </c>
       <c r="F20" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="G20" t="n">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="21">
@@ -2730,19 +2993,19 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" t="n">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="F21" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -2753,16 +3016,16 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
         <v>3.0</v>
       </c>
       <c r="F22" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -2776,10 +3039,10 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
         <v>159.0</v>
@@ -2799,10 +3062,10 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
         <v>0.0</v>
@@ -2822,10 +3085,10 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
         <v>123.0</v>
@@ -2834,6 +3097,98 @@
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G29" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2878,10 +3233,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
         <v>39.0</v>
@@ -2901,10 +3256,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
         <v>346.0</v>
@@ -2924,10 +3279,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>666.0</v>
@@ -2947,13 +3302,13 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>242.0</v>
+        <v>238.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -2970,10 +3325,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
         <v>566.0</v>
@@ -2993,10 +3348,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
         <v>2109.0</v>
@@ -3016,10 +3371,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
         <v>23.0</v>
@@ -3039,10 +3394,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
         <v>996.0</v>
@@ -3062,13 +3417,13 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1074.0</v>
+        <v>1078.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3085,13 +3440,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>847.0</v>
+        <v>850.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3108,13 +3463,13 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3246.0</v>
+        <v>3247.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3131,10 +3486,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
         <v>274.0</v>
@@ -3154,10 +3509,10 @@
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>127.0</v>
@@ -3177,10 +3532,10 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
         <v>261.0</v>
@@ -3200,10 +3555,10 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
         <v>2692.0</v>
@@ -3223,13 +3578,13 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1500.0</v>
+        <v>1504.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3246,10 +3601,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E18" t="n">
         <v>0.0</v>
@@ -3269,10 +3624,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
         <v>522.0</v>
@@ -3292,13 +3647,13 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8773.0</v>
+        <v>8777.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3315,10 +3670,10 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
         <v>2784.0</v>
@@ -3338,13 +3693,13 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4545.0</v>
+        <v>4531.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3361,10 +3716,10 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" t="n">
         <v>3316.0</v>
@@ -3384,19 +3739,19 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>9011.0</v>
+        <v>6788.0</v>
       </c>
       <c r="F24" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="n">
-        <v>220.0</v>
+        <v>171.0</v>
       </c>
     </row>
     <row r="25">
@@ -3407,19 +3762,19 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>4806.0</v>
+        <v>3125.0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="26">
@@ -3430,13 +3785,13 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>1244.0</v>
+        <v>667.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3453,10 +3808,10 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E27" t="n">
         <v>410.0</v>
@@ -3476,10 +3831,10 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
         <v>0.0</v>
@@ -3499,10 +3854,10 @@
         <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
         <v>3050.0</v>
@@ -3522,10 +3877,10 @@
         <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E30" t="n">
         <v>20.0</v>
@@ -3534,6 +3889,98 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2229.0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1681.0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" t="n">
+        <v>579.0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G34" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1339,7 +1339,7 @@
         <v>31.0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H45" t="n">
         <v>143.0</v>
@@ -1518,13 +1518,13 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1324.0</v>
+        <v>1327.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>670.0</v>
+        <v>671.0</v>
       </c>
     </row>
     <row r="53">
@@ -1544,7 +1544,7 @@
         <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
       <c r="G53" t="n">
         <v>25.0</v>
@@ -1576,7 +1576,7 @@
         <v>8.0</v>
       </c>
       <c r="H54" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="55">
@@ -2588,7 +2588,7 @@
         <v>2.0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -2792,7 +2792,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>118.0</v>
+        <v>121.0</v>
       </c>
       <c r="F12" t="n">
         <v>68.0</v>
@@ -2818,7 +2818,7 @@
         <v>38.0</v>
       </c>
       <c r="F13" t="n">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="G13" t="n">
         <v>16.0</v>
@@ -2930,7 +2930,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="F18" t="n">
         <v>18.0</v>
@@ -3262,7 +3262,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>346.0</v>
+        <v>347.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>666.0</v>
+        <v>677.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3308,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>238.0</v>
+        <v>244.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>566.0</v>
+        <v>567.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3377,7 +3377,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>996.0</v>
+        <v>1003.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>850.0</v>
+        <v>851.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3538,7 +3538,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>261.0</v>
+        <v>263.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3561,7 +3561,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>2692.0</v>
+        <v>2704.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1504.0</v>
+        <v>1509.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3630,7 +3630,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>522.0</v>
+        <v>523.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8777.0</v>
+        <v>8781.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2784.0</v>
+        <v>2786.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3316.0</v>
+        <v>3320.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3125.0</v>
+        <v>3130.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1102,7 +1102,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1524,7 +1524,7 @@
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>671.0</v>
+        <v>672.0</v>
       </c>
     </row>
     <row r="53">
@@ -2792,13 +2792,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>121.0</v>
+        <v>124.0</v>
       </c>
       <c r="F12" t="n">
         <v>68.0</v>
       </c>
       <c r="G12" t="n">
-        <v>224.0</v>
+        <v>228.0</v>
       </c>
     </row>
     <row r="13">
@@ -2933,7 +2933,7 @@
         <v>70.0</v>
       </c>
       <c r="F18" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="G18" t="n">
         <v>69.0</v>
@@ -3045,13 +3045,13 @@
         <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>159.0</v>
+        <v>161.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="24">
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>851.0</v>
+        <v>859.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3247.0</v>
+        <v>3249.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>127.0</v>
+        <v>129.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8781.0</v>
+        <v>8785.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2786.0</v>
+        <v>2788.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6788.0</v>
+        <v>6789.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3130.0</v>
+        <v>3131.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>667.0</v>
+        <v>671.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3952,7 +3952,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>1681.0</v>
+        <v>1686.0</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
@@ -3975,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>579.0</v>
+        <v>580.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -1674,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G58" t="n">
         <v>4.0</v>
@@ -1726,7 +1726,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -1882,7 +1882,7 @@
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>308.0</v>
+        <v>309.0</v>
       </c>
       <c r="G66" t="n">
         <v>0.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1078.0</v>
+        <v>1080.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>129.0</v>
+        <v>133.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8785.0</v>
+        <v>8787.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2788.0</v>
+        <v>2789.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6789.0</v>
+        <v>6790.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3131.0</v>
+        <v>3133.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3952,7 +3952,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>1686.0</v>
+        <v>1687.0</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2070,7 +2070,7 @@
         <v>1.0</v>
       </c>
       <c r="H73" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
     </row>
     <row r="74">
@@ -2096,7 +2096,7 @@
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="75">
@@ -2798,7 +2798,7 @@
         <v>68.0</v>
       </c>
       <c r="G12" t="n">
-        <v>228.0</v>
+        <v>230.0</v>
       </c>
     </row>
     <row r="13">
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>49.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="24">
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>124.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>123.0</v>
+        <v>127.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1258,7 +1258,7 @@
         <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1310,7 +1310,7 @@
         <v>37</v>
       </c>
       <c r="F44" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1524,7 +1524,7 @@
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>672.0</v>
+        <v>673.0</v>
       </c>
     </row>
     <row r="53">
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1700,7 +1700,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G59" t="n">
         <v>12.0</v>
@@ -2723,10 +2723,10 @@
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -2792,7 +2792,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>124.0</v>
+        <v>126.0</v>
       </c>
       <c r="F12" t="n">
         <v>68.0</v>
@@ -2815,7 +2815,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="F13" t="n">
         <v>43.0</v>
@@ -3308,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1080.0</v>
+        <v>1083.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3249.0</v>
+        <v>3251.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1509.0</v>
+        <v>1513.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3630,7 +3630,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>523.0</v>
+        <v>525.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8787.0</v>
+        <v>8789.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2789.0</v>
+        <v>2795.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4531.0</v>
+        <v>4536.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3133.0</v>
+        <v>3140.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>671.0</v>
+        <v>672.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3975,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>580.0</v>
+        <v>582.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -764,7 +764,7 @@
         <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="G23" t="n">
         <v>1.0</v>
@@ -1264,7 +1264,7 @@
         <v>4.0</v>
       </c>
       <c r="H42" t="n">
-        <v>65.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="43">
@@ -1420,7 +1420,7 @@
         <v>0.0</v>
       </c>
       <c r="H48" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="49">
@@ -2798,7 +2798,7 @@
         <v>68.0</v>
       </c>
       <c r="G12" t="n">
-        <v>230.0</v>
+        <v>232.0</v>
       </c>
     </row>
     <row r="13">
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1003.0</v>
+        <v>1007.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1083.0</v>
+        <v>1084.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>859.0</v>
+        <v>862.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8789.0</v>
+        <v>8794.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6790.0</v>
+        <v>6796.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3140.0</v>
+        <v>3142.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -426,7 +426,7 @@
         <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>43.0</v>
+        <v>45.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -1258,7 +1258,7 @@
         <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G42" t="n">
         <v>4.0</v>
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -1934,7 +1934,7 @@
         <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G68" t="n">
         <v>0.0</v>
@@ -2070,7 +2070,7 @@
         <v>1.0</v>
       </c>
       <c r="H73" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="74">
@@ -2772,7 +2772,7 @@
         <v>19.0</v>
       </c>
       <c r="F11" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -2792,7 +2792,7 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
       <c r="F12" t="n">
         <v>68.0</v>
@@ -2861,7 +2861,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F15" t="n">
         <v>6.0</v>
@@ -3262,7 +3262,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>347.0</v>
+        <v>348.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>677.0</v>
+        <v>681.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1084.0</v>
+        <v>1089.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3251.0</v>
+        <v>3260.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3492,7 +3492,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3561,7 +3561,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>2704.0</v>
+        <v>2714.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2795.0</v>
+        <v>2803.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6796.0</v>
+        <v>6798.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3860,7 +3860,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>3050.0</v>
+        <v>3053.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1518,7 +1518,7 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1327.0</v>
+        <v>1330.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
@@ -1674,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>126.0</v>
+        <v>129.0</v>
       </c>
       <c r="G58" t="n">
         <v>4.0</v>
@@ -2930,13 +2930,13 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="F18" t="n">
         <v>19.0</v>
       </c>
       <c r="G18" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
     </row>
     <row r="19">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>127.0</v>
+        <v>134.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3163,7 +3163,7 @@
         <v>1.0</v>
       </c>
       <c r="F28" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -3354,7 +3354,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>2109.0</v>
+        <v>2114.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3260.0</v>
+        <v>3261.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8794.0</v>
+        <v>8800.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4536.0</v>
+        <v>4554.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6798.0</v>
+        <v>6800.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1680,7 +1680,7 @@
         <v>4.0</v>
       </c>
       <c r="H58" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="59">
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>60.0</v>
+        <v>64.0</v>
       </c>
     </row>
     <row r="24">
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>567.0</v>
+        <v>569.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1089.0</v>
+        <v>1092.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3261.0</v>
+        <v>3262.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3630,7 +3630,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>525.0</v>
+        <v>528.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6800.0</v>
+        <v>6803.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>672.0</v>
+        <v>673.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1524,7 +1524,7 @@
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>673.0</v>
+        <v>675.0</v>
       </c>
     </row>
     <row r="53">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -764,7 +764,7 @@
         <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G23" t="n">
         <v>1.0</v>
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1680,7 +1680,7 @@
         <v>4.0</v>
       </c>
       <c r="H58" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="59">
@@ -2792,13 +2792,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="F12" t="n">
         <v>68.0</v>
       </c>
       <c r="G12" t="n">
-        <v>232.0</v>
+        <v>233.0</v>
       </c>
     </row>
     <row r="13">
@@ -2936,7 +2936,7 @@
         <v>19.0</v>
       </c>
       <c r="G18" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="19">
@@ -3025,7 +3025,7 @@
         <v>3.0</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>681.0</v>
+        <v>682.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3308,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>245.0</v>
+        <v>247.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1007.0</v>
+        <v>1009.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1092.0</v>
+        <v>1095.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>862.0</v>
+        <v>867.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3538,7 +3538,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>263.0</v>
+        <v>267.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1513.0</v>
+        <v>1514.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8800.0</v>
+        <v>8804.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2803.0</v>
+        <v>2809.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3320.0</v>
+        <v>3322.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3952,7 +3952,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>1687.0</v>
+        <v>1690.0</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
@@ -3975,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>582.0</v>
+        <v>583.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2772,7 +2772,7 @@
         <v>19.0</v>
       </c>
       <c r="F11" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -2844,7 +2844,7 @@
         <v>0.0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
@@ -2930,13 +2930,13 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="F18" t="n">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="G18" t="n">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="19">
@@ -2976,7 +2976,7 @@
         <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="F20" t="n">
         <v>4.0</v>
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>64.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="24">
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1095.0</v>
+        <v>1097.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>867.0</v>
+        <v>874.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3492,7 +3492,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>275.0</v>
+        <v>278.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4554.0</v>
+        <v>4556.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6803.0</v>
+        <v>6806.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3814,7 +3814,7 @@
         <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>410.0</v>
+        <v>416.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1518,13 +1518,13 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1330.0</v>
+        <v>1335.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>675.0</v>
+        <v>676.0</v>
       </c>
     </row>
     <row r="53">
@@ -1576,7 +1576,7 @@
         <v>8.0</v>
       </c>
       <c r="H54" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="55">
@@ -1726,7 +1726,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
       <c r="G60" t="n">
         <v>0.0</v>
@@ -2480,7 +2480,7 @@
         <v>36</v>
       </c>
       <c r="F89" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G89" t="n">
         <v>2.0</v>
@@ -2795,7 +2795,7 @@
         <v>129.0</v>
       </c>
       <c r="F12" t="n">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="G12" t="n">
         <v>233.0</v>
@@ -2930,7 +2930,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="F18" t="n">
         <v>22.0</v>
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>129.0</v>
+        <v>133.0</v>
       </c>
     </row>
     <row r="25">
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>682.0</v>
+        <v>683.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3449,7 +3449,7 @@
         <v>874.0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8804.0</v>
+        <v>8818.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2809.0</v>
+        <v>2823.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3142.0</v>
+        <v>3144.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3843,7 +3843,7 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="29">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1524,7 +1524,7 @@
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>676.0</v>
+        <v>680.0</v>
       </c>
     </row>
     <row r="53">
@@ -2890,7 +2890,7 @@
         <v>4.0</v>
       </c>
       <c r="G16" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="17">
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>75.0</v>
+        <v>78.0</v>
       </c>
     </row>
     <row r="24">
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1097.0</v>
+        <v>1098.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>874.0</v>
+        <v>875.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3653,13 +3653,13 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8818.0</v>
+        <v>8819.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
       </c>
       <c r="G20" t="n">
-        <v>183.0</v>
+        <v>184.0</v>
       </c>
     </row>
     <row r="21">
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6806.0</v>
+        <v>6813.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2798,7 +2798,7 @@
         <v>69.0</v>
       </c>
       <c r="G12" t="n">
-        <v>233.0</v>
+        <v>235.0</v>
       </c>
     </row>
     <row r="13">
@@ -2936,7 +2936,7 @@
         <v>22.0</v>
       </c>
       <c r="G18" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="19">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
       <c r="G57" t="n">
         <v>4.0</v>
@@ -1706,7 +1706,7 @@
         <v>12.0</v>
       </c>
       <c r="H59" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="60">
@@ -2930,13 +2930,13 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>73.0</v>
+        <v>76.0</v>
       </c>
       <c r="F18" t="n">
         <v>22.0</v>
       </c>
       <c r="G18" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
     </row>
     <row r="19">
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>673.0</v>
+        <v>674.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3975,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>583.0</v>
+        <v>584.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1102,7 +1102,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>125.0</v>
+        <v>126.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -2064,13 +2064,13 @@
         <v>35</v>
       </c>
       <c r="F73" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G73" t="n">
         <v>1.0</v>
       </c>
       <c r="H73" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="74">
@@ -2798,7 +2798,7 @@
         <v>69.0</v>
       </c>
       <c r="G12" t="n">
-        <v>235.0</v>
+        <v>236.0</v>
       </c>
     </row>
     <row r="13">
@@ -2976,7 +2976,7 @@
         <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="F20" t="n">
         <v>4.0</v>
@@ -3045,13 +3045,13 @@
         <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>78.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="24">
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1009.0</v>
+        <v>1018.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3492,7 +3492,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>278.0</v>
+        <v>280.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2823.0</v>
+        <v>2824.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3322.0</v>
+        <v>3327.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1518,13 +1518,13 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1335.0</v>
+        <v>1338.0</v>
       </c>
       <c r="G52" t="n">
         <v>91.0</v>
       </c>
       <c r="H52" t="n">
-        <v>680.0</v>
+        <v>681.0</v>
       </c>
     </row>
     <row r="53">
@@ -1570,7 +1570,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>250.0</v>
+        <v>252.0</v>
       </c>
       <c r="G54" t="n">
         <v>8.0</v>
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>126.0</v>
+        <v>128.0</v>
       </c>
       <c r="G56" t="n">
         <v>10.0</v>
@@ -2090,13 +2090,13 @@
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="75">
@@ -2246,7 +2246,7 @@
         <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -2861,7 +2861,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="F15" t="n">
         <v>6.0</v>
@@ -2930,7 +2930,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="F18" t="n">
         <v>22.0</v>
@@ -3022,10 +3022,10 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F22" t="n">
         <v>3.0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>4.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="24">
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>133.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>135.0</v>
+        <v>140.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>683.0</v>
+        <v>687.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3308,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>247.0</v>
+        <v>257.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>875.0</v>
+        <v>876.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3262.0</v>
+        <v>3264.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3561,7 +3561,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>2714.0</v>
+        <v>2721.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1514.0</v>
+        <v>1516.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8819.0</v>
+        <v>8823.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2824.0</v>
+        <v>2825.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3144.0</v>
+        <v>3146.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>674.0</v>
+        <v>678.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -34,10 +34,10 @@
     <t>Negativo</t>
   </si>
   <si>
-    <t>Non idoneo</t>
+    <t>Positivo</t>
   </si>
   <si>
-    <t>Positivo</t>
+    <t>Non idoneo</t>
   </si>
   <si>
     <t>Pl</t>
@@ -374,7 +374,7 @@
         <v>35</v>
       </c>
       <c r="F8" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -400,10 +400,10 @@
         <v>36</v>
       </c>
       <c r="F9" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H9" t="n">
         <v>0.0</v>
@@ -426,7 +426,7 @@
         <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>45.0</v>
+        <v>26.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -481,10 +481,10 @@
         <v>9.0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -530,7 +530,7 @@
         <v>35</v>
       </c>
       <c r="F14" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -556,7 +556,7 @@
         <v>36</v>
       </c>
       <c r="F15" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -582,7 +582,7 @@
         <v>37</v>
       </c>
       <c r="F16" t="n">
-        <v>70.0</v>
+        <v>79.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>21.0</v>
+        <v>17.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -634,13 +634,13 @@
         <v>36</v>
       </c>
       <c r="F18" t="n">
-        <v>26.0</v>
+        <v>15.0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="19">
@@ -660,7 +660,7 @@
         <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" t="n">
         <v>0.0</v>
@@ -741,10 +741,10 @@
         <v>15.0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -793,10 +793,10 @@
         <v>50.0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -998,13 +998,13 @@
         <v>36</v>
       </c>
       <c r="F32" t="n">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
       <c r="G32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H32" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -1024,10 +1024,10 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>29.0</v>
+        <v>39.0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H33" t="n">
         <v>0.0</v>
@@ -1183,10 +1183,10 @@
         <v>5.0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -1258,13 +1258,13 @@
         <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>53.0</v>
+        <v>55.0</v>
       </c>
       <c r="G42" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="H42" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>67.0</v>
       </c>
     </row>
     <row r="43">
@@ -1284,13 +1284,13 @@
         <v>36</v>
       </c>
       <c r="F43" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G43" t="n">
-        <v>3.0</v>
+        <v>29.0</v>
       </c>
       <c r="H43" t="n">
-        <v>29.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="44">
@@ -1310,13 +1310,13 @@
         <v>37</v>
       </c>
       <c r="F44" t="n">
-        <v>92.0</v>
+        <v>111.0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H44" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -1339,10 +1339,10 @@
         <v>31.0</v>
       </c>
       <c r="G45" t="n">
+        <v>143.0</v>
+      </c>
+      <c r="H45" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>143.0</v>
       </c>
     </row>
     <row r="46">
@@ -1365,10 +1365,10 @@
         <v>41.0</v>
       </c>
       <c r="G46" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="H46" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>27.0</v>
       </c>
     </row>
     <row r="47">
@@ -1391,10 +1391,10 @@
         <v>82.0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H47" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
@@ -1417,10 +1417,10 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H48" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -1521,10 +1521,10 @@
         <v>1338.0</v>
       </c>
       <c r="G52" t="n">
+        <v>681.0</v>
+      </c>
+      <c r="H52" t="n">
         <v>91.0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>681.0</v>
       </c>
     </row>
     <row r="53">
@@ -1544,13 +1544,13 @@
         <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>230.0</v>
+        <v>231.0</v>
       </c>
       <c r="G53" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="H53" t="n">
         <v>25.0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>65.0</v>
       </c>
     </row>
     <row r="54">
@@ -1573,10 +1573,10 @@
         <v>252.0</v>
       </c>
       <c r="G54" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H54" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>16.0</v>
       </c>
     </row>
     <row r="55">
@@ -1596,13 +1596,13 @@
         <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="G55" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H55" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="56">
@@ -1625,10 +1625,10 @@
         <v>128.0</v>
       </c>
       <c r="G56" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="H56" t="n">
         <v>10.0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>28.0</v>
       </c>
     </row>
     <row r="57">
@@ -1651,10 +1651,10 @@
         <v>138.0</v>
       </c>
       <c r="G57" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H57" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="58">
@@ -1674,13 +1674,13 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>129.0</v>
+        <v>135.0</v>
       </c>
       <c r="G58" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="H58" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>92.0</v>
       </c>
     </row>
     <row r="59">
@@ -1700,13 +1700,13 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>173.0</v>
+        <v>185.0</v>
       </c>
       <c r="G59" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="H59" t="n">
         <v>12.0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>47.0</v>
       </c>
     </row>
     <row r="60">
@@ -1726,13 +1726,13 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>98.0</v>
+        <v>108.0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H60" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1755,10 +1755,10 @@
         <v>42.0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0</v>
+        <v>97.0</v>
       </c>
       <c r="H61" t="n">
-        <v>97.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1781,10 +1781,10 @@
         <v>78.0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="H62" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1807,10 +1807,10 @@
         <v>128.0</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H63" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1833,10 +1833,10 @@
         <v>140.0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0</v>
+        <v>244.0</v>
       </c>
       <c r="H64" t="n">
-        <v>244.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1859,10 +1859,10 @@
         <v>169.0</v>
       </c>
       <c r="G65" t="n">
+        <v>124.0</v>
+      </c>
+      <c r="H65" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>124.0</v>
       </c>
     </row>
     <row r="66">
@@ -1885,10 +1885,10 @@
         <v>309.0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H66" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1911,10 +1911,10 @@
         <v>120.0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H67" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1937,10 +1937,10 @@
         <v>63.0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H68" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1986,7 +1986,7 @@
         <v>35</v>
       </c>
       <c r="F70" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2012,13 +2012,13 @@
         <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>11.0</v>
+        <v>25.0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="72">
@@ -2038,13 +2038,13 @@
         <v>37</v>
       </c>
       <c r="F72" t="n">
-        <v>4.0</v>
+        <v>22.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="73">
@@ -2067,10 +2067,10 @@
         <v>44.0</v>
       </c>
       <c r="G73" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="H73" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H73" t="n">
-        <v>112.0</v>
       </c>
     </row>
     <row r="74">
@@ -2093,10 +2093,10 @@
         <v>51.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>123.0</v>
       </c>
       <c r="H74" t="n">
-        <v>123.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -2145,10 +2145,10 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0</v>
+        <v>17.0</v>
       </c>
       <c r="H76" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2171,10 +2171,10 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0</v>
+        <v>29.0</v>
       </c>
       <c r="H77" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2223,10 +2223,10 @@
         <v>133.0</v>
       </c>
       <c r="G79" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H79" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2275,10 +2275,10 @@
         <v>1.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H81" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -2301,10 +2301,10 @@
         <v>24.0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="H82" t="n">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -2327,10 +2327,10 @@
         <v>31.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H83" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -2353,10 +2353,10 @@
         <v>46.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H84" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -2405,10 +2405,10 @@
         <v>19.0</v>
       </c>
       <c r="G86" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H86" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2483,10 +2483,10 @@
         <v>21.0</v>
       </c>
       <c r="G89" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H89" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2542,10 +2542,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -2562,10 +2562,10 @@
         <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -2608,10 +2608,10 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -2723,10 +2723,10 @@
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="F9" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -2792,10 +2792,10 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="F12" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G12" t="n">
         <v>236.0</v>
@@ -2913,7 +2913,7 @@
         <v>6.0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
@@ -2930,10 +2930,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>77.0</v>
+        <v>82.0</v>
       </c>
       <c r="F18" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G18" t="n">
         <v>75.0</v>
@@ -3022,10 +3022,10 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="F22" t="n">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>140.0</v>
+        <v>141.0</v>
       </c>
     </row>
     <row r="25">
@@ -3219,10 +3219,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
-      </c>
-      <c r="G1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>687.0</v>
+        <v>114.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>569.0</v>
+        <v>571.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3354,7 +3354,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>2114.0</v>
+        <v>2087.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>3264.0</v>
+        <v>1693.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3561,7 +3561,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>2721.0</v>
+        <v>3294.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8823.0</v>
+        <v>8825.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2825.0</v>
+        <v>2826.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4556.0</v>
+        <v>4967.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>678.0</v>
+        <v>2739.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1547,7 +1547,7 @@
         <v>231.0</v>
       </c>
       <c r="G53" t="n">
-        <v>65.0</v>
+        <v>70.0</v>
       </c>
       <c r="H53" t="n">
         <v>25.0</v>
@@ -2093,7 +2093,7 @@
         <v>51.0</v>
       </c>
       <c r="G74" t="n">
-        <v>123.0</v>
+        <v>130.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2405,7 +2405,7 @@
         <v>19.0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H86" t="n">
         <v>1.0</v>
@@ -2976,7 +2976,7 @@
         <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="F20" t="n">
         <v>4.0</v>
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="24">
@@ -3143,7 +3143,7 @@
         <v>11.0</v>
       </c>
       <c r="G27" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="28">
@@ -3423,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1098.0</v>
+        <v>1102.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6813.0</v>
+        <v>6814.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -3045,7 +3045,7 @@
         <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1518,10 +1518,10 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1338.0</v>
+        <v>1340.0</v>
       </c>
       <c r="G52" t="n">
-        <v>681.0</v>
+        <v>683.0</v>
       </c>
       <c r="H52" t="n">
         <v>91.0</v>
@@ -1570,7 +1570,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G54" t="n">
         <v>16.0</v>
@@ -1596,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="G56" t="n">
         <v>28.0</v>
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G57" t="n">
         <v>1.0</v>
@@ -1674,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>135.0</v>
+        <v>136.0</v>
       </c>
       <c r="G58" t="n">
         <v>92.0</v>
@@ -2064,10 +2064,10 @@
         <v>35</v>
       </c>
       <c r="F73" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="G73" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="H73" t="n">
         <v>1.0</v>
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>90.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="24">
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1018.0</v>
+        <v>1021.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3446,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>876.0</v>
+        <v>878.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3469,7 +3469,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>1693.0</v>
+        <v>1694.0</v>
       </c>
       <c r="F12" t="n">
         <v>1.0</v>
@@ -3492,7 +3492,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>280.0</v>
+        <v>283.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8825.0</v>
+        <v>8826.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2826.0</v>
+        <v>2828.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4967.0</v>
+        <v>4977.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3327.0</v>
+        <v>3331.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6814.0</v>
+        <v>6822.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3791,7 +3791,7 @@
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>2739.0</v>
+        <v>2740.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
@@ -3975,7 +3975,7 @@
         <v>27</v>
       </c>
       <c r="E34" t="n">
-        <v>584.0</v>
+        <v>585.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1596,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>72.0</v>
+        <v>71.0</v>
       </c>
       <c r="G55" t="n">
         <v>6.0</v>
@@ -3160,7 +3160,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F28" t="n">
         <v>5.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3146.0</v>
+        <v>3147.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3952,7 +3952,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>1690.0</v>
+        <v>1691.0</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2220,7 +2220,7 @@
         <v>36</v>
       </c>
       <c r="F79" t="n">
-        <v>133.0</v>
+        <v>134.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2772,7 +2772,7 @@
         <v>19.0</v>
       </c>
       <c r="F11" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G11" t="n">
         <v>1.0</v>
@@ -2795,7 +2795,7 @@
         <v>130.0</v>
       </c>
       <c r="F12" t="n">
-        <v>70.0</v>
+        <v>72.0</v>
       </c>
       <c r="G12" t="n">
         <v>236.0</v>
@@ -2818,7 +2818,7 @@
         <v>39.0</v>
       </c>
       <c r="F13" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G13" t="n">
         <v>16.0</v>
@@ -2864,7 +2864,7 @@
         <v>15.0</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -3045,13 +3045,13 @@
         <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>98.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="24">
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>143.0</v>
+        <v>148.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>142.0</v>
+        <v>148.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3262,7 +3262,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>348.0</v>
+        <v>352.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3285,7 +3285,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>114.0</v>
+        <v>126.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>571.0</v>
+        <v>572.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3561,7 +3561,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3294.0</v>
+        <v>3297.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1516.0</v>
+        <v>1518.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2828.0</v>
+        <v>2829.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -764,7 +764,7 @@
         <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="G23" t="n">
         <v>1.0</v>
@@ -894,7 +894,7 @@
         <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1518,10 +1518,10 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1340.0</v>
+        <v>1341.0</v>
       </c>
       <c r="G52" t="n">
-        <v>683.0</v>
+        <v>687.0</v>
       </c>
       <c r="H52" t="n">
         <v>91.0</v>
@@ -1674,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G58" t="n">
         <v>92.0</v>
@@ -2930,10 +2930,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>82.0</v>
+        <v>85.0</v>
       </c>
       <c r="F18" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G18" t="n">
         <v>75.0</v>
@@ -3022,10 +3022,10 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="F22" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1021.0</v>
+        <v>1024.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3653,13 +3653,13 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8826.0</v>
+        <v>8838.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
       </c>
       <c r="G20" t="n">
-        <v>184.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="21">
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2829.0</v>
+        <v>2830.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3331.0</v>
+        <v>3332.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1287,7 +1287,7 @@
         <v>44.0</v>
       </c>
       <c r="G43" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="H43" t="n">
         <v>4.0</v>
@@ -2798,7 +2798,7 @@
         <v>72.0</v>
       </c>
       <c r="G12" t="n">
-        <v>236.0</v>
+        <v>237.0</v>
       </c>
     </row>
     <row r="13">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -3630,7 +3630,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>528.0</v>
+        <v>529.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1001,7 +1001,7 @@
         <v>30.0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H32" t="n">
         <v>1.0</v>
@@ -1102,7 +1102,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1544,7 +1544,7 @@
         <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>231.0</v>
+        <v>233.0</v>
       </c>
       <c r="G53" t="n">
         <v>70.0</v>
@@ -1599,7 +1599,7 @@
         <v>71.0</v>
       </c>
       <c r="G55" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H55" t="n">
         <v>1.0</v>
@@ -2090,7 +2090,7 @@
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G74" t="n">
         <v>130.0</v>
@@ -2798,7 +2798,7 @@
         <v>72.0</v>
       </c>
       <c r="G12" t="n">
-        <v>237.0</v>
+        <v>238.0</v>
       </c>
     </row>
     <row r="13">
@@ -2930,10 +2930,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="F18" t="n">
-        <v>24.0</v>
+        <v>27.0</v>
       </c>
       <c r="G18" t="n">
         <v>75.0</v>
@@ -3022,7 +3022,7 @@
         <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F22" t="n">
         <v>12.0</v>
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>148.0</v>
+        <v>156.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8838.0</v>
+        <v>8839.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4977.0</v>
+        <v>4978.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1674,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G58" t="n">
         <v>92.0</v>
@@ -1726,7 +1726,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1830,7 +1830,7 @@
         <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>140.0</v>
+        <v>143.0</v>
       </c>
       <c r="G64" t="n">
         <v>244.0</v>
@@ -1856,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G65" t="n">
         <v>124.0</v>
@@ -1882,7 +1882,7 @@
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>309.0</v>
+        <v>310.0</v>
       </c>
       <c r="G66" t="n">
         <v>16.0</v>
@@ -2067,7 +2067,7 @@
         <v>45.0</v>
       </c>
       <c r="G73" t="n">
-        <v>113.0</v>
+        <v>120.0</v>
       </c>
       <c r="H73" t="n">
         <v>1.0</v>
@@ -2171,7 +2171,7 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2936,7 +2936,7 @@
         <v>27.0</v>
       </c>
       <c r="G18" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="19">
@@ -3028,7 +3028,7 @@
         <v>12.0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -3051,7 +3051,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>105.0</v>
+        <v>108.0</v>
       </c>
     </row>
     <row r="24">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G57" t="n">
         <v>1.0</v>
@@ -1726,7 +1726,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="G60" t="n">
         <v>2.0</v>
@@ -1856,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="G65" t="n">
         <v>124.0</v>
@@ -2930,10 +2930,10 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>86.0</v>
+        <v>89.0</v>
       </c>
       <c r="F18" t="n">
-        <v>27.0</v>
+        <v>24.0</v>
       </c>
       <c r="G18" t="n">
         <v>76.0</v>
@@ -3160,7 +3160,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F28" t="n">
         <v>5.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2830.0</v>
+        <v>2831.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1518,7 +1518,7 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1341.0</v>
+        <v>1342.0</v>
       </c>
       <c r="G52" t="n">
         <v>687.0</v>
@@ -1544,7 +1544,7 @@
         <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>233.0</v>
+        <v>234.0</v>
       </c>
       <c r="G53" t="n">
         <v>70.0</v>
@@ -1570,7 +1570,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>253.0</v>
+        <v>255.0</v>
       </c>
       <c r="G54" t="n">
         <v>16.0</v>
@@ -1625,7 +1625,7 @@
         <v>129.0</v>
       </c>
       <c r="G56" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="H56" t="n">
         <v>10.0</v>
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G57" t="n">
         <v>1.0</v>
@@ -1677,7 +1677,7 @@
         <v>139.0</v>
       </c>
       <c r="G58" t="n">
-        <v>92.0</v>
+        <v>95.0</v>
       </c>
       <c r="H58" t="n">
         <v>4.0</v>
@@ -1700,7 +1700,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="G59" t="n">
         <v>47.0</v>
@@ -2067,7 +2067,7 @@
         <v>45.0</v>
       </c>
       <c r="G73" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="H73" t="n">
         <v>1.0</v>
@@ -2093,7 +2093,7 @@
         <v>52.0</v>
       </c>
       <c r="G74" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2798,7 +2798,7 @@
         <v>72.0</v>
       </c>
       <c r="G12" t="n">
-        <v>238.0</v>
+        <v>240.0</v>
       </c>
     </row>
     <row r="13">
@@ -2936,7 +2936,7 @@
         <v>24.0</v>
       </c>
       <c r="G18" t="n">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="19">
@@ -3045,13 +3045,13 @@
         <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>165.0</v>
+        <v>166.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
     </row>
     <row r="24">
@@ -3163,7 +3163,7 @@
         <v>3.0</v>
       </c>
       <c r="F28" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -3400,7 +3400,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1024.0</v>
+        <v>1025.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8839.0</v>
+        <v>8840.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2831.0</v>
+        <v>2832.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3699,7 +3699,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4978.0</v>
+        <v>4997.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3722,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3332.0</v>
+        <v>3335.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3768,7 +3768,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3147.0</v>
+        <v>3151.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -894,7 +894,7 @@
         <v>35</v>
       </c>
       <c r="F28" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -946,7 +946,7 @@
         <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1076,7 +1076,7 @@
         <v>36</v>
       </c>
       <c r="F35" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1856,7 +1856,7 @@
         <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>172.0</v>
+        <v>173.0</v>
       </c>
       <c r="G65" t="n">
         <v>124.0</v>
@@ -1934,7 +1934,7 @@
         <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G68" t="n">
         <v>6.0</v>
@@ -2145,7 +2145,7 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2379,7 +2379,7 @@
         <v>4.0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2798,7 +2798,7 @@
         <v>72.0</v>
       </c>
       <c r="G12" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
     </row>
     <row r="13">
@@ -3025,7 +3025,7 @@
         <v>17.0</v>
       </c>
       <c r="F22" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G22" t="n">
         <v>2.0</v>
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>156.0</v>
+        <v>160.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -426,7 +426,7 @@
         <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -1310,7 +1310,7 @@
         <v>37</v>
       </c>
       <c r="F44" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G44" t="n">
         <v>6.0</v>
@@ -1336,7 +1336,7 @@
         <v>35</v>
       </c>
       <c r="F45" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G45" t="n">
         <v>143.0</v>
@@ -1388,7 +1388,7 @@
         <v>37</v>
       </c>
       <c r="F47" t="n">
-        <v>82.0</v>
+        <v>84.0</v>
       </c>
       <c r="G47" t="n">
         <v>3.0</v>
@@ -1518,10 +1518,10 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>1342.0</v>
+        <v>1343.0</v>
       </c>
       <c r="G52" t="n">
-        <v>687.0</v>
+        <v>688.0</v>
       </c>
       <c r="H52" t="n">
         <v>91.0</v>
@@ -1596,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G55" t="n">
         <v>8.0</v>
@@ -1622,7 +1622,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="G56" t="n">
         <v>30.0</v>
@@ -1648,7 +1648,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>142.0</v>
+        <v>145.0</v>
       </c>
       <c r="G57" t="n">
         <v>1.0</v>
@@ -2171,7 +2171,7 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2769,7 +2769,7 @@
         <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="F11" t="n">
         <v>15.0</v>
@@ -2792,10 +2792,10 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>130.0</v>
+        <v>147.0</v>
       </c>
       <c r="F12" t="n">
-        <v>72.0</v>
+        <v>75.0</v>
       </c>
       <c r="G12" t="n">
         <v>241.0</v>
@@ -2815,7 +2815,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="F13" t="n">
         <v>44.0</v>
@@ -2861,7 +2861,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F15" t="n">
         <v>14.0</v>
@@ -3074,7 +3074,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>160.0</v>
+        <v>167.0</v>
       </c>
     </row>
     <row r="25">
@@ -3091,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3262,7 +3262,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>352.0</v>
+        <v>353.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3308,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3331,7 +3331,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>572.0</v>
+        <v>575.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3561,7 +3561,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3297.0</v>
+        <v>3327.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -3584,7 +3584,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1518.0</v>
+        <v>1521.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3630,7 +3630,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>529.0</v>
+        <v>531.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -3653,7 +3653,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8840.0</v>
+        <v>8846.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3676,7 +3676,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2832.0</v>
+        <v>2843.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="38">
   <si>
     <t>Area</t>
   </si>
@@ -1411,13 +1411,13 @@
         <v>30</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F48" t="n">
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1434,16 +1434,16 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F49" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1463,10 +1463,10 @@
         <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F50" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -1489,10 +1489,10 @@
         <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F51" t="n">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G51" t="n">
         <v>0.0</v>
@@ -1509,22 +1509,22 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F52" t="n">
-        <v>1343.0</v>
+        <v>16.0</v>
       </c>
       <c r="G52" t="n">
-        <v>688.0</v>
+        <v>0.0</v>
       </c>
       <c r="H52" t="n">
-        <v>91.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -1541,16 +1541,16 @@
         <v>31</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>234.0</v>
+        <v>1343.0</v>
       </c>
       <c r="G53" t="n">
-        <v>70.0</v>
+        <v>688.0</v>
       </c>
       <c r="H53" t="n">
-        <v>25.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="54">
@@ -1567,16 +1567,16 @@
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F54" t="n">
-        <v>255.0</v>
+        <v>234.0</v>
       </c>
       <c r="G54" t="n">
-        <v>16.0</v>
+        <v>70.0</v>
       </c>
       <c r="H54" t="n">
-        <v>8.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="55">
@@ -1590,19 +1590,19 @@
         <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F55" t="n">
-        <v>72.0</v>
+        <v>255.0</v>
       </c>
       <c r="G55" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H55" t="n">
         <v>8.0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="56">
@@ -1619,16 +1619,16 @@
         <v>32</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>130.0</v>
+        <v>73.0</v>
       </c>
       <c r="G56" t="n">
-        <v>30.0</v>
+        <v>8.0</v>
       </c>
       <c r="H56" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57">
@@ -1645,16 +1645,16 @@
         <v>32</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>145.0</v>
+        <v>131.0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.0</v>
+        <v>30.0</v>
       </c>
       <c r="H57" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="58">
@@ -1668,16 +1668,16 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F58" t="n">
-        <v>139.0</v>
+        <v>145.0</v>
       </c>
       <c r="G58" t="n">
-        <v>95.0</v>
+        <v>1.0</v>
       </c>
       <c r="H58" t="n">
         <v>4.0</v>
@@ -1697,16 +1697,16 @@
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>186.0</v>
+        <v>139.0</v>
       </c>
       <c r="G59" t="n">
-        <v>47.0</v>
+        <v>95.0</v>
       </c>
       <c r="H59" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="60">
@@ -1723,16 +1723,16 @@
         <v>22</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>110.0</v>
+        <v>186.0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0</v>
+        <v>47.0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="61">
@@ -1743,19 +1743,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F61" t="n">
-        <v>42.0</v>
+        <v>110.0</v>
       </c>
       <c r="G61" t="n">
-        <v>97.0</v>
+        <v>2.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1775,13 +1775,13 @@
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>78.0</v>
+        <v>42.0</v>
       </c>
       <c r="G62" t="n">
-        <v>21.0</v>
+        <v>97.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1801,13 +1801,13 @@
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F63" t="n">
-        <v>128.0</v>
+        <v>78.0</v>
       </c>
       <c r="G63" t="n">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1821,19 +1821,19 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F64" t="n">
-        <v>143.0</v>
+        <v>128.0</v>
       </c>
       <c r="G64" t="n">
-        <v>244.0</v>
+        <v>8.0</v>
       </c>
       <c r="H64" t="n">
         <v>0.0</v>
@@ -1853,16 +1853,16 @@
         <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>173.0</v>
+        <v>143.0</v>
       </c>
       <c r="G65" t="n">
-        <v>124.0</v>
+        <v>244.0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1879,16 +1879,16 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>310.0</v>
+        <v>173.0</v>
       </c>
       <c r="G66" t="n">
-        <v>16.0</v>
+        <v>124.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="67">
@@ -1902,16 +1902,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F67" t="n">
-        <v>120.0</v>
+        <v>310.0</v>
       </c>
       <c r="G67" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1931,13 +1931,13 @@
         <v>26</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F68" t="n">
-        <v>65.0</v>
+        <v>120.0</v>
       </c>
       <c r="G68" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1957,13 +1957,13 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>56.0</v>
+        <v>65.0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -1980,13 +1980,13 @@
         <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F70" t="n">
-        <v>15.0</v>
+        <v>56.0</v>
       </c>
       <c r="G70" t="n">
         <v>0.0</v>
@@ -2009,16 +2009,16 @@
         <v>27</v>
       </c>
       <c r="E71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F71" t="n">
-        <v>25.0</v>
+        <v>15.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2035,16 +2035,16 @@
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F72" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="G72" t="n">
         <v>0.0</v>
       </c>
       <c r="H72" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="73">
@@ -2055,19 +2055,19 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F73" t="n">
-        <v>45.0</v>
+        <v>22.0</v>
       </c>
       <c r="G73" t="n">
-        <v>121.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
         <v>1.0</v>
@@ -2087,16 +2087,16 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>52.0</v>
+        <v>47.0</v>
       </c>
       <c r="G74" t="n">
-        <v>131.0</v>
+        <v>124.0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="75">
@@ -2113,13 +2113,13 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F75" t="n">
-        <v>24.0</v>
+        <v>52.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>131.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2136,16 +2136,16 @@
         <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="G76" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2165,13 +2165,13 @@
         <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n">
         <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>31.0</v>
+        <v>18.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2188,16 +2188,16 @@
         <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E78" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>31.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2217,16 +2217,16 @@
         <v>34</v>
       </c>
       <c r="E79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n">
-        <v>134.0</v>
+        <v>24.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
       </c>
       <c r="H79" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2243,16 +2243,16 @@
         <v>34</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>36.0</v>
+        <v>134.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="81">
@@ -2260,22 +2260,22 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E81" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="G81" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2289,19 +2289,19 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E82" t="s">
         <v>35</v>
       </c>
       <c r="F82" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G82" t="n">
-        <v>61.0</v>
+        <v>12.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2321,13 +2321,13 @@
         <v>25</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F83" t="n">
-        <v>31.0</v>
+        <v>24.0</v>
       </c>
       <c r="G83" t="n">
-        <v>18.0</v>
+        <v>61.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2347,13 +2347,13 @@
         <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F84" t="n">
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="G84" t="n">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2370,16 +2370,16 @@
         <v>15</v>
       </c>
       <c r="D85" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F85" t="n">
-        <v>4.0</v>
+        <v>46.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2399,16 +2399,16 @@
         <v>26</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F86" t="n">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H86" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2425,16 +2425,16 @@
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F87" t="n">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H87" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="88">
@@ -2448,13 +2448,13 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F88" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
@@ -2477,16 +2477,16 @@
         <v>27</v>
       </c>
       <c r="E89" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2503,15 +2503,41 @@
         <v>27</v>
       </c>
       <c r="E90" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>27</v>
+      </c>
+      <c r="E91" t="s">
         <v>37</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F91" t="n">
         <v>2.0</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H90" t="n">
+      <c r="G91" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H91" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2723,10 +2749,10 @@
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -3051,7 +3077,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>109.0</v>
+        <v>112.0</v>
       </c>
     </row>
     <row r="24">
@@ -3074,7 +3100,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>167.0</v>
+        <v>173.0</v>
       </c>
     </row>
     <row r="25">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1287,7 +1287,7 @@
         <v>44.0</v>
       </c>
       <c r="G43" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="H43" t="n">
         <v>4.0</v>
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1625,7 +1625,7 @@
         <v>73.0</v>
       </c>
       <c r="G56" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="H56" t="n">
         <v>1.0</v>
@@ -2749,13 +2749,13 @@
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="10">
@@ -3702,7 +3702,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2843.0</v>
+        <v>2844.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3725,7 +3725,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4997.0</v>
+        <v>4998.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1648,7 +1648,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G57" t="n">
         <v>30.0</v>
@@ -1804,7 +1804,7 @@
         <v>36</v>
       </c>
       <c r="F63" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G63" t="n">
         <v>21.0</v>
@@ -2818,13 +2818,13 @@
         <v>19</v>
       </c>
       <c r="E12" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="F12" t="n">
         <v>75.0</v>
       </c>
       <c r="G12" t="n">
-        <v>241.0</v>
+        <v>244.0</v>
       </c>
     </row>
     <row r="13">
@@ -3288,7 +3288,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>353.0</v>
+        <v>357.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3334,7 +3334,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>258.0</v>
+        <v>259.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3426,7 +3426,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1025.0</v>
+        <v>1026.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3449,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1102.0</v>
+        <v>1104.0</v>
       </c>
       <c r="F10" t="n">
         <v>0.0</v>
@@ -3564,7 +3564,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>267.0</v>
+        <v>271.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3610,7 +3610,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1521.0</v>
+        <v>1523.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -3702,7 +3702,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2844.0</v>
+        <v>2847.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3748,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3335.0</v>
+        <v>3336.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -920,7 +920,7 @@
         <v>36</v>
       </c>
       <c r="F29" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1700,7 +1700,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>139.0</v>
+        <v>141.0</v>
       </c>
       <c r="G59" t="n">
         <v>95.0</v>
@@ -1856,7 +1856,7 @@
         <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>143.0</v>
+        <v>145.0</v>
       </c>
       <c r="G65" t="n">
         <v>244.0</v>
@@ -1908,7 +1908,7 @@
         <v>37</v>
       </c>
       <c r="F67" t="n">
-        <v>310.0</v>
+        <v>311.0</v>
       </c>
       <c r="G67" t="n">
         <v>16.0</v>
@@ -1960,7 +1960,7 @@
         <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G69" t="n">
         <v>6.0</v>
@@ -2197,7 +2197,7 @@
         <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2749,10 +2749,10 @@
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -2956,7 +2956,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
       <c r="F18" t="n">
         <v>24.0</v>
@@ -3051,7 +3051,7 @@
         <v>17.0</v>
       </c>
       <c r="F22" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="G22" t="n">
         <v>2.0</v>
@@ -3100,7 +3100,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>173.0</v>
+        <v>179.0</v>
       </c>
     </row>
     <row r="25">
@@ -3117,7 +3117,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3472,7 +3472,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>878.0</v>
+        <v>882.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3725,7 +3725,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>4998.0</v>
+        <v>5009.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3151.0</v>
+        <v>3153.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1544,10 +1544,10 @@
         <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>1343.0</v>
+        <v>1344.0</v>
       </c>
       <c r="G53" t="n">
-        <v>688.0</v>
+        <v>691.0</v>
       </c>
       <c r="H53" t="n">
         <v>91.0</v>
@@ -1570,7 +1570,7 @@
         <v>36</v>
       </c>
       <c r="F54" t="n">
-        <v>234.0</v>
+        <v>236.0</v>
       </c>
       <c r="G54" t="n">
         <v>70.0</v>
@@ -1596,7 +1596,7 @@
         <v>37</v>
       </c>
       <c r="F55" t="n">
-        <v>255.0</v>
+        <v>257.0</v>
       </c>
       <c r="G55" t="n">
         <v>16.0</v>
@@ -1622,7 +1622,7 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="G56" t="n">
         <v>9.0</v>
@@ -1648,7 +1648,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G57" t="n">
         <v>30.0</v>
@@ -2093,7 +2093,7 @@
         <v>47.0</v>
       </c>
       <c r="G74" t="n">
-        <v>124.0</v>
+        <v>132.0</v>
       </c>
       <c r="H74" t="n">
         <v>1.0</v>
@@ -2197,7 +2197,7 @@
         <v>0.0</v>
       </c>
       <c r="G78" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2962,7 +2962,7 @@
         <v>24.0</v>
       </c>
       <c r="G18" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="19">
@@ -3077,7 +3077,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>112.0</v>
+        <v>116.0</v>
       </c>
     </row>
     <row r="24">
@@ -3100,7 +3100,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="25">
@@ -3186,10 +3186,10 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F28" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" t="n">
         <v>1.0</v>
@@ -3679,7 +3679,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8846.0</v>
+        <v>8852.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3702,7 +3702,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2847.0</v>
+        <v>2855.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3725,7 +3725,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>5009.0</v>
+        <v>5010.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3846,7 +3846,7 @@
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="28">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1261,7 +1261,7 @@
         <v>55.0</v>
       </c>
       <c r="G42" t="n">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="H42" t="n">
         <v>4.0</v>
@@ -2824,7 +2824,7 @@
         <v>75.0</v>
       </c>
       <c r="G12" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="13">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1703,7 +1703,7 @@
         <v>141.0</v>
       </c>
       <c r="G59" t="n">
-        <v>95.0</v>
+        <v>96.0</v>
       </c>
       <c r="H59" t="n">
         <v>4.0</v>
@@ -2246,7 +2246,7 @@
         <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="G80" t="n">
         <v>0.0</v>
@@ -3100,7 +3100,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>181.0</v>
+        <v>183.0</v>
       </c>
     </row>
     <row r="25">
@@ -3117,7 +3117,7 @@
         <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>152.0</v>
+        <v>158.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1287,7 +1287,7 @@
         <v>44.0</v>
       </c>
       <c r="G43" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="H43" t="n">
         <v>4.0</v>
@@ -1339,7 +1339,7 @@
         <v>32.0</v>
       </c>
       <c r="G45" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="H45" t="n">
         <v>4.0</v>
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1544,7 +1544,7 @@
         <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>1344.0</v>
+        <v>1349.0</v>
       </c>
       <c r="G53" t="n">
         <v>691.0</v>
@@ -1674,7 +1674,7 @@
         <v>37</v>
       </c>
       <c r="F58" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="G58" t="n">
         <v>1.0</v>
@@ -1729,7 +1729,7 @@
         <v>186.0</v>
       </c>
       <c r="G60" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="H60" t="n">
         <v>12.0</v>
@@ -1960,7 +1960,7 @@
         <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>66.0</v>
+        <v>68.0</v>
       </c>
       <c r="G69" t="n">
         <v>6.0</v>
@@ -2749,10 +2749,10 @@
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>7.0</v>
+        <v>11.0</v>
       </c>
       <c r="F9" t="n">
-        <v>8.0</v>
+        <v>12.0</v>
       </c>
       <c r="G9" t="n">
         <v>1.0</v>
@@ -3679,7 +3679,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8852.0</v>
+        <v>8856.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -3702,7 +3702,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2855.0</v>
+        <v>2860.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3725,7 +3725,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>5010.0</v>
+        <v>5012.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -608,7 +608,7 @@
         <v>35</v>
       </c>
       <c r="F17" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -1287,7 +1287,7 @@
         <v>44.0</v>
       </c>
       <c r="G43" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="H43" t="n">
         <v>4.0</v>
@@ -1417,7 +1417,7 @@
         <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1622,7 +1622,7 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="G56" t="n">
         <v>9.0</v>
@@ -1651,7 +1651,7 @@
         <v>133.0</v>
       </c>
       <c r="G57" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="H57" t="n">
         <v>10.0</v>
@@ -1700,7 +1700,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>141.0</v>
+        <v>143.0</v>
       </c>
       <c r="G59" t="n">
         <v>96.0</v>
@@ -2755,7 +2755,7 @@
         <v>12.0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="10">
@@ -3077,7 +3077,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>116.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="24">
@@ -3426,7 +3426,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1026.0</v>
+        <v>1031.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3702,7 +3702,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>2860.0</v>
+        <v>2861.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3725,7 +3725,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>5012.0</v>
+        <v>5014.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="37">
   <si>
     <t>Area</t>
   </si>
@@ -83,9 +83,6 @@
   </si>
   <si>
     <t>Savona</t>
-  </si>
-  <si>
-    <t>Lodi</t>
   </si>
   <si>
     <t>Pavia</t>
@@ -215,7 +212,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>5.0</v>
@@ -241,7 +238,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
         <v>1.0</v>
@@ -267,7 +264,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -293,7 +290,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F5" t="n">
         <v>9.0</v>
@@ -319,7 +316,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>7.0</v>
@@ -345,7 +342,7 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" t="n">
         <v>7.0</v>
@@ -371,7 +368,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" t="n">
         <v>5.0</v>
@@ -397,10 +394,10 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -423,7 +420,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" t="n">
         <v>27.0</v>
@@ -449,7 +446,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
         <v>10.0</v>
@@ -475,7 +472,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
         <v>9.0</v>
@@ -501,7 +498,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
         <v>33.0</v>
@@ -527,7 +524,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F14" t="n">
         <v>8.0</v>
@@ -553,7 +550,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F15" t="n">
         <v>25.0</v>
@@ -579,7 +576,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>79.0</v>
@@ -605,7 +602,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
         <v>19.0</v>
@@ -631,7 +628,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
         <v>15.0</v>
@@ -657,7 +654,7 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" t="n">
         <v>5.0</v>
@@ -683,13 +680,13 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="H20" t="n">
         <v>0.0</v>
@@ -709,16 +706,16 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.0</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="22">
@@ -732,16 +729,16 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" t="n">
-        <v>15.0</v>
+        <v>47.0</v>
       </c>
       <c r="G22" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H22" t="n">
         <v>0.0</v>
@@ -755,22 +752,22 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F23" t="n">
-        <v>48.0</v>
+        <v>19.0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -781,16 +778,16 @@
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F24" t="n">
-        <v>50.0</v>
+        <v>15.0</v>
       </c>
       <c r="G24" t="n">
         <v>1.0</v>
@@ -810,13 +807,13 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F25" t="n">
-        <v>13.0</v>
+        <v>72.0</v>
       </c>
       <c r="G25" t="n">
         <v>0.0</v>
@@ -839,10 +836,10 @@
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26" t="n">
-        <v>23.0</v>
+        <v>54.0</v>
       </c>
       <c r="G26" t="n">
         <v>0.0</v>
@@ -865,13 +862,13 @@
         <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F27" t="n">
-        <v>40.0</v>
+        <v>22.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H27" t="n">
         <v>0.0</v>
@@ -888,13 +885,13 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -917,16 +914,16 @@
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F29" t="n">
-        <v>41.0</v>
+        <v>20.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="30">
@@ -943,16 +940,16 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
-        <v>53.0</v>
+        <v>35.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="31">
@@ -966,13 +963,13 @@
         <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F31" t="n">
-        <v>19.0</v>
+        <v>43.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -989,22 +986,22 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F32" t="n">
-        <v>30.0</v>
+        <v>6.0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -1015,16 +1012,16 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D33" t="s">
         <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>39.0</v>
+        <v>14.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1044,13 +1041,13 @@
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F34" t="n">
-        <v>6.0</v>
+        <v>29.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1073,10 +1070,10 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1099,10 +1096,10 @@
         <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F36" t="n">
-        <v>29.0</v>
+        <v>1.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1116,22 +1113,22 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F37" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1142,19 +1139,19 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F38" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1177,13 +1174,13 @@
         <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F39" t="n">
         <v>5.0</v>
       </c>
       <c r="G39" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H39" t="n">
         <v>0.0</v>
@@ -1200,19 +1197,19 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F40" t="n">
-        <v>9.0</v>
+        <v>56.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>68.0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="41">
@@ -1226,19 +1223,19 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F41" t="n">
-        <v>5.0</v>
+        <v>44.0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0</v>
+        <v>33.0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="42">
@@ -1255,16 +1252,16 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F42" t="n">
-        <v>55.0</v>
+        <v>112.0</v>
       </c>
       <c r="G42" t="n">
-        <v>68.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -1278,16 +1275,16 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F43" t="n">
-        <v>44.0</v>
+        <v>32.0</v>
       </c>
       <c r="G43" t="n">
-        <v>33.0</v>
+        <v>144.0</v>
       </c>
       <c r="H43" t="n">
         <v>4.0</v>
@@ -1304,19 +1301,19 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F44" t="n">
-        <v>112.0</v>
+        <v>41.0</v>
       </c>
       <c r="G44" t="n">
-        <v>6.0</v>
+        <v>27.0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="45">
@@ -1333,16 +1330,16 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F45" t="n">
-        <v>32.0</v>
+        <v>84.0</v>
       </c>
       <c r="G45" t="n">
-        <v>144.0</v>
+        <v>3.0</v>
       </c>
       <c r="H45" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1356,19 +1353,19 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F46" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
       <c r="G46" t="n">
-        <v>27.0</v>
+        <v>14.0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1382,16 +1379,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F47" t="n">
-        <v>84.0</v>
+        <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1408,16 +1405,16 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G48" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1434,16 +1431,16 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G49" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H49" t="n">
         <v>0.0</v>
@@ -1463,10 +1460,10 @@
         <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F50" t="n">
-        <v>4.0</v>
+        <v>16.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -1483,22 +1480,22 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F51" t="n">
-        <v>13.0</v>
+        <v>1349.0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0</v>
+        <v>691.0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="52">
@@ -1509,22 +1506,22 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>16.0</v>
+        <v>236.0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0</v>
+        <v>70.0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="53">
@@ -1538,19 +1535,19 @@
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>1349.0</v>
+        <v>257.0</v>
       </c>
       <c r="G53" t="n">
-        <v>691.0</v>
+        <v>16.0</v>
       </c>
       <c r="H53" t="n">
-        <v>91.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="54">
@@ -1567,16 +1564,16 @@
         <v>31</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>236.0</v>
+        <v>75.0</v>
       </c>
       <c r="G54" t="n">
-        <v>70.0</v>
+        <v>9.0</v>
       </c>
       <c r="H54" t="n">
-        <v>25.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="55">
@@ -1593,16 +1590,16 @@
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>257.0</v>
+        <v>133.0</v>
       </c>
       <c r="G55" t="n">
-        <v>16.0</v>
+        <v>31.0</v>
       </c>
       <c r="H55" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="56">
@@ -1616,19 +1613,19 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>75.0</v>
+        <v>147.0</v>
       </c>
       <c r="G56" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="57">
@@ -1642,19 +1639,19 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>133.0</v>
+        <v>143.0</v>
       </c>
       <c r="G57" t="n">
-        <v>31.0</v>
+        <v>96.0</v>
       </c>
       <c r="H57" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="58">
@@ -1668,19 +1665,19 @@
         <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F58" t="n">
-        <v>147.0</v>
+        <v>186.0</v>
       </c>
       <c r="G58" t="n">
-        <v>1.0</v>
+        <v>49.0</v>
       </c>
       <c r="H58" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="59">
@@ -1697,16 +1694,16 @@
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>143.0</v>
+        <v>110.0</v>
       </c>
       <c r="G59" t="n">
-        <v>96.0</v>
+        <v>2.0</v>
       </c>
       <c r="H59" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1717,22 +1714,22 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F60" t="n">
-        <v>186.0</v>
+        <v>42.0</v>
       </c>
       <c r="G60" t="n">
-        <v>49.0</v>
+        <v>97.0</v>
       </c>
       <c r="H60" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1743,19 +1740,19 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F61" t="n">
-        <v>110.0</v>
+        <v>79.0</v>
       </c>
       <c r="G61" t="n">
-        <v>2.0</v>
+        <v>21.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1772,16 +1769,16 @@
         <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>42.0</v>
+        <v>128.0</v>
       </c>
       <c r="G62" t="n">
-        <v>97.0</v>
+        <v>8.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1795,19 +1792,19 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F63" t="n">
-        <v>79.0</v>
+        <v>127.0</v>
       </c>
       <c r="G63" t="n">
-        <v>21.0</v>
+        <v>244.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1821,22 +1818,22 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>128.0</v>
+        <v>158.0</v>
       </c>
       <c r="G64" t="n">
-        <v>8.0</v>
+        <v>123.0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="65">
@@ -1850,16 +1847,16 @@
         <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>145.0</v>
+        <v>240.0</v>
       </c>
       <c r="G65" t="n">
-        <v>244.0</v>
+        <v>16.0</v>
       </c>
       <c r="H65" t="n">
         <v>0.0</v>
@@ -1879,16 +1876,16 @@
         <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F66" t="n">
-        <v>173.0</v>
+        <v>75.0</v>
       </c>
       <c r="G66" t="n">
-        <v>124.0</v>
+        <v>2.0</v>
       </c>
       <c r="H66" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1905,13 +1902,13 @@
         <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F67" t="n">
-        <v>311.0</v>
+        <v>48.0</v>
       </c>
       <c r="G67" t="n">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1928,16 +1925,16 @@
         <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>120.0</v>
+        <v>41.0</v>
       </c>
       <c r="G68" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1957,13 +1954,13 @@
         <v>26</v>
       </c>
       <c r="E69" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F69" t="n">
-        <v>68.0</v>
+        <v>21.0</v>
       </c>
       <c r="G69" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -1983,16 +1980,16 @@
         <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F70" t="n">
-        <v>56.0</v>
+        <v>32.0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="71">
@@ -2006,19 +2003,19 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>15.0</v>
+        <v>30.0</v>
       </c>
       <c r="G71" t="n">
         <v>0.0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="72">
@@ -2029,22 +2026,22 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D72" t="s">
         <v>27</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F72" t="n">
-        <v>25.0</v>
+        <v>47.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>132.0</v>
       </c>
       <c r="H72" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="73">
@@ -2055,22 +2052,22 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D73" t="s">
         <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F73" t="n">
-        <v>22.0</v>
+        <v>52.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>131.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2084,19 +2081,19 @@
         <v>16</v>
       </c>
       <c r="D74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>47.0</v>
+        <v>24.0</v>
       </c>
       <c r="G74" t="n">
-        <v>132.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -2110,16 +2107,16 @@
         <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E75" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F75" t="n">
-        <v>52.0</v>
+        <v>0.0</v>
       </c>
       <c r="G75" t="n">
-        <v>131.0</v>
+        <v>18.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2136,16 +2133,16 @@
         <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E76" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F76" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2165,13 +2162,13 @@
         <v>33</v>
       </c>
       <c r="E77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="G77" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2191,16 +2188,16 @@
         <v>33</v>
       </c>
       <c r="E78" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0</v>
+        <v>135.0</v>
       </c>
       <c r="G78" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="79">
@@ -2214,13 +2211,13 @@
         <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F79" t="n">
-        <v>24.0</v>
+        <v>36.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2234,25 +2231,25 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" t="s">
         <v>34</v>
       </c>
-      <c r="E80" t="s">
-        <v>36</v>
-      </c>
       <c r="F80" t="n">
-        <v>135.0</v>
+        <v>1.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="H80" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -2260,22 +2257,22 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D81" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" t="s">
         <v>34</v>
       </c>
-      <c r="E81" t="s">
-        <v>37</v>
-      </c>
       <c r="F81" t="n">
-        <v>36.0</v>
+        <v>24.0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2289,19 +2286,19 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
         <v>35</v>
       </c>
       <c r="F82" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="G82" t="n">
-        <v>12.0</v>
+        <v>18.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2318,16 +2315,16 @@
         <v>15</v>
       </c>
       <c r="D83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F83" t="n">
-        <v>24.0</v>
+        <v>46.0</v>
       </c>
       <c r="G83" t="n">
-        <v>61.0</v>
+        <v>3.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2347,13 +2344,13 @@
         <v>25</v>
       </c>
       <c r="E84" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F84" t="n">
-        <v>31.0</v>
+        <v>4.0</v>
       </c>
       <c r="G84" t="n">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2373,16 +2370,16 @@
         <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F85" t="n">
-        <v>46.0</v>
+        <v>19.0</v>
       </c>
       <c r="G85" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="86">
@@ -2396,16 +2393,16 @@
         <v>15</v>
       </c>
       <c r="D86" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F86" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G86" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H86" t="n">
         <v>0.0</v>
@@ -2425,16 +2422,16 @@
         <v>26</v>
       </c>
       <c r="E87" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F87" t="n">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="G87" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H87" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="88">
@@ -2451,16 +2448,16 @@
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F88" t="n">
-        <v>10.0</v>
+        <v>21.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="89">
@@ -2474,70 +2471,18 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E89" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F89" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
       </c>
       <c r="H89" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>8</v>
-      </c>
-      <c r="B90" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" t="s">
-        <v>27</v>
-      </c>
-      <c r="E90" t="s">
-        <v>36</v>
-      </c>
-      <c r="F90" t="n">
-        <v>21.0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>8</v>
-      </c>
-      <c r="B91" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91" t="s">
-        <v>27</v>
-      </c>
-      <c r="E91" t="s">
-        <v>37</v>
-      </c>
-      <c r="F91" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H91" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2657,13 +2602,13 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6">
@@ -2674,19 +2619,19 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0</v>
+        <v>12.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -2703,10 +2648,10 @@
         <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -2726,7 +2671,7 @@
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F8" t="n">
         <v>1.0</v>
@@ -2743,19 +2688,19 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
         <v>27</v>
       </c>
       <c r="E9" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="F9" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="G9" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -2763,22 +2708,22 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -2792,16 +2737,16 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>20.0</v>
+        <v>149.0</v>
       </c>
       <c r="F11" t="n">
-        <v>15.0</v>
+        <v>75.0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0</v>
+        <v>245.0</v>
       </c>
     </row>
     <row r="12">
@@ -2815,16 +2760,16 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>149.0</v>
+        <v>40.0</v>
       </c>
       <c r="F12" t="n">
-        <v>75.0</v>
+        <v>44.0</v>
       </c>
       <c r="G12" t="n">
-        <v>245.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="13">
@@ -2838,16 +2783,16 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="F13" t="n">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
       <c r="G13" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14">
@@ -2861,16 +2806,16 @@
         <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="15">
@@ -2881,19 +2826,19 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="F15" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="16">
@@ -2910,13 +2855,13 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="F16" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G16" t="n">
-        <v>50.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="17">
@@ -2930,16 +2875,16 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>17.0</v>
+        <v>90.0</v>
       </c>
       <c r="F17" t="n">
-        <v>6.0</v>
+        <v>24.0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0</v>
+        <v>81.0</v>
       </c>
     </row>
     <row r="18">
@@ -2950,19 +2895,19 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>90.0</v>
+        <v>19.0</v>
       </c>
       <c r="F18" t="n">
-        <v>24.0</v>
+        <v>7.0</v>
       </c>
       <c r="G18" t="n">
-        <v>81.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -2973,19 +2918,19 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>19.0</v>
+        <v>34.0</v>
       </c>
       <c r="F19" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="20">
@@ -2999,16 +2944,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>46.0</v>
+        <v>26.0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.0</v>
+        <v>26.0</v>
       </c>
       <c r="G20" t="n">
-        <v>25.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="21">
@@ -3019,19 +2964,19 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>14.0</v>
+        <v>166.0</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0</v>
+        <v>117.0</v>
       </c>
     </row>
     <row r="22">
@@ -3042,19 +2987,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="F22" t="n">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="23">
@@ -3068,16 +3013,16 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E23" t="n">
-        <v>166.0</v>
+        <v>160.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>117.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -3085,22 +3030,22 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>183.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -3108,22 +3053,22 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>158.0</v>
+        <v>17.0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="26">
@@ -3134,19 +3079,19 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G26" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -3160,61 +3105,15 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="F27" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27" t="n">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
-      <c r="D29" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G29" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3334,7 +3233,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>259.0</v>
+        <v>260.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3357,7 +3256,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>575.0</v>
+        <v>581.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3403,13 +3302,13 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>24.0</v>
+        <v>656.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="9">
@@ -3420,19 +3319,19 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1031.0</v>
+        <v>1295.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
       </c>
       <c r="G9" t="n">
-        <v>11.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="10">
@@ -3449,13 +3348,13 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1104.0</v>
+        <v>1746.0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
@@ -3472,7 +3371,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>882.0</v>
+        <v>1171.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3489,16 +3388,16 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>1694.0</v>
+        <v>284.0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" t="n">
         <v>0.0</v>
@@ -3518,7 +3417,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>283.0</v>
+        <v>139.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3532,16 +3431,16 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>139.0</v>
+        <v>271.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3561,16 +3460,16 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>271.0</v>
+        <v>3336.0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="16">
@@ -3584,16 +3483,16 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>3327.0</v>
+        <v>1532.0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="17">
@@ -3607,16 +3506,16 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
-        <v>1523.0</v>
+        <v>0.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>40.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
@@ -3630,16 +3529,16 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0</v>
+        <v>533.0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -3650,19 +3549,19 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>531.0</v>
+        <v>8856.0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>185.0</v>
       </c>
     </row>
     <row r="20">
@@ -3679,13 +3578,13 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>8856.0</v>
+        <v>2861.0</v>
       </c>
       <c r="F20" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>185.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="21">
@@ -3699,16 +3598,16 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>2861.0</v>
+        <v>5014.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="22">
@@ -3719,19 +3618,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>5014.0</v>
+        <v>3336.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>5.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="23">
@@ -3742,19 +3641,19 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>3336.0</v>
+        <v>5634.0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" t="n">
-        <v>82.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="24">
@@ -3771,13 +3670,13 @@
         <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>6822.0</v>
+        <v>1581.0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>171.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="25">
@@ -3794,13 +3693,13 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3153.0</v>
+        <v>3315.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3811,19 +3710,19 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
         <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>2740.0</v>
+        <v>416.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="27">
@@ -3837,16 +3736,16 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E27" t="n">
-        <v>416.0</v>
+        <v>0.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>6.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="28">
@@ -3863,13 +3762,13 @@
         <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0</v>
+        <v>3053.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>47.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -3883,10 +3782,10 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>3053.0</v>
+        <v>20.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -3900,16 +3799,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E30" t="n">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -3926,19 +3825,19 @@
         <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>14.0</v>
+        <v>2229.0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="32">
@@ -3955,13 +3854,13 @@
         <v>25</v>
       </c>
       <c r="E32" t="n">
-        <v>2229.0</v>
+        <v>1691.0</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G32" t="n">
-        <v>49.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="33">
@@ -3978,35 +3877,12 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>1691.0</v>
+        <v>585.0</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" t="s">
-        <v>27</v>
-      </c>
-      <c r="E34" t="n">
-        <v>585.0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G34" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1362,7 +1362,7 @@
         <v>0.0</v>
       </c>
       <c r="G46" t="n">
-        <v>14.0</v>
+        <v>21.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1489,13 +1489,13 @@
         <v>34</v>
       </c>
       <c r="F51" t="n">
-        <v>1349.0</v>
+        <v>1352.0</v>
       </c>
       <c r="G51" t="n">
-        <v>691.0</v>
+        <v>696.0</v>
       </c>
       <c r="H51" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="52">
@@ -1515,7 +1515,7 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>236.0</v>
+        <v>239.0</v>
       </c>
       <c r="G52" t="n">
         <v>70.0</v>
@@ -1541,7 +1541,7 @@
         <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
       <c r="G53" t="n">
         <v>16.0</v>
@@ -1827,7 +1827,7 @@
         <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>158.0</v>
+        <v>161.0</v>
       </c>
       <c r="G64" t="n">
         <v>123.0</v>
@@ -2950,7 +2950,7 @@
         <v>26.0</v>
       </c>
       <c r="F20" t="n">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="G20" t="n">
         <v>9.0</v>
@@ -3187,7 +3187,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>357.0</v>
+        <v>363.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3440,7 +3440,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>271.0</v>
+        <v>273.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3555,7 +3555,7 @@
         <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>8856.0</v>
+        <v>8865.0</v>
       </c>
       <c r="F19" t="n">
         <v>18.0</v>
@@ -3578,7 +3578,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2861.0</v>
+        <v>2870.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1515,7 +1515,7 @@
         <v>35</v>
       </c>
       <c r="F52" t="n">
-        <v>239.0</v>
+        <v>240.0</v>
       </c>
       <c r="G52" t="n">
         <v>70.0</v>
@@ -1567,7 +1567,7 @@
         <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
       <c r="G54" t="n">
         <v>9.0</v>
@@ -1619,7 +1619,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="G56" t="n">
         <v>1.0</v>
@@ -1827,7 +1827,7 @@
         <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>161.0</v>
+        <v>163.0</v>
       </c>
       <c r="G64" t="n">
         <v>123.0</v>
@@ -2878,7 +2878,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
       <c r="F17" t="n">
         <v>24.0</v>
@@ -2947,7 +2947,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="F20" t="n">
         <v>29.0</v>
@@ -2976,7 +2976,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="22">
@@ -2999,7 +2999,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>187.0</v>
+        <v>189.0</v>
       </c>
     </row>
     <row r="23">
@@ -3016,7 +3016,7 @@
         <v>33</v>
       </c>
       <c r="E23" t="n">
-        <v>160.0</v>
+        <v>163.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3325,7 +3325,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1295.0</v>
+        <v>1299.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3555,13 +3555,13 @@
         <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>8865.0</v>
+        <v>8871.0</v>
       </c>
       <c r="F19" t="n">
         <v>18.0</v>
       </c>
       <c r="G19" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
     </row>
     <row r="20">
@@ -3578,7 +3578,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2870.0</v>
+        <v>2871.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3601,7 +3601,7 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>5014.0</v>
+        <v>5015.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2999,7 +2999,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>189.0</v>
+        <v>192.0</v>
       </c>
     </row>
     <row r="23">

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1255,7 +1255,7 @@
         <v>36</v>
       </c>
       <c r="F42" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G42" t="n">
         <v>6.0</v>
@@ -1362,7 +1362,7 @@
         <v>0.0</v>
       </c>
       <c r="G46" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -2064,7 +2064,7 @@
         <v>52.0</v>
       </c>
       <c r="G73" t="n">
-        <v>131.0</v>
+        <v>129.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2743,10 +2743,10 @@
         <v>149.0</v>
       </c>
       <c r="F11" t="n">
-        <v>75.0</v>
+        <v>77.0</v>
       </c>
       <c r="G11" t="n">
-        <v>245.0</v>
+        <v>249.0</v>
       </c>
     </row>
     <row r="12">
@@ -2947,13 +2947,13 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>27.0</v>
+        <v>31.0</v>
       </c>
       <c r="F20" t="n">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="G20" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="21">
@@ -2976,7 +2976,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>118.0</v>
+        <v>120.0</v>
       </c>
     </row>
     <row r="22">
@@ -3693,7 +3693,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3315.0</v>
+        <v>3316.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1362,7 +1362,7 @@
         <v>0.0</v>
       </c>
       <c r="G46" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1645,7 +1645,7 @@
         <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>143.0</v>
+        <v>146.0</v>
       </c>
       <c r="G57" t="n">
         <v>96.0</v>
@@ -1801,7 +1801,7 @@
         <v>34</v>
       </c>
       <c r="F63" t="n">
-        <v>127.0</v>
+        <v>130.0</v>
       </c>
       <c r="G63" t="n">
         <v>244.0</v>
@@ -1827,7 +1827,7 @@
         <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G64" t="n">
         <v>123.0</v>
@@ -2746,7 +2746,7 @@
         <v>77.0</v>
       </c>
       <c r="G11" t="n">
-        <v>249.0</v>
+        <v>252.0</v>
       </c>
     </row>
     <row r="12">
@@ -2947,10 +2947,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="F20" t="n">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -3555,7 +3555,7 @@
         <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>8871.0</v>
+        <v>8881.0</v>
       </c>
       <c r="F19" t="n">
         <v>18.0</v>
@@ -3578,7 +3578,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2871.0</v>
+        <v>2881.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3601,7 +3601,7 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>5015.0</v>
+        <v>5020.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3624,7 +3624,7 @@
         <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>3336.0</v>
+        <v>3338.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3647,7 +3647,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>5634.0</v>
+        <v>5635.0</v>
       </c>
       <c r="F23" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -553,7 +553,7 @@
         <v>35</v>
       </c>
       <c r="F15" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -1021,7 +1021,7 @@
         <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1362,7 +1362,7 @@
         <v>0.0</v>
       </c>
       <c r="G46" t="n">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1593,7 +1593,7 @@
         <v>35</v>
       </c>
       <c r="F55" t="n">
-        <v>133.0</v>
+        <v>136.0</v>
       </c>
       <c r="G55" t="n">
         <v>31.0</v>
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="F11" t="n">
         <v>77.0</v>
       </c>
       <c r="G11" t="n">
-        <v>252.0</v>
+        <v>254.0</v>
       </c>
     </row>
     <row r="12">
@@ -2878,10 +2878,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>91.0</v>
+        <v>95.0</v>
       </c>
       <c r="F17" t="n">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="G17" t="n">
         <v>81.0</v>
@@ -3187,7 +3187,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>363.0</v>
+        <v>366.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3256,7 +3256,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>581.0</v>
+        <v>584.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3440,7 +3440,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3463,7 +3463,7 @@
         <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>3336.0</v>
+        <v>3337.0</v>
       </c>
       <c r="F15" t="n">
         <v>2.0</v>
@@ -3486,13 +3486,13 @@
         <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>1532.0</v>
+        <v>1533.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
       </c>
       <c r="G16" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="17">
@@ -3532,7 +3532,7 @@
         <v>21</v>
       </c>
       <c r="E18" t="n">
-        <v>533.0</v>
+        <v>539.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -3578,7 +3578,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2881.0</v>
+        <v>2901.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3601,7 +3601,7 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>5020.0</v>
+        <v>5021.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="37">
   <si>
     <t>Area</t>
   </si>
@@ -1070,13 +1070,13 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G35" t="n">
         <v>2.0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1096,13 +1096,13 @@
         <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G36" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1113,22 +1113,22 @@
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F37" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G37" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H37" t="n">
         <v>0.0</v>
@@ -1148,13 +1148,13 @@
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F38" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1174,10 +1174,10 @@
         <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1197,19 +1197,19 @@
         <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F40" t="n">
-        <v>56.0</v>
+        <v>5.0</v>
       </c>
       <c r="G40" t="n">
-        <v>68.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
@@ -1226,13 +1226,13 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F41" t="n">
-        <v>44.0</v>
+        <v>56.0</v>
       </c>
       <c r="G41" t="n">
-        <v>33.0</v>
+        <v>68.0</v>
       </c>
       <c r="H41" t="n">
         <v>4.0</v>
@@ -1252,16 +1252,16 @@
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>113.0</v>
+        <v>44.0</v>
       </c>
       <c r="G42" t="n">
-        <v>6.0</v>
+        <v>33.0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="43">
@@ -1275,19 +1275,19 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F43" t="n">
-        <v>32.0</v>
+        <v>113.0</v>
       </c>
       <c r="G43" t="n">
-        <v>144.0</v>
+        <v>6.0</v>
       </c>
       <c r="H43" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
@@ -1304,16 +1304,16 @@
         <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F44" t="n">
-        <v>41.0</v>
+        <v>32.0</v>
       </c>
       <c r="G44" t="n">
-        <v>27.0</v>
+        <v>144.0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="45">
@@ -1330,16 +1330,16 @@
         <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F45" t="n">
-        <v>84.0</v>
+        <v>41.0</v>
       </c>
       <c r="G45" t="n">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="46">
@@ -1353,16 +1353,16 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0</v>
+        <v>84.0</v>
       </c>
       <c r="G46" t="n">
-        <v>29.0</v>
+        <v>3.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1382,13 +1382,13 @@
         <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F47" t="n">
         <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>7.0</v>
+        <v>31.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1405,16 +1405,16 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F48" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H48" t="n">
         <v>0.0</v>
@@ -1434,10 +1434,10 @@
         <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F49" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="G49" t="n">
         <v>0.0</v>
@@ -1460,10 +1460,10 @@
         <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F50" t="n">
-        <v>16.0</v>
+        <v>13.0</v>
       </c>
       <c r="G50" t="n">
         <v>0.0</v>
@@ -1480,22 +1480,22 @@
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E51" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F51" t="n">
-        <v>1352.0</v>
+        <v>16.0</v>
       </c>
       <c r="G51" t="n">
-        <v>696.0</v>
+        <v>0.0</v>
       </c>
       <c r="H51" t="n">
-        <v>92.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1512,16 +1512,16 @@
         <v>30</v>
       </c>
       <c r="E52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>240.0</v>
+        <v>1353.0</v>
       </c>
       <c r="G52" t="n">
-        <v>70.0</v>
+        <v>697.0</v>
       </c>
       <c r="H52" t="n">
-        <v>25.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="53">
@@ -1538,16 +1538,16 @@
         <v>30</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>258.0</v>
+        <v>240.0</v>
       </c>
       <c r="G53" t="n">
-        <v>16.0</v>
+        <v>70.0</v>
       </c>
       <c r="H53" t="n">
-        <v>8.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="54">
@@ -1561,19 +1561,19 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E54" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F54" t="n">
-        <v>77.0</v>
+        <v>259.0</v>
       </c>
       <c r="G54" t="n">
-        <v>9.0</v>
+        <v>16.0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="55">
@@ -1590,16 +1590,16 @@
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F55" t="n">
-        <v>136.0</v>
+        <v>77.0</v>
       </c>
       <c r="G55" t="n">
-        <v>31.0</v>
+        <v>9.0</v>
       </c>
       <c r="H55" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="56">
@@ -1616,16 +1616,16 @@
         <v>31</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>148.0</v>
+        <v>136.0</v>
       </c>
       <c r="G56" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="H56" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="57">
@@ -1639,16 +1639,16 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>146.0</v>
+        <v>148.0</v>
       </c>
       <c r="G57" t="n">
-        <v>96.0</v>
+        <v>1.0</v>
       </c>
       <c r="H57" t="n">
         <v>4.0</v>
@@ -1668,16 +1668,16 @@
         <v>22</v>
       </c>
       <c r="E58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F58" t="n">
-        <v>186.0</v>
+        <v>146.0</v>
       </c>
       <c r="G58" t="n">
-        <v>49.0</v>
+        <v>96.0</v>
       </c>
       <c r="H58" t="n">
-        <v>12.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="59">
@@ -1694,16 +1694,16 @@
         <v>22</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>110.0</v>
+        <v>186.0</v>
       </c>
       <c r="G59" t="n">
-        <v>2.0</v>
+        <v>49.0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="60">
@@ -1714,19 +1714,19 @@
         <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E60" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F60" t="n">
-        <v>42.0</v>
+        <v>110.0</v>
       </c>
       <c r="G60" t="n">
-        <v>97.0</v>
+        <v>2.0</v>
       </c>
       <c r="H60" t="n">
         <v>0.0</v>
@@ -1746,13 +1746,13 @@
         <v>23</v>
       </c>
       <c r="E61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F61" t="n">
-        <v>79.0</v>
+        <v>42.0</v>
       </c>
       <c r="G61" t="n">
-        <v>21.0</v>
+        <v>97.0</v>
       </c>
       <c r="H61" t="n">
         <v>0.0</v>
@@ -1772,13 +1772,13 @@
         <v>23</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F62" t="n">
-        <v>128.0</v>
+        <v>79.0</v>
       </c>
       <c r="G62" t="n">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="H62" t="n">
         <v>0.0</v>
@@ -1792,19 +1792,19 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F63" t="n">
-        <v>130.0</v>
+        <v>128.0</v>
       </c>
       <c r="G63" t="n">
-        <v>244.0</v>
+        <v>8.0</v>
       </c>
       <c r="H63" t="n">
         <v>0.0</v>
@@ -1824,16 +1824,16 @@
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F64" t="n">
-        <v>164.0</v>
+        <v>130.0</v>
       </c>
       <c r="G64" t="n">
-        <v>123.0</v>
+        <v>244.0</v>
       </c>
       <c r="H64" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1850,16 +1850,16 @@
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F65" t="n">
-        <v>240.0</v>
+        <v>164.0</v>
       </c>
       <c r="G65" t="n">
-        <v>16.0</v>
+        <v>123.0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="66">
@@ -1873,16 +1873,16 @@
         <v>15</v>
       </c>
       <c r="D66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F66" t="n">
-        <v>75.0</v>
+        <v>240.0</v>
       </c>
       <c r="G66" t="n">
-        <v>2.0</v>
+        <v>16.0</v>
       </c>
       <c r="H66" t="n">
         <v>0.0</v>
@@ -1902,13 +1902,13 @@
         <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F67" t="n">
-        <v>48.0</v>
+        <v>75.0</v>
       </c>
       <c r="G67" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1928,13 +1928,13 @@
         <v>25</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F68" t="n">
-        <v>41.0</v>
+        <v>48.0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1951,13 +1951,13 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E69" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F69" t="n">
-        <v>21.0</v>
+        <v>41.0</v>
       </c>
       <c r="G69" t="n">
         <v>0.0</v>
@@ -1980,16 +1980,16 @@
         <v>26</v>
       </c>
       <c r="E70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F70" t="n">
-        <v>32.0</v>
+        <v>21.0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -2006,16 +2006,16 @@
         <v>26</v>
       </c>
       <c r="E71" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F71" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H71" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="72">
@@ -2026,19 +2026,19 @@
         <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F72" t="n">
-        <v>47.0</v>
+        <v>30.0</v>
       </c>
       <c r="G72" t="n">
-        <v>132.0</v>
+        <v>0.0</v>
       </c>
       <c r="H72" t="n">
         <v>1.0</v>
@@ -2058,16 +2058,16 @@
         <v>27</v>
       </c>
       <c r="E73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F73" t="n">
-        <v>52.0</v>
+        <v>47.0</v>
       </c>
       <c r="G73" t="n">
-        <v>129.0</v>
+        <v>132.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
@@ -2084,13 +2084,13 @@
         <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F74" t="n">
-        <v>24.0</v>
+        <v>53.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>129.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2107,16 +2107,16 @@
         <v>16</v>
       </c>
       <c r="D75" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0</v>
+        <v>24.0</v>
       </c>
       <c r="G75" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2136,13 +2136,13 @@
         <v>32</v>
       </c>
       <c r="E76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F76" t="n">
         <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>36.0</v>
+        <v>19.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2159,16 +2159,16 @@
         <v>16</v>
       </c>
       <c r="D77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F77" t="n">
-        <v>24.0</v>
+        <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2188,16 +2188,16 @@
         <v>33</v>
       </c>
       <c r="E78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F78" t="n">
-        <v>135.0</v>
+        <v>24.0</v>
       </c>
       <c r="G78" t="n">
         <v>0.0</v>
       </c>
       <c r="H78" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -2214,16 +2214,16 @@
         <v>33</v>
       </c>
       <c r="E79" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n">
-        <v>36.0</v>
+        <v>136.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="80">
@@ -2231,22 +2231,22 @@
         <v>8</v>
       </c>
       <c r="B80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>1.0</v>
+        <v>36.0</v>
       </c>
       <c r="G80" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H80" t="n">
         <v>0.0</v>
@@ -2260,19 +2260,19 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E81" t="s">
         <v>34</v>
       </c>
       <c r="F81" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G81" t="n">
-        <v>61.0</v>
+        <v>12.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2292,13 +2292,13 @@
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F82" t="n">
-        <v>31.0</v>
+        <v>24.0</v>
       </c>
       <c r="G82" t="n">
-        <v>18.0</v>
+        <v>61.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2318,13 +2318,13 @@
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F83" t="n">
-        <v>46.0</v>
+        <v>31.0</v>
       </c>
       <c r="G83" t="n">
-        <v>3.0</v>
+        <v>18.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2341,16 +2341,16 @@
         <v>15</v>
       </c>
       <c r="D84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F84" t="n">
-        <v>4.0</v>
+        <v>46.0</v>
       </c>
       <c r="G84" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2370,16 +2370,16 @@
         <v>25</v>
       </c>
       <c r="E85" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F85" t="n">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="G85" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
@@ -2396,16 +2396,16 @@
         <v>25</v>
       </c>
       <c r="E86" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F86" t="n">
-        <v>10.0</v>
+        <v>19.0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="87">
@@ -2419,13 +2419,13 @@
         <v>15</v>
       </c>
       <c r="D87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F87" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2448,16 +2448,16 @@
         <v>26</v>
       </c>
       <c r="E88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F88" t="n">
-        <v>21.0</v>
+        <v>3.0</v>
       </c>
       <c r="G88" t="n">
         <v>0.0</v>
       </c>
       <c r="H88" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="89">
@@ -2474,15 +2474,41 @@
         <v>26</v>
       </c>
       <c r="E89" t="s">
+        <v>35</v>
+      </c>
+      <c r="F89" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>8</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>26</v>
+      </c>
+      <c r="E90" t="s">
         <v>36</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F90" t="n">
         <v>2.0</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H89" t="n">
+      <c r="G90" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H90" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2970,7 +2996,7 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -2999,7 +3025,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>192.0</v>
+        <v>194.0</v>
       </c>
     </row>
     <row r="23">
@@ -3555,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>8881.0</v>
+        <v>8884.0</v>
       </c>
       <c r="F19" t="n">
         <v>18.0</v>
@@ -3578,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2901.0</v>
+        <v>2906.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3647,7 +3673,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>5635.0</v>
+        <v>5636.0</v>
       </c>
       <c r="F23" t="n">
         <v>1.0</v>
@@ -3762,7 +3788,7 @@
         <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>3053.0</v>
+        <v>3054.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3785,7 +3811,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -3877,7 +3903,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>585.0</v>
+        <v>586.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2015,7 +2015,7 @@
         <v>1.0</v>
       </c>
       <c r="H71" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="72">
@@ -2168,7 +2168,7 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2766,13 +2766,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="F11" t="n">
-        <v>77.0</v>
+        <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>254.0</v>
+        <v>255.0</v>
       </c>
     </row>
     <row r="12">
@@ -2838,7 +2838,7 @@
         <v>16.0</v>
       </c>
       <c r="F14" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -3025,7 +3025,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>194.0</v>
+        <v>196.0</v>
       </c>
     </row>
     <row r="23">
@@ -3282,7 +3282,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>584.0</v>
+        <v>586.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3397,7 +3397,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>1171.0</v>
+        <v>1172.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3466,7 +3466,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3650,7 +3650,7 @@
         <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>3338.0</v>
+        <v>3342.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3673,7 +3673,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>5636.0</v>
+        <v>5639.0</v>
       </c>
       <c r="F23" t="n">
         <v>1.0</v>
@@ -3857,7 +3857,7 @@
         <v>24</v>
       </c>
       <c r="E31" t="n">
-        <v>2229.0</v>
+        <v>2232.0</v>
       </c>
       <c r="F31" t="n">
         <v>2.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -397,7 +397,7 @@
         <v>35</v>
       </c>
       <c r="F9" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G9" t="n">
         <v>0.0</v>
@@ -1645,7 +1645,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>148.0</v>
+        <v>149.0</v>
       </c>
       <c r="G57" t="n">
         <v>1.0</v>
@@ -1697,7 +1697,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
       <c r="G59" t="n">
         <v>49.0</v>
@@ -2559,7 +2559,7 @@
         <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -2700,7 +2700,7 @@
         <v>2.0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -2904,10 +2904,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>95.0</v>
+        <v>98.0</v>
       </c>
       <c r="F17" t="n">
-        <v>20.0</v>
+        <v>26.0</v>
       </c>
       <c r="G17" t="n">
         <v>81.0</v>
@@ -3604,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2906.0</v>
+        <v>2917.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3627,7 +3627,7 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>5021.0</v>
+        <v>5022.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3719,7 +3719,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3316.0</v>
+        <v>3324.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3903,7 +3903,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>586.0</v>
+        <v>587.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1388,7 +1388,7 @@
         <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1515,7 +1515,7 @@
         <v>34</v>
       </c>
       <c r="F52" t="n">
-        <v>1353.0</v>
+        <v>1354.0</v>
       </c>
       <c r="G52" t="n">
         <v>697.0</v>
@@ -1541,7 +1541,7 @@
         <v>35</v>
       </c>
       <c r="F53" t="n">
-        <v>240.0</v>
+        <v>242.0</v>
       </c>
       <c r="G53" t="n">
         <v>70.0</v>
@@ -1697,7 +1697,7 @@
         <v>35</v>
       </c>
       <c r="F59" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
       <c r="G59" t="n">
         <v>49.0</v>
@@ -2996,7 +2996,7 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>167.0</v>
+        <v>177.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3581,7 +3581,7 @@
         <v>30</v>
       </c>
       <c r="E19" t="n">
-        <v>8884.0</v>
+        <v>8904.0</v>
       </c>
       <c r="F19" t="n">
         <v>18.0</v>
@@ -3604,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2917.0</v>
+        <v>2918.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3627,7 +3627,7 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>5022.0</v>
+        <v>5027.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3650,7 +3650,7 @@
         <v>23</v>
       </c>
       <c r="E22" t="n">
-        <v>3342.0</v>
+        <v>3347.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -319,7 +319,7 @@
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -1284,7 +1284,7 @@
         <v>113.0</v>
       </c>
       <c r="G43" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1388,7 +1388,7 @@
         <v>0.0</v>
       </c>
       <c r="G47" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1518,7 +1518,7 @@
         <v>1354.0</v>
       </c>
       <c r="G52" t="n">
-        <v>697.0</v>
+        <v>698.0</v>
       </c>
       <c r="H52" t="n">
         <v>92.0</v>
@@ -1619,7 +1619,7 @@
         <v>35</v>
       </c>
       <c r="F56" t="n">
-        <v>136.0</v>
+        <v>138.0</v>
       </c>
       <c r="G56" t="n">
         <v>31.0</v>
@@ -1645,7 +1645,7 @@
         <v>36</v>
       </c>
       <c r="F57" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G57" t="n">
         <v>1.0</v>
@@ -2009,13 +2009,13 @@
         <v>35</v>
       </c>
       <c r="F71" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G71" t="n">
         <v>1.0</v>
       </c>
       <c r="H71" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="72">
@@ -2605,7 +2605,7 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -2766,13 +2766,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>151.0</v>
+        <v>156.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>255.0</v>
+        <v>256.0</v>
       </c>
     </row>
     <row r="12">
@@ -3489,7 +3489,7 @@
         <v>19</v>
       </c>
       <c r="E15" t="n">
-        <v>3337.0</v>
+        <v>3350.0</v>
       </c>
       <c r="F15" t="n">
         <v>2.0</v>
@@ -3587,7 +3587,7 @@
         <v>18.0</v>
       </c>
       <c r="G19" t="n">
-        <v>186.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="20">
@@ -3604,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2918.0</v>
+        <v>2931.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3673,7 +3673,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>5639.0</v>
+        <v>5642.0</v>
       </c>
       <c r="F23" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -319,10 +319,10 @@
         <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H6" t="n">
         <v>0.0</v>
@@ -995,7 +995,7 @@
         <v>34</v>
       </c>
       <c r="F32" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1021,7 +1021,7 @@
         <v>35</v>
       </c>
       <c r="F33" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1047,7 +1047,7 @@
         <v>36</v>
       </c>
       <c r="F34" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1333,7 +1333,7 @@
         <v>35</v>
       </c>
       <c r="F45" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G45" t="n">
         <v>27.0</v>
@@ -2090,7 +2090,7 @@
         <v>53.0</v>
       </c>
       <c r="G74" t="n">
-        <v>129.0</v>
+        <v>130.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2142,7 +2142,7 @@
         <v>0.0</v>
       </c>
       <c r="G76" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2168,7 +2168,7 @@
         <v>0.0</v>
       </c>
       <c r="G77" t="n">
-        <v>38.0</v>
+        <v>40.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2605,10 +2605,10 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -2766,7 +2766,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>156.0</v>
+        <v>161.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
@@ -2792,7 +2792,7 @@
         <v>40.0</v>
       </c>
       <c r="F12" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="G12" t="n">
         <v>16.0</v>
@@ -2887,7 +2887,7 @@
         <v>6.0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="17">
@@ -3002,7 +3002,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="22">
@@ -3025,7 +3025,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>196.0</v>
+        <v>201.0</v>
       </c>
     </row>
     <row r="23">
@@ -3042,7 +3042,7 @@
         <v>33</v>
       </c>
       <c r="E23" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3351,7 +3351,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1299.0</v>
+        <v>1301.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3397,7 +3397,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>1172.0</v>
+        <v>1175.0</v>
       </c>
       <c r="F11" t="n">
         <v>1.0</v>
@@ -3604,7 +3604,7 @@
         <v>31</v>
       </c>
       <c r="E20" t="n">
-        <v>2931.0</v>
+        <v>2938.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3627,7 +3627,7 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>5027.0</v>
+        <v>5028.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3673,7 +3673,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>5642.0</v>
+        <v>5643.0</v>
       </c>
       <c r="F23" t="n">
         <v>1.0</v>
@@ -3719,7 +3719,7 @@
         <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>3324.0</v>
+        <v>3325.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -3788,7 +3788,7 @@
         <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>3054.0</v>
+        <v>3060.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3903,7 +3903,7 @@
         <v>26</v>
       </c>
       <c r="E33" t="n">
-        <v>587.0</v>
+        <v>588.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="39">
   <si>
     <t>Area</t>
   </si>
@@ -100,7 +100,13 @@
     <t>Lucca</t>
   </si>
   <si>
+    <t>Pisa</t>
+  </si>
+  <si>
     <t>Pistoia</t>
+  </si>
+  <si>
+    <t>Prato</t>
   </si>
   <si>
     <t>Reggio emilia</t>
@@ -212,10 +218,10 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G2" t="n">
         <v>0.0</v>
@@ -238,10 +244,10 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -264,10 +270,10 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -290,10 +296,10 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -316,13 +322,13 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H6" t="n">
         <v>0.0</v>
@@ -342,10 +348,10 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -368,7 +374,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>5.0</v>
@@ -394,7 +400,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F9" t="n">
         <v>7.0</v>
@@ -420,7 +426,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F10" t="n">
         <v>27.0</v>
@@ -446,7 +452,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
         <v>10.0</v>
@@ -472,7 +478,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F12" t="n">
         <v>9.0</v>
@@ -498,7 +504,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
         <v>33.0</v>
@@ -524,7 +530,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F14" t="n">
         <v>8.0</v>
@@ -550,7 +556,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F15" t="n">
         <v>26.0</v>
@@ -576,7 +582,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F16" t="n">
         <v>79.0</v>
@@ -602,10 +608,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>19.0</v>
+        <v>11.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -628,16 +634,16 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
@@ -654,10 +660,10 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F19" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G19" t="n">
         <v>0.0</v>
@@ -680,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
         <v>14.0</v>
@@ -706,7 +712,7 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F21" t="n">
         <v>41.0</v>
@@ -732,7 +738,7 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F22" t="n">
         <v>47.0</v>
@@ -758,7 +764,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F23" t="n">
         <v>19.0</v>
@@ -784,7 +790,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F24" t="n">
         <v>15.0</v>
@@ -810,7 +816,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F25" t="n">
         <v>72.0</v>
@@ -836,7 +842,7 @@
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
         <v>54.0</v>
@@ -862,7 +868,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F27" t="n">
         <v>22.0</v>
@@ -888,7 +894,7 @@
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
         <v>20.0</v>
@@ -914,10 +920,10 @@
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F29" t="n">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -940,16 +946,16 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>35.0</v>
+        <v>27.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="31">
@@ -966,10 +972,10 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F31" t="n">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -992,10 +998,10 @@
         <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F32" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1018,10 +1024,10 @@
         <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>16.0</v>
+        <v>49.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1044,10 +1050,10 @@
         <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>30.0</v>
+        <v>76.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1070,13 +1076,13 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" t="n">
         <v>0.0</v>
@@ -1093,16 +1099,16 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F36" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H36" t="n">
         <v>0.0</v>
@@ -1119,13 +1125,13 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F37" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1139,22 +1145,22 @@
         <v>8</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F38" t="n">
-        <v>5.0</v>
+        <v>31.0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H38" t="n">
         <v>0.0</v>
@@ -1165,19 +1171,19 @@
         <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F39" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1191,19 +1197,19 @@
         <v>8</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F40" t="n">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1217,25 +1223,25 @@
         <v>8</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F41" t="n">
-        <v>56.0</v>
+        <v>15.0</v>
       </c>
       <c r="G41" t="n">
-        <v>68.0</v>
+        <v>0.0</v>
       </c>
       <c r="H41" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
@@ -1249,19 +1255,19 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F42" t="n">
-        <v>44.0</v>
+        <v>8.0</v>
       </c>
       <c r="G42" t="n">
-        <v>33.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
@@ -1275,16 +1281,16 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F43" t="n">
-        <v>113.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H43" t="n">
         <v>0.0</v>
@@ -1301,19 +1307,19 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F44" t="n">
-        <v>32.0</v>
+        <v>1.0</v>
       </c>
       <c r="G44" t="n">
-        <v>144.0</v>
+        <v>0.0</v>
       </c>
       <c r="H44" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
@@ -1327,19 +1333,19 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F45" t="n">
-        <v>42.0</v>
+        <v>8.0</v>
       </c>
       <c r="G45" t="n">
-        <v>27.0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1353,16 +1359,16 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F46" t="n">
-        <v>84.0</v>
+        <v>12.0</v>
       </c>
       <c r="G46" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -1379,16 +1385,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="G47" t="n">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1405,19 +1411,19 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0</v>
+        <v>56.0</v>
       </c>
       <c r="G48" t="n">
-        <v>7.0</v>
+        <v>69.0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="49">
@@ -1431,19 +1437,19 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F49" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="H49" t="n">
         <v>4.0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1457,16 +1463,16 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F50" t="n">
-        <v>13.0</v>
+        <v>113.0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1483,19 +1489,19 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E51" t="s">
         <v>36</v>
       </c>
       <c r="F51" t="n">
-        <v>16.0</v>
+        <v>32.0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0</v>
+        <v>144.0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="52">
@@ -1506,22 +1512,22 @@
         <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F52" t="n">
-        <v>1354.0</v>
+        <v>42.0</v>
       </c>
       <c r="G52" t="n">
-        <v>698.0</v>
+        <v>27.0</v>
       </c>
       <c r="H52" t="n">
-        <v>92.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="53">
@@ -1532,22 +1538,22 @@
         <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F53" t="n">
-        <v>242.0</v>
+        <v>84.0</v>
       </c>
       <c r="G53" t="n">
-        <v>70.0</v>
+        <v>3.0</v>
       </c>
       <c r="H53" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -1558,22 +1564,22 @@
         <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E54" t="s">
         <v>36</v>
       </c>
       <c r="F54" t="n">
-        <v>259.0</v>
+        <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>16.0</v>
+        <v>34.0</v>
       </c>
       <c r="H54" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1584,22 +1590,22 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
         <v>31</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F55" t="n">
-        <v>77.0</v>
+        <v>0.0</v>
       </c>
       <c r="G55" t="n">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -1610,22 +1616,22 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>138.0</v>
+        <v>4.0</v>
       </c>
       <c r="G56" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="H56" t="n">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -1636,22 +1642,22 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>150.0</v>
+        <v>13.0</v>
       </c>
       <c r="G57" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1662,22 +1668,22 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F58" t="n">
-        <v>146.0</v>
+        <v>16.0</v>
       </c>
       <c r="G58" t="n">
-        <v>96.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1691,19 +1697,19 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>188.0</v>
+        <v>1359.0</v>
       </c>
       <c r="G59" t="n">
-        <v>49.0</v>
+        <v>698.0</v>
       </c>
       <c r="H59" t="n">
-        <v>12.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="60">
@@ -1717,19 +1723,19 @@
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>110.0</v>
+        <v>242.0</v>
       </c>
       <c r="G60" t="n">
-        <v>2.0</v>
+        <v>70.0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="61">
@@ -1740,22 +1746,22 @@
         <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E61" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>42.0</v>
+        <v>260.0</v>
       </c>
       <c r="G61" t="n">
-        <v>97.0</v>
+        <v>16.0</v>
       </c>
       <c r="H61" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="62">
@@ -1766,22 +1772,22 @@
         <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>79.0</v>
+        <v>77.0</v>
       </c>
       <c r="G62" t="n">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="63">
@@ -1792,22 +1798,22 @@
         <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E63" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>128.0</v>
+        <v>138.0</v>
       </c>
       <c r="G63" t="n">
-        <v>8.0</v>
+        <v>31.0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="64">
@@ -1818,22 +1824,22 @@
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E64" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>130.0</v>
+        <v>150.0</v>
       </c>
       <c r="G64" t="n">
-        <v>244.0</v>
+        <v>1.0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="65">
@@ -1844,22 +1850,22 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>164.0</v>
+        <v>154.0</v>
       </c>
       <c r="G65" t="n">
-        <v>123.0</v>
+        <v>96.0</v>
       </c>
       <c r="H65" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="66">
@@ -1870,22 +1876,22 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>240.0</v>
+        <v>191.0</v>
       </c>
       <c r="G66" t="n">
-        <v>16.0</v>
+        <v>49.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="67">
@@ -1896,16 +1902,16 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F67" t="n">
-        <v>75.0</v>
+        <v>111.0</v>
       </c>
       <c r="G67" t="n">
         <v>2.0</v>
@@ -1922,19 +1928,19 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>48.0</v>
+        <v>42.0</v>
       </c>
       <c r="G68" t="n">
-        <v>5.0</v>
+        <v>97.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1948,19 +1954,19 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F69" t="n">
-        <v>41.0</v>
+        <v>79.0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="H69" t="n">
         <v>0.0</v>
@@ -1974,19 +1980,19 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>21.0</v>
+        <v>128.0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2003,19 +2009,19 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>33.0</v>
+        <v>130.0</v>
       </c>
       <c r="G71" t="n">
-        <v>1.0</v>
+        <v>244.0</v>
       </c>
       <c r="H71" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2029,19 +2035,19 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F72" t="n">
-        <v>30.0</v>
+        <v>164.0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0</v>
+        <v>123.0</v>
       </c>
       <c r="H72" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="73">
@@ -2052,22 +2058,22 @@
         <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F73" t="n">
-        <v>47.0</v>
+        <v>240.0</v>
       </c>
       <c r="G73" t="n">
-        <v>132.0</v>
+        <v>16.0</v>
       </c>
       <c r="H73" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -2078,19 +2084,19 @@
         <v>10</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>53.0</v>
+        <v>75.0</v>
       </c>
       <c r="G74" t="n">
-        <v>130.0</v>
+        <v>2.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2104,19 +2110,19 @@
         <v>10</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F75" t="n">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="H75" t="n">
         <v>0.0</v>
@@ -2130,19 +2136,19 @@
         <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
       <c r="G76" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="H76" t="n">
         <v>0.0</v>
@@ -2156,19 +2162,19 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F77" t="n">
-        <v>0.0</v>
+        <v>36.0</v>
       </c>
       <c r="G77" t="n">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -2182,22 +2188,22 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F78" t="n">
-        <v>24.0</v>
+        <v>55.0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="79">
@@ -2208,22 +2214,22 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F79" t="n">
-        <v>136.0</v>
+        <v>63.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
       </c>
       <c r="H79" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
@@ -2237,19 +2243,19 @@
         <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E80" t="s">
         <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>36.0</v>
+        <v>53.0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.0</v>
+        <v>132.0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -2257,22 +2263,22 @@
         <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E81" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F81" t="n">
-        <v>1.0</v>
+        <v>57.0</v>
       </c>
       <c r="G81" t="n">
-        <v>12.0</v>
+        <v>130.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2283,22 +2289,22 @@
         <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E82" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F82" t="n">
-        <v>24.0</v>
+        <v>41.0</v>
       </c>
       <c r="G82" t="n">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
       <c r="H82" t="n">
         <v>0.0</v>
@@ -2309,22 +2315,22 @@
         <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E83" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F83" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="H83" t="n">
         <v>0.0</v>
@@ -2335,22 +2341,22 @@
         <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D84" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F84" t="n">
-        <v>46.0</v>
+        <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>3.0</v>
+        <v>40.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2361,22 +2367,22 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D85" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F85" t="n">
-        <v>4.0</v>
+        <v>24.0</v>
       </c>
       <c r="G85" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H85" t="n">
         <v>0.0</v>
@@ -2387,25 +2393,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D86" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E86" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F86" t="n">
-        <v>19.0</v>
+        <v>136.0</v>
       </c>
       <c r="G86" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="87">
@@ -2413,19 +2419,19 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D87" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E87" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F87" t="n">
-        <v>10.0</v>
+        <v>36.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2439,22 +2445,22 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F88" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2465,25 +2471,25 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F89" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="90">
@@ -2491,24 +2497,284 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" t="s">
+        <v>38</v>
+      </c>
+      <c r="F90" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>8</v>
+      </c>
+      <c r="B91" t="s">
         <v>11</v>
       </c>
-      <c r="C90" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>22</v>
+      </c>
+      <c r="E91" t="s">
+        <v>36</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" t="s">
+        <v>36</v>
+      </c>
+      <c r="F92" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" t="s">
+        <v>37</v>
+      </c>
+      <c r="F93" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" t="s">
+        <v>38</v>
+      </c>
+      <c r="F94" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>36</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" t="s">
+        <v>38</v>
+      </c>
+      <c r="F97" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
         <v>26</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E98" t="s">
         <v>36</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F98" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" t="s">
+        <v>26</v>
+      </c>
+      <c r="E99" t="s">
+        <v>37</v>
+      </c>
+      <c r="F99" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H99" t="n">
         <v>2.0</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H90" t="n">
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" t="s">
+        <v>26</v>
+      </c>
+      <c r="E100" t="s">
+        <v>38</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H100" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -2605,10 +2871,10 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -2628,10 +2894,10 @@
         <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G5" t="n">
         <v>4.0</v>
@@ -2697,10 +2963,10 @@
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F8" t="n">
-        <v>8.0</v>
+        <v>1.0</v>
       </c>
       <c r="G8" t="n">
         <v>0.0</v>
@@ -2772,7 +3038,7 @@
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>256.0</v>
+        <v>257.0</v>
       </c>
     </row>
     <row r="12">
@@ -2809,7 +3075,7 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
         <v>0.0</v>
@@ -2855,7 +3121,7 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
         <v>14.0</v>
@@ -2878,7 +3144,7 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
         <v>17.0</v>
@@ -2904,10 +3170,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>98.0</v>
+        <v>108.0</v>
       </c>
       <c r="F17" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
       <c r="G17" t="n">
         <v>81.0</v>
@@ -2973,10 +3239,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>33.0</v>
+        <v>44.0</v>
       </c>
       <c r="F20" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -2996,13 +3262,13 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>177.0</v>
+        <v>178.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="22">
@@ -3016,7 +3282,7 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E22" t="n">
         <v>0.0</v>
@@ -3039,7 +3305,7 @@
         <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E23" t="n">
         <v>165.0</v>
@@ -3190,7 +3456,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>39.0</v>
+        <v>78.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3213,7 +3479,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>366.0</v>
+        <v>389.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3305,7 +3571,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>2087.0</v>
+        <v>1202.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3374,7 +3640,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1746.0</v>
+        <v>1747.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3397,10 +3663,10 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>1175.0</v>
+        <v>431.0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -3420,7 +3686,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>284.0</v>
+        <v>588.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3440,10 +3706,10 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>139.0</v>
+        <v>383.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3457,16 +3723,16 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>275.0</v>
+        <v>57.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3486,16 +3752,16 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>3350.0</v>
+        <v>98.0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G15" t="n">
-        <v>38.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -3509,16 +3775,16 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>1533.0</v>
+        <v>316.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
       </c>
       <c r="G16" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -3532,16 +3798,16 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0</v>
+        <v>3350.0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="18">
@@ -3555,16 +3821,16 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>539.0</v>
+        <v>1533.0</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="19">
@@ -3575,19 +3841,19 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>8904.0</v>
+        <v>0.0</v>
       </c>
       <c r="F19" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>187.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="20">
@@ -3598,19 +3864,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>2938.0</v>
+        <v>539.0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G20" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -3624,16 +3890,16 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>5028.0</v>
+        <v>8909.0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="G21" t="n">
-        <v>5.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="22">
@@ -3644,19 +3910,19 @@
         <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>3347.0</v>
+        <v>2946.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>82.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="23">
@@ -3667,19 +3933,19 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>5643.0</v>
+        <v>5976.0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>164.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="24">
@@ -3690,19 +3956,19 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>1581.0</v>
+        <v>3347.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>12.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="25">
@@ -3716,16 +3982,16 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>3325.0</v>
+        <v>5643.0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="26">
@@ -3736,19 +4002,19 @@
         <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>416.0</v>
+        <v>1581.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="27">
@@ -3759,19 +4025,19 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0</v>
+        <v>4361.0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" t="n">
-        <v>47.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -3785,16 +4051,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>3060.0</v>
+        <v>745.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="29">
@@ -3808,16 +4074,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="30">
@@ -3825,16 +4091,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>14.0</v>
+        <v>3060.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -3848,22 +4114,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>2232.0</v>
+        <v>1008.0</v>
       </c>
       <c r="F31" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -3874,19 +4140,19 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E32" t="n">
-        <v>1691.0</v>
+        <v>14.0</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -3900,15 +4166,61 @@
         <v>15</v>
       </c>
       <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2232.0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1691.0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
         <v>26</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E35" t="n">
         <v>588.0</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G33" t="n">
+      <c r="F35" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G35" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2356,7 +2356,7 @@
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -3291,7 +3291,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
     </row>
     <row r="23">
@@ -3686,7 +3686,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>588.0</v>
+        <v>589.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3709,7 +3709,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>383.0</v>
+        <v>388.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3968,7 +3968,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="25">
@@ -4083,7 +4083,7 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="30">
@@ -4123,7 +4123,7 @@
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>1008.0</v>
+        <v>1010.0</v>
       </c>
       <c r="F31" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1342,7 +1342,7 @@
         <v>8.0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H45" t="n">
         <v>0.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G60" t="n">
         <v>70.0</v>
@@ -1807,7 +1807,7 @@
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -3032,7 +3032,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>161.0</v>
+        <v>165.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
@@ -3055,7 +3055,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>40.0</v>
+        <v>42.0</v>
       </c>
       <c r="F12" t="n">
         <v>46.0</v>
@@ -3170,7 +3170,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="F17" t="n">
         <v>24.0</v>
@@ -3239,7 +3239,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="F20" t="n">
         <v>30.0</v>
@@ -3456,7 +3456,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>78.0</v>
+        <v>103.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3479,7 +3479,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>389.0</v>
+        <v>391.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3548,7 +3548,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>586.0</v>
+        <v>590.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3755,7 +3755,7 @@
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>98.0</v>
+        <v>104.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3778,7 +3778,7 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>316.0</v>
+        <v>317.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -3801,7 +3801,7 @@
         <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>3350.0</v>
+        <v>3356.0</v>
       </c>
       <c r="F17" t="n">
         <v>2.0</v>
@@ -3824,7 +3824,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>1533.0</v>
+        <v>1534.0</v>
       </c>
       <c r="F18" t="n">
         <v>0.0</v>
@@ -3870,7 +3870,7 @@
         <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>539.0</v>
+        <v>553.0</v>
       </c>
       <c r="F20" t="n">
         <v>2.0</v>
@@ -3893,7 +3893,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>8909.0</v>
+        <v>8916.0</v>
       </c>
       <c r="F21" t="n">
         <v>18.0</v>
@@ -3916,7 +3916,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>2946.0</v>
+        <v>2949.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4215,7 +4215,7 @@
         <v>26</v>
       </c>
       <c r="E35" t="n">
-        <v>588.0</v>
+        <v>589.0</v>
       </c>
       <c r="F35" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -637,7 +637,7 @@
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>1359.0</v>
+        <v>1360.0</v>
       </c>
       <c r="G59" t="n">
         <v>698.0</v>
@@ -1885,7 +1885,7 @@
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>191.0</v>
+        <v>192.0</v>
       </c>
       <c r="G66" t="n">
         <v>49.0</v>
@@ -2119,7 +2119,7 @@
         <v>37</v>
       </c>
       <c r="F75" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G75" t="n">
         <v>5.0</v>
@@ -2917,7 +2917,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3038,7 +3038,7 @@
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>257.0</v>
+        <v>258.0</v>
       </c>
     </row>
     <row r="12">
@@ -3061,7 +3061,7 @@
         <v>46.0</v>
       </c>
       <c r="G12" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="13">
@@ -3239,7 +3239,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>46.0</v>
+        <v>48.0</v>
       </c>
       <c r="F20" t="n">
         <v>30.0</v>
@@ -3893,7 +3893,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>8916.0</v>
+        <v>8922.0</v>
       </c>
       <c r="F21" t="n">
         <v>18.0</v>
@@ -3916,7 +3916,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>2949.0</v>
+        <v>2950.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3939,7 +3939,7 @@
         <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>5976.0</v>
+        <v>5982.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3962,7 +3962,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>3347.0</v>
+        <v>3352.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="39">
   <si>
     <t>Area</t>
   </si>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>150.0</v>
+        <v>152.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -2405,7 +2405,7 @@
         <v>37</v>
       </c>
       <c r="F86" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2483,10 +2483,10 @@
         <v>37</v>
       </c>
       <c r="F89" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -3032,7 +3032,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>165.0</v>
+        <v>167.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
@@ -3170,7 +3170,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="F17" t="n">
         <v>24.0</v>
@@ -3239,10 +3239,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>48.0</v>
+        <v>55.0</v>
       </c>
       <c r="F20" t="n">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -3262,7 +3262,7 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>178.0</v>
+        <v>179.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3322,22 +3322,22 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G24" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -3348,19 +3348,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3374,16 +3374,16 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="F26" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="27">
@@ -3397,15 +3397,38 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" t="s">
         <v>26</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F27" t="n">
+      <c r="E28" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F28" t="n">
         <v>2.0</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G28" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3456,7 +3479,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3479,7 +3502,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>391.0</v>
+        <v>392.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3663,7 +3686,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3686,7 +3709,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>589.0</v>
+        <v>591.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3709,7 +3732,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>388.0</v>
+        <v>391.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3732,7 +3755,7 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3870,7 +3893,7 @@
         <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>553.0</v>
+        <v>556.0</v>
       </c>
       <c r="F20" t="n">
         <v>2.0</v>
@@ -3916,7 +3939,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>2950.0</v>
+        <v>2956.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4031,7 +4054,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>4361.0</v>
+        <v>4363.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4054,7 +4077,7 @@
         <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>745.0</v>
+        <v>747.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -4123,7 +4146,7 @@
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>1010.0</v>
+        <v>1011.0</v>
       </c>
       <c r="F31" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -871,7 +871,7 @@
         <v>37</v>
       </c>
       <c r="F27" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>1360.0</v>
+        <v>1361.0</v>
       </c>
       <c r="G59" t="n">
         <v>698.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="G61" t="n">
         <v>16.0</v>
@@ -1888,7 +1888,7 @@
         <v>192.0</v>
       </c>
       <c r="G66" t="n">
-        <v>49.0</v>
+        <v>53.0</v>
       </c>
       <c r="H66" t="n">
         <v>13.0</v>
@@ -2119,7 +2119,7 @@
         <v>37</v>
       </c>
       <c r="F75" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G75" t="n">
         <v>5.0</v>
@@ -2197,7 +2197,7 @@
         <v>37</v>
       </c>
       <c r="F78" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -3101,7 +3101,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="F14" t="n">
         <v>16.0</v>
@@ -3153,7 +3153,7 @@
         <v>6.0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="17">
@@ -3176,7 +3176,7 @@
         <v>24.0</v>
       </c>
       <c r="G17" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
     </row>
     <row r="18">
@@ -3239,10 +3239,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>55.0</v>
+        <v>63.0</v>
       </c>
       <c r="F20" t="n">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -3663,7 +3663,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1747.0</v>
+        <v>1751.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3755,7 +3755,7 @@
         <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3916,7 +3916,7 @@
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>8922.0</v>
+        <v>8925.0</v>
       </c>
       <c r="F21" t="n">
         <v>18.0</v>
@@ -4054,7 +4054,7 @@
         <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>4363.0</v>
+        <v>4369.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4146,7 +4146,7 @@
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>1011.0</v>
+        <v>1022.0</v>
       </c>
       <c r="F31" t="n">
         <v>1.0</v>
@@ -4238,7 +4238,7 @@
         <v>26</v>
       </c>
       <c r="E35" t="n">
-        <v>589.0</v>
+        <v>590.0</v>
       </c>
       <c r="F35" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -1027,7 +1027,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1576,7 +1576,7 @@
         <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1859,7 +1859,7 @@
         <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>154.0</v>
+        <v>155.0</v>
       </c>
       <c r="G65" t="n">
         <v>96.0</v>
@@ -1911,7 +1911,7 @@
         <v>38</v>
       </c>
       <c r="F67" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G67" t="n">
         <v>2.0</v>
@@ -3291,7 +3291,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>202.0</v>
+        <v>207.0</v>
       </c>
     </row>
     <row r="23">
@@ -3308,7 +3308,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>165.0</v>
+        <v>172.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3663,7 +3663,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1751.0</v>
+        <v>1752.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3939,7 +3939,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>2956.0</v>
+        <v>2958.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -3962,7 +3962,7 @@
         <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>5982.0</v>
+        <v>5988.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3985,7 +3985,7 @@
         <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>3352.0</v>
+        <v>3356.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -3709,7 +3709,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>591.0</v>
+        <v>593.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -3732,7 +3732,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>391.0</v>
+        <v>396.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4146,7 +4146,7 @@
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>1022.0</v>
+        <v>1023.0</v>
       </c>
       <c r="F31" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="39">
   <si>
     <t>Area</t>
   </si>
@@ -1255,16 +1255,16 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E42" t="s">
         <v>36</v>
       </c>
       <c r="F42" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1281,13 +1281,13 @@
         <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43" t="s">
         <v>37</v>
       </c>
       <c r="F43" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1307,13 +1307,13 @@
         <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
         <v>38</v>
       </c>
       <c r="F44" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1333,19 +1333,19 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" t="s">
         <v>36</v>
       </c>
       <c r="F45" t="n">
-        <v>8.0</v>
+        <v>55.0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.0</v>
+        <v>69.0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="46">
@@ -1359,19 +1359,19 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
         <v>37</v>
       </c>
       <c r="F46" t="n">
-        <v>12.0</v>
+        <v>43.0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.0</v>
+        <v>33.0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="47">
@@ -1385,16 +1385,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" t="s">
         <v>38</v>
       </c>
       <c r="F47" t="n">
-        <v>6.0</v>
+        <v>114.0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1411,16 +1411,16 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
         <v>36</v>
       </c>
       <c r="F48" t="n">
-        <v>56.0</v>
+        <v>32.0</v>
       </c>
       <c r="G48" t="n">
-        <v>69.0</v>
+        <v>144.0</v>
       </c>
       <c r="H48" t="n">
         <v>4.0</v>
@@ -1437,19 +1437,19 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E49" t="s">
         <v>37</v>
       </c>
       <c r="F49" t="n">
-        <v>44.0</v>
+        <v>42.0</v>
       </c>
       <c r="G49" t="n">
-        <v>33.0</v>
+        <v>27.0</v>
       </c>
       <c r="H49" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="50">
@@ -1463,16 +1463,16 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
         <v>38</v>
       </c>
       <c r="F50" t="n">
-        <v>113.0</v>
+        <v>84.0</v>
       </c>
       <c r="G50" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1489,19 +1489,19 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E51" t="s">
         <v>36</v>
       </c>
       <c r="F51" t="n">
-        <v>32.0</v>
+        <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>144.0</v>
+        <v>35.0</v>
       </c>
       <c r="H51" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1515,19 +1515,19 @@
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
         <v>37</v>
       </c>
       <c r="F52" t="n">
-        <v>42.0</v>
+        <v>0.0</v>
       </c>
       <c r="G52" t="n">
-        <v>27.0</v>
+        <v>7.0</v>
       </c>
       <c r="H52" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -1541,16 +1541,16 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F53" t="n">
-        <v>84.0</v>
+        <v>4.0</v>
       </c>
       <c r="G53" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1567,16 +1567,16 @@
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
       <c r="G54" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1593,16 +1593,16 @@
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="G55" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1616,22 +1616,22 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E56" t="s">
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>4.0</v>
+        <v>1361.0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0</v>
+        <v>698.0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="57">
@@ -1642,22 +1642,22 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E57" t="s">
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>13.0</v>
+        <v>243.0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0</v>
+        <v>70.0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="58">
@@ -1668,22 +1668,22 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E58" t="s">
         <v>38</v>
       </c>
       <c r="F58" t="n">
+        <v>261.0</v>
+      </c>
+      <c r="G58" t="n">
         <v>16.0</v>
       </c>
-      <c r="G58" t="n">
-        <v>0.0</v>
-      </c>
       <c r="H58" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="59">
@@ -1697,19 +1697,19 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E59" t="s">
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>1361.0</v>
+        <v>77.0</v>
       </c>
       <c r="G59" t="n">
-        <v>698.0</v>
+        <v>9.0</v>
       </c>
       <c r="H59" t="n">
-        <v>92.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="60">
@@ -1723,19 +1723,19 @@
         <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E60" t="s">
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>243.0</v>
+        <v>139.0</v>
       </c>
       <c r="G60" t="n">
-        <v>70.0</v>
+        <v>31.0</v>
       </c>
       <c r="H60" t="n">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="61">
@@ -1749,19 +1749,19 @@
         <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E61" t="s">
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>261.0</v>
+        <v>152.0</v>
       </c>
       <c r="G61" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="H61" t="n">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="62">
@@ -1775,19 +1775,19 @@
         <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E62" t="s">
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>77.0</v>
+        <v>155.0</v>
       </c>
       <c r="G62" t="n">
-        <v>9.0</v>
+        <v>96.0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="63">
@@ -1801,19 +1801,19 @@
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E63" t="s">
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>139.0</v>
+        <v>192.0</v>
       </c>
       <c r="G63" t="n">
-        <v>31.0</v>
+        <v>53.0</v>
       </c>
       <c r="H63" t="n">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="64">
@@ -1827,19 +1827,19 @@
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E64" t="s">
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>152.0</v>
+        <v>112.0</v>
       </c>
       <c r="G64" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H64" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1850,22 +1850,22 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E65" t="s">
         <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>155.0</v>
+        <v>42.0</v>
       </c>
       <c r="G65" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
       <c r="H65" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1876,22 +1876,22 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E66" t="s">
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>192.0</v>
+        <v>79.0</v>
       </c>
       <c r="G66" t="n">
-        <v>53.0</v>
+        <v>21.0</v>
       </c>
       <c r="H66" t="n">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1902,19 +1902,19 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E67" t="s">
         <v>38</v>
       </c>
       <c r="F67" t="n">
-        <v>112.0</v>
+        <v>128.0</v>
       </c>
       <c r="G67" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="H67" t="n">
         <v>0.0</v>
@@ -1928,19 +1928,19 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E68" t="s">
         <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>42.0</v>
+        <v>130.0</v>
       </c>
       <c r="G68" t="n">
-        <v>97.0</v>
+        <v>244.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1954,22 +1954,22 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69" t="s">
         <v>37</v>
       </c>
       <c r="F69" t="n">
-        <v>79.0</v>
+        <v>164.0</v>
       </c>
       <c r="G69" t="n">
-        <v>21.0</v>
+        <v>123.0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="70">
@@ -1980,19 +1980,19 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E70" t="s">
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>128.0</v>
+        <v>240.0</v>
       </c>
       <c r="G70" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2009,16 +2009,16 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
         <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>130.0</v>
+        <v>75.0</v>
       </c>
       <c r="G71" t="n">
-        <v>244.0</v>
+        <v>2.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2035,19 +2035,19 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
         <v>37</v>
       </c>
       <c r="F72" t="n">
-        <v>164.0</v>
+        <v>50.0</v>
       </c>
       <c r="G72" t="n">
-        <v>123.0</v>
+        <v>5.0</v>
       </c>
       <c r="H72" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -2061,16 +2061,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E73" t="s">
         <v>38</v>
       </c>
       <c r="F73" t="n">
-        <v>240.0</v>
+        <v>41.0</v>
       </c>
       <c r="G73" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2087,16 +2087,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E74" t="s">
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>75.0</v>
+        <v>36.0</v>
       </c>
       <c r="G74" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2113,19 +2113,19 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E75" t="s">
         <v>37</v>
       </c>
       <c r="F75" t="n">
-        <v>50.0</v>
+        <v>56.0</v>
       </c>
       <c r="G75" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="76">
@@ -2139,19 +2139,19 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E76" t="s">
         <v>38</v>
       </c>
       <c r="F76" t="n">
-        <v>41.0</v>
+        <v>63.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="77">
@@ -2162,22 +2162,22 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D77" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E77" t="s">
         <v>36</v>
       </c>
       <c r="F77" t="n">
-        <v>36.0</v>
+        <v>52.0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0</v>
+        <v>132.0</v>
       </c>
       <c r="H77" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="78">
@@ -2188,10 +2188,10 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D78" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E78" t="s">
         <v>37</v>
@@ -2200,10 +2200,10 @@
         <v>56.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>130.0</v>
       </c>
       <c r="H78" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -2214,22 +2214,22 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E79" t="s">
         <v>38</v>
       </c>
       <c r="F79" t="n">
-        <v>63.0</v>
+        <v>37.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2243,19 +2243,19 @@
         <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E80" t="s">
         <v>36</v>
       </c>
       <c r="F80" t="n">
-        <v>53.0</v>
+        <v>0.0</v>
       </c>
       <c r="G80" t="n">
-        <v>132.0</v>
+        <v>15.0</v>
       </c>
       <c r="H80" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -2269,16 +2269,16 @@
         <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E81" t="s">
         <v>37</v>
       </c>
       <c r="F81" t="n">
-        <v>57.0</v>
+        <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>130.0</v>
+        <v>26.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2295,13 +2295,13 @@
         <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F82" t="n">
-        <v>41.0</v>
+        <v>8.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2321,19 +2321,19 @@
         <v>16</v>
       </c>
       <c r="D83" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="G83" t="n">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="H83" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="84">
@@ -2347,16 +2347,16 @@
         <v>16</v>
       </c>
       <c r="D84" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="G84" t="n">
-        <v>42.0</v>
+        <v>0.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2367,19 +2367,19 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E85" t="s">
         <v>36</v>
       </c>
       <c r="F85" t="n">
-        <v>24.0</v>
+        <v>8.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2393,25 +2393,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E86" t="s">
         <v>37</v>
       </c>
       <c r="F86" t="n">
-        <v>137.0</v>
+        <v>3.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2419,19 +2419,19 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D87" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E87" t="s">
         <v>38</v>
       </c>
       <c r="F87" t="n">
-        <v>36.0</v>
+        <v>1.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2445,22 +2445,22 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D88" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E88" t="s">
         <v>36</v>
       </c>
       <c r="F88" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G88" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2471,22 +2471,22 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E89" t="s">
         <v>37</v>
       </c>
       <c r="F89" t="n">
-        <v>23.0</v>
+        <v>2.0</v>
       </c>
       <c r="G89" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2497,19 +2497,19 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E90" t="s">
         <v>38</v>
       </c>
       <c r="F90" t="n">
-        <v>33.0</v>
+        <v>1.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2526,10 +2526,10 @@
         <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E91" t="s">
         <v>36</v>
@@ -2538,7 +2538,7 @@
         <v>1.0</v>
       </c>
       <c r="G91" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H91" t="n">
         <v>0.0</v>
@@ -2552,19 +2552,19 @@
         <v>11</v>
       </c>
       <c r="C92" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E92" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F92" t="n">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="G92" t="n">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
       <c r="H92" t="n">
         <v>0.0</v>
@@ -2578,19 +2578,19 @@
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E93" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F93" t="n">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" t="n">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2610,13 +2610,13 @@
         <v>24</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F94" t="n">
-        <v>46.0</v>
+        <v>24.0</v>
       </c>
       <c r="G94" t="n">
-        <v>3.0</v>
+        <v>61.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2633,16 +2633,16 @@
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F95" t="n">
-        <v>4.0</v>
+        <v>31.0</v>
       </c>
       <c r="G95" t="n">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2659,19 +2659,19 @@
         <v>15</v>
       </c>
       <c r="D96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E96" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F96" t="n">
-        <v>19.0</v>
+        <v>46.0</v>
       </c>
       <c r="G96" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H96" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="97">
@@ -2688,13 +2688,13 @@
         <v>25</v>
       </c>
       <c r="E97" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F97" t="n">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2711,19 +2711,19 @@
         <v>15</v>
       </c>
       <c r="D98" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F98" t="n">
-        <v>3.0</v>
+        <v>19.0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="99">
@@ -2737,19 +2737,19 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F99" t="n">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
       </c>
       <c r="H99" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="100">
@@ -2766,15 +2766,353 @@
         <v>26</v>
       </c>
       <c r="E100" t="s">
+        <v>36</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" t="s">
+        <v>26</v>
+      </c>
+      <c r="E102" t="s">
         <v>38</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F102" t="n">
         <v>2.0</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H100" t="n">
+      <c r="G102" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" t="s">
+        <v>27</v>
+      </c>
+      <c r="E103" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>16</v>
+      </c>
+      <c r="D104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104" t="s">
+        <v>37</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" t="s">
+        <v>27</v>
+      </c>
+      <c r="E105" t="s">
+        <v>38</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>16</v>
+      </c>
+      <c r="D106" t="s">
+        <v>34</v>
+      </c>
+      <c r="E106" t="s">
+        <v>36</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>16</v>
+      </c>
+      <c r="D107" t="s">
+        <v>34</v>
+      </c>
+      <c r="E107" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" t="s">
+        <v>35</v>
+      </c>
+      <c r="E108" t="s">
+        <v>36</v>
+      </c>
+      <c r="F108" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109" t="s">
+        <v>37</v>
+      </c>
+      <c r="F109" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" t="s">
+        <v>35</v>
+      </c>
+      <c r="E110" t="s">
+        <v>38</v>
+      </c>
+      <c r="F110" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>16</v>
+      </c>
+      <c r="D111" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" t="s">
+        <v>36</v>
+      </c>
+      <c r="F111" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>8</v>
+      </c>
+      <c r="B112" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" t="s">
+        <v>29</v>
+      </c>
+      <c r="E112" t="s">
+        <v>37</v>
+      </c>
+      <c r="F112" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>8</v>
+      </c>
+      <c r="B113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" t="s">
+        <v>16</v>
+      </c>
+      <c r="D113" t="s">
+        <v>29</v>
+      </c>
+      <c r="E113" t="s">
+        <v>38</v>
+      </c>
+      <c r="F113" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H113" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3032,7 +3370,7 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
@@ -3239,10 +3577,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="F20" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -3291,7 +3629,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>207.0</v>
+        <v>111.0</v>
       </c>
     </row>
     <row r="23">
@@ -3308,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>172.0</v>
+        <v>107.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3322,22 +3660,22 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -3348,19 +3686,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="26">
@@ -3374,16 +3712,16 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
       <c r="F26" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="G26" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="27">
@@ -3397,16 +3735,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -3417,19 +3755,65 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
         <v>0.0</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>96.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>
@@ -3571,7 +3955,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>590.0</v>
+        <v>592.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3663,7 +4047,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1752.0</v>
+        <v>1755.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3775,10 +4159,10 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>104.0</v>
+        <v>279.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -3798,16 +4182,16 @@
         <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>317.0</v>
+        <v>3343.0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0</v>
+        <v>38.0</v>
       </c>
     </row>
     <row r="17">
@@ -3821,16 +4205,16 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>3356.0</v>
+        <v>1534.0</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>38.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="18">
@@ -3844,16 +4228,16 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E18" t="n">
-        <v>1534.0</v>
+        <v>0.0</v>
       </c>
       <c r="F18" t="n">
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>41.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
@@ -3867,16 +4251,16 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0</v>
+        <v>554.0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
@@ -3887,19 +4271,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>556.0</v>
+        <v>8925.0</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0</v>
+        <v>18.0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="21">
@@ -3913,16 +4297,16 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>8925.0</v>
+        <v>2960.0</v>
       </c>
       <c r="F21" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>187.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="22">
@@ -3936,16 +4320,16 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>2958.0</v>
+        <v>5988.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="23">
@@ -3956,19 +4340,19 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>5988.0</v>
+        <v>3356.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>5.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="24">
@@ -3979,19 +4363,19 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>3356.0</v>
+        <v>5643.0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="n">
-        <v>83.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="25">
@@ -4005,16 +4389,16 @@
         <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>5643.0</v>
+        <v>1581.0</v>
       </c>
       <c r="F25" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>164.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="26">
@@ -4028,16 +4412,16 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>1581.0</v>
+        <v>4369.0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -4048,19 +4432,19 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>4369.0</v>
+        <v>653.0</v>
       </c>
       <c r="F27" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="28">
@@ -4074,16 +4458,16 @@
         <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E28" t="n">
-        <v>747.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>6.0</v>
+        <v>34.0</v>
       </c>
     </row>
     <row r="29">
@@ -4097,16 +4481,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0</v>
+        <v>1846.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>48.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -4114,16 +4498,16 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>3060.0</v>
+        <v>104.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -4137,19 +4521,19 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>1023.0</v>
+        <v>38.0</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -4163,13 +4547,13 @@
         <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E32" t="n">
-        <v>14.0</v>
+        <v>13.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -4186,19 +4570,19 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>2232.0</v>
+        <v>2.0</v>
       </c>
       <c r="F33" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G33" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -4209,19 +4593,19 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
-        <v>1691.0</v>
+        <v>14.0</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -4235,15 +4619,153 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2232.0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>49.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1691.0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37" t="s">
         <v>26</v>
       </c>
-      <c r="E35" t="n">
-        <v>590.0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="E37" t="n">
+        <v>591.0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1214.0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1023.0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G41" t="n">
         <v>0.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -617,7 +617,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -1651,7 +1651,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="G57" t="n">
         <v>70.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>155.0</v>
+        <v>158.0</v>
       </c>
       <c r="G62" t="n">
         <v>96.0</v>
@@ -3508,7 +3508,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>110.0</v>
+        <v>113.0</v>
       </c>
       <c r="F17" t="n">
         <v>24.0</v>
@@ -4024,7 +4024,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1301.0</v>
+        <v>1303.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4277,7 +4277,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8925.0</v>
+        <v>8931.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4300,7 +4300,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2960.0</v>
+        <v>2961.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>5988.0</v>
+        <v>5997.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5643.0</v>
+        <v>5651.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4622,7 +4622,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="n">
-        <v>2232.0</v>
+        <v>2236.0</v>
       </c>
       <c r="F35" t="n">
         <v>2.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1157,7 +1157,7 @@
         <v>38</v>
       </c>
       <c r="F38" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>152.0</v>
+        <v>153.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>158.0</v>
+        <v>161.0</v>
       </c>
       <c r="G62" t="n">
         <v>96.0</v>
@@ -1807,7 +1807,7 @@
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>192.0</v>
+        <v>193.0</v>
       </c>
       <c r="G63" t="n">
         <v>53.0</v>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G64" t="n">
         <v>2.0</v>
@@ -1989,7 +1989,7 @@
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>240.0</v>
+        <v>241.0</v>
       </c>
       <c r="G70" t="n">
         <v>16.0</v>
@@ -2174,7 +2174,7 @@
         <v>52.0</v>
       </c>
       <c r="G77" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="H77" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>56.0</v>
       </c>
       <c r="G78" t="n">
-        <v>130.0</v>
+        <v>132.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2301,7 +2301,7 @@
         <v>36</v>
       </c>
       <c r="F82" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2486,7 +2486,7 @@
         <v>2.0</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2769,7 +2769,7 @@
         <v>36</v>
       </c>
       <c r="F100" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -3084,7 +3084,7 @@
         <v>23.0</v>
       </c>
       <c r="G112" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>258.0</v>
+        <v>261.0</v>
       </c>
     </row>
     <row r="12">
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>64.0</v>
+        <v>68.0</v>
       </c>
       <c r="F20" t="n">
         <v>28.0</v>
@@ -3600,13 +3600,13 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>179.0</v>
+        <v>181.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>123.0</v>
+        <v>128.0</v>
       </c>
     </row>
     <row r="22">
@@ -3767,7 +3767,7 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>96.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="29">
@@ -3807,7 +3807,7 @@
         <v>29</v>
       </c>
       <c r="E30" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -3886,7 +3886,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>392.0</v>
+        <v>431.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3932,7 +3932,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>260.0</v>
+        <v>261.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3955,7 +3955,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>592.0</v>
+        <v>593.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4024,7 +4024,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1303.0</v>
+        <v>1306.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4070,7 +4070,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>432.0</v>
+        <v>436.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>396.0</v>
+        <v>398.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4162,7 +4162,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>279.0</v>
+        <v>286.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4185,7 +4185,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3343.0</v>
+        <v>3345.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4208,7 +4208,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1534.0</v>
+        <v>1537.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4254,7 +4254,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>554.0</v>
+        <v>559.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4277,7 +4277,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8931.0</v>
+        <v>8932.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4300,7 +4300,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2961.0</v>
+        <v>2965.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>5997.0</v>
+        <v>6003.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5651.0</v>
+        <v>5656.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4415,7 +4415,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4369.0</v>
+        <v>4373.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4438,7 +4438,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>653.0</v>
+        <v>654.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4507,7 +4507,7 @@
         <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -4530,13 +4530,13 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>38.0</v>
+        <v>46.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="32">
@@ -4622,7 +4622,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="n">
-        <v>2236.0</v>
+        <v>2237.0</v>
       </c>
       <c r="F35" t="n">
         <v>2.0</v>
@@ -4668,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="E37" t="n">
-        <v>591.0</v>
+        <v>593.0</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1023.0</v>
+        <v>1024.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1625,10 +1625,10 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1361.0</v>
+        <v>1365.0</v>
       </c>
       <c r="G56" t="n">
-        <v>698.0</v>
+        <v>699.0</v>
       </c>
       <c r="H56" t="n">
         <v>92.0</v>
@@ -1677,7 +1677,7 @@
         <v>38</v>
       </c>
       <c r="F58" t="n">
-        <v>261.0</v>
+        <v>263.0</v>
       </c>
       <c r="G58" t="n">
         <v>16.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>153.0</v>
+        <v>156.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -3347,7 +3347,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="F10" t="n">
         <v>15.0</v>
@@ -4047,7 +4047,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1755.0</v>
+        <v>1756.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4070,7 +4070,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>436.0</v>
+        <v>437.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4093,7 +4093,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>593.0</v>
+        <v>594.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4277,7 +4277,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8932.0</v>
+        <v>8938.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4300,7 +4300,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2965.0</v>
+        <v>2967.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>1581.0</v>
+        <v>1582.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4373.0</v>
+        <v>4374.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4438,7 +4438,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>654.0</v>
+        <v>655.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4760,7 +4760,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1024.0</v>
+        <v>1025.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2954,7 +2954,7 @@
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -4070,7 +4070,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>437.0</v>
+        <v>438.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4093,7 +4093,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>594.0</v>
+        <v>595.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4300,7 +4300,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2967.0</v>
+        <v>2968.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4374.0</v>
+        <v>4376.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4668,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="E37" t="n">
-        <v>593.0</v>
+        <v>595.0</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="39">
   <si>
     <t>Area</t>
   </si>
@@ -1027,7 +1027,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -2486,7 +2486,7 @@
         <v>2.0</v>
       </c>
       <c r="G89" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2873,7 +2873,7 @@
         <v>37</v>
       </c>
       <c r="F104" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -3606,7 +3606,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
     </row>
     <row r="22">
@@ -3663,19 +3663,19 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G24" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -3686,19 +3686,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="F25" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3712,16 +3712,16 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="F26" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G26" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="27">
@@ -3735,16 +3735,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F27" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28">
@@ -3755,19 +3755,19 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
         <v>0.0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G28" t="n">
-        <v>97.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -3781,16 +3781,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>65.0</v>
+        <v>0.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>97.0</v>
       </c>
     </row>
     <row r="30">
@@ -3804,15 +3804,38 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" t="s">
         <v>29</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>6.0</v>
       </c>
-      <c r="F30" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="F31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.0</v>
       </c>
     </row>
@@ -4093,7 +4116,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4438,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4760,7 +4783,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1025.0</v>
+        <v>1028.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -897,7 +897,7 @@
         <v>38</v>
       </c>
       <c r="F28" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1469,7 +1469,7 @@
         <v>38</v>
       </c>
       <c r="F50" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G50" t="n">
         <v>3.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1365.0</v>
+        <v>1366.0</v>
       </c>
       <c r="G56" t="n">
         <v>699.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>156.0</v>
+        <v>158.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1781,10 +1781,10 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>161.0</v>
+        <v>162.0</v>
       </c>
       <c r="G62" t="n">
-        <v>96.0</v>
+        <v>101.0</v>
       </c>
       <c r="H62" t="n">
         <v>4.0</v>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G64" t="n">
         <v>2.0</v>
@@ -2093,7 +2093,7 @@
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -3508,13 +3508,13 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="F17" t="n">
         <v>24.0</v>
       </c>
       <c r="G17" t="n">
-        <v>82.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="18">
@@ -3577,10 +3577,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>68.0</v>
+        <v>74.0</v>
       </c>
       <c r="F20" t="n">
-        <v>28.0</v>
+        <v>30.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>593.0</v>
+        <v>599.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4208,7 +4208,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3345.0</v>
+        <v>3378.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4231,7 +4231,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1537.0</v>
+        <v>1538.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4277,7 +4277,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>559.0</v>
+        <v>569.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4300,7 +4300,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8938.0</v>
+        <v>8939.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2968.0</v>
+        <v>2971.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6003.0</v>
+        <v>6005.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5656.0</v>
+        <v>5660.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4438,7 +4438,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4376.0</v>
+        <v>4381.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4668,7 +4668,7 @@
         <v>25</v>
       </c>
       <c r="E36" t="n">
-        <v>1691.0</v>
+        <v>1693.0</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -611,13 +611,13 @@
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -1498,7 +1498,7 @@
         <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>35.0</v>
+        <v>43.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1366.0</v>
+        <v>1367.0</v>
       </c>
       <c r="G56" t="n">
         <v>699.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G62" t="n">
         <v>101.0</v>
@@ -1885,7 +1885,7 @@
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G66" t="n">
         <v>21.0</v>
@@ -3376,7 +3376,7 @@
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>261.0</v>
+        <v>266.0</v>
       </c>
     </row>
     <row r="12">
@@ -3399,7 +3399,7 @@
         <v>46.0</v>
       </c>
       <c r="G12" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="13">
@@ -3508,10 +3508,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>114.0</v>
+        <v>117.0</v>
       </c>
       <c r="F17" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="G17" t="n">
         <v>90.0</v>
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="F20" t="n">
         <v>30.0</v>
@@ -4214,7 +4214,7 @@
         <v>2.0</v>
       </c>
       <c r="G16" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="17">
@@ -4300,7 +4300,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8939.0</v>
+        <v>8947.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2971.0</v>
+        <v>2973.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6005.0</v>
+        <v>6017.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5660.0</v>
+        <v>5665.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4438,7 +4438,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4381.0</v>
+        <v>4383.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -273,7 +273,7 @@
         <v>38</v>
       </c>
       <c r="F4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -325,7 +325,7 @@
         <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -1157,7 +1157,7 @@
         <v>38</v>
       </c>
       <c r="F38" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1209,7 +1209,7 @@
         <v>37</v>
       </c>
       <c r="F40" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1235,7 +1235,7 @@
         <v>38</v>
       </c>
       <c r="F41" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1498,7 +1498,7 @@
         <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -2460,7 +2460,7 @@
         <v>2.0</v>
       </c>
       <c r="G88" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2720,7 +2720,7 @@
         <v>19.0</v>
       </c>
       <c r="G98" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="H98" t="n">
         <v>1.0</v>
@@ -3058,7 +3058,7 @@
         <v>5.0</v>
       </c>
       <c r="G111" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3081,10 +3081,10 @@
         <v>37</v>
       </c>
       <c r="F112" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G112" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>169.0</v>
+        <v>173.0</v>
       </c>
       <c r="F11" t="n">
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>266.0</v>
+        <v>267.0</v>
       </c>
     </row>
     <row r="12">
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="F20" t="n">
         <v>30.0</v>
@@ -3675,7 +3675,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="25">
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -4024,7 +4024,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>656.0</v>
+        <v>658.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -4277,7 +4277,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>569.0</v>
+        <v>570.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2973.0</v>
+        <v>2984.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3356.0</v>
+        <v>3359.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>1582.0</v>
+        <v>1586.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>106.0</v>
+        <v>107.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -4760,7 +4760,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1214.0</v>
+        <v>1215.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4789,7 +4789,7 @@
         <v>1.0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1027,7 +1027,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G64" t="n">
         <v>2.0</v>
@@ -3029,7 +3029,7 @@
         <v>38</v>
       </c>
       <c r="F110" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3058,7 +3058,7 @@
         <v>5.0</v>
       </c>
       <c r="G111" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3514,7 +3514,7 @@
         <v>26.0</v>
       </c>
       <c r="G17" t="n">
-        <v>90.0</v>
+        <v>91.0</v>
       </c>
     </row>
     <row r="18">
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="F20" t="n">
         <v>30.0</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1756.0</v>
+        <v>1761.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2984.0</v>
+        <v>2987.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6017.0</v>
+        <v>6019.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3359.0</v>
+        <v>3364.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5665.0</v>
+        <v>5666.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4438,7 +4438,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4383.0</v>
+        <v>4386.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4461,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>656.0</v>
+        <v>657.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4507,7 +4507,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1846.0</v>
+        <v>1848.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -637,7 +637,7 @@
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>163.0</v>
+        <v>164.0</v>
       </c>
       <c r="G62" t="n">
         <v>101.0</v>
@@ -1807,7 +1807,7 @@
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>193.0</v>
+        <v>194.0</v>
       </c>
       <c r="G63" t="n">
         <v>53.0</v>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>115.0</v>
+        <v>117.0</v>
       </c>
       <c r="G64" t="n">
         <v>2.0</v>
@@ -3107,7 +3107,7 @@
         <v>38</v>
       </c>
       <c r="F113" t="n">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -3376,7 +3376,7 @@
         <v>79.0</v>
       </c>
       <c r="G11" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
     </row>
     <row r="12">
@@ -3600,13 +3600,13 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>181.0</v>
+        <v>184.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>129.0</v>
+        <v>131.0</v>
       </c>
     </row>
     <row r="22">
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1761.0</v>
+        <v>1762.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2987.0</v>
+        <v>2993.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6019.0</v>
+        <v>6034.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>657.0</v>
+        <v>659.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1339,7 +1339,7 @@
         <v>36</v>
       </c>
       <c r="F45" t="n">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="G45" t="n">
         <v>69.0</v>
@@ -3347,7 +3347,7 @@
         <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="F10" t="n">
         <v>15.0</v>
@@ -3373,7 +3373,7 @@
         <v>173.0</v>
       </c>
       <c r="F11" t="n">
-        <v>79.0</v>
+        <v>90.0</v>
       </c>
       <c r="G11" t="n">
         <v>268.0</v>
@@ -3393,10 +3393,10 @@
         <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>42.0</v>
+        <v>44.0</v>
       </c>
       <c r="F12" t="n">
-        <v>46.0</v>
+        <v>49.0</v>
       </c>
       <c r="G12" t="n">
         <v>18.0</v>
@@ -3439,7 +3439,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="F14" t="n">
         <v>16.0</v>
@@ -3629,7 +3629,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>111.0</v>
+        <v>115.0</v>
       </c>
     </row>
     <row r="23">
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>107.0</v>
+        <v>109.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3669,7 +3669,7 @@
         <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3790,7 +3790,7 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>97.0</v>
+        <v>98.0</v>
       </c>
     </row>
     <row r="30">
@@ -3807,7 +3807,7 @@
         <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>65.0</v>
+        <v>68.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3909,7 +3909,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>431.0</v>
+        <v>439.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>599.0</v>
+        <v>610.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4185,7 +4185,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>286.0</v>
+        <v>289.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4277,7 +4277,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>570.0</v>
+        <v>580.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4507,7 +4507,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1848.0</v>
+        <v>1850.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>107.0</v>
+        <v>108.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1028.0</v>
+        <v>1031.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -351,7 +351,7 @@
         <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -871,7 +871,7 @@
         <v>37</v>
       </c>
       <c r="F27" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -897,7 +897,7 @@
         <v>38</v>
       </c>
       <c r="F28" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1937,7 +1937,7 @@
         <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="G68" t="n">
         <v>244.0</v>
@@ -3373,7 +3373,7 @@
         <v>173.0</v>
       </c>
       <c r="F11" t="n">
-        <v>90.0</v>
+        <v>94.0</v>
       </c>
       <c r="G11" t="n">
         <v>268.0</v>
@@ -3508,7 +3508,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>117.0</v>
+        <v>118.0</v>
       </c>
       <c r="F17" t="n">
         <v>26.0</v>
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="F20" t="n">
         <v>30.0</v>
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>106.0</v>
+        <v>120.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -4047,7 +4047,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1306.0</v>
+        <v>1310.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4093,7 +4093,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>438.0</v>
+        <v>439.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>2993.0</v>
+        <v>3000.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6034.0</v>
+        <v>6046.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>108.0</v>
+        <v>110.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -4645,7 +4645,7 @@
         <v>24</v>
       </c>
       <c r="E35" t="n">
-        <v>2237.0</v>
+        <v>2238.0</v>
       </c>
       <c r="F35" t="n">
         <v>2.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1498,7 +1498,7 @@
         <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -1859,7 +1859,7 @@
         <v>36</v>
       </c>
       <c r="F65" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G65" t="n">
         <v>97.0</v>
@@ -2174,7 +2174,7 @@
         <v>52.0</v>
       </c>
       <c r="G77" t="n">
-        <v>134.0</v>
+        <v>138.0</v>
       </c>
       <c r="H77" t="n">
         <v>1.0</v>
@@ -2200,7 +2200,7 @@
         <v>56.0</v>
       </c>
       <c r="G78" t="n">
-        <v>132.0</v>
+        <v>134.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2460,7 +2460,7 @@
         <v>2.0</v>
       </c>
       <c r="G88" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -3600,13 +3600,13 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>184.0</v>
+        <v>189.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>131.0</v>
+        <v>134.0</v>
       </c>
     </row>
     <row r="22">
@@ -4369,7 +4369,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3364.0</v>
+        <v>3369.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>659.0</v>
+        <v>664.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -559,7 +559,7 @@
         <v>37</v>
       </c>
       <c r="F15" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -1498,7 +1498,7 @@
         <v>0.0</v>
       </c>
       <c r="G51" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="H51" t="n">
         <v>0.0</v>
@@ -2200,7 +2200,7 @@
         <v>56.0</v>
       </c>
       <c r="G78" t="n">
-        <v>134.0</v>
+        <v>135.0</v>
       </c>
       <c r="H78" t="n">
         <v>0.0</v>
@@ -2278,7 +2278,7 @@
         <v>0.0</v>
       </c>
       <c r="G81" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -3107,7 +3107,7 @@
         <v>38</v>
       </c>
       <c r="F113" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="G113" t="n">
         <v>0.0</v>
@@ -3439,7 +3439,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="F14" t="n">
         <v>16.0</v>
@@ -3606,7 +3606,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>134.0</v>
+        <v>136.0</v>
       </c>
     </row>
     <row r="22">
@@ -3790,7 +3790,7 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>98.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="30">
@@ -3830,7 +3830,7 @@
         <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -3886,7 +3886,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3909,7 +3909,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>439.0</v>
+        <v>446.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3932,7 +3932,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>126.0</v>
+        <v>145.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3955,7 +3955,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>261.0</v>
+        <v>262.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>610.0</v>
+        <v>612.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>597.0</v>
+        <v>601.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4208,7 +4208,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3378.0</v>
+        <v>3408.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4231,7 +4231,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1538.0</v>
+        <v>1540.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4277,7 +4277,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>580.0</v>
+        <v>587.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4507,7 +4507,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1850.0</v>
+        <v>1852.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4760,7 +4760,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1215.0</v>
+        <v>1218.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1784,7 +1784,7 @@
         <v>164.0</v>
       </c>
       <c r="G62" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="H62" t="n">
         <v>4.0</v>
@@ -2486,7 +2486,7 @@
         <v>2.0</v>
       </c>
       <c r="G89" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -3055,7 +3055,7 @@
         <v>36</v>
       </c>
       <c r="F111" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G111" t="n">
         <v>4.0</v>
@@ -3376,7 +3376,7 @@
         <v>94.0</v>
       </c>
       <c r="G11" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
     </row>
     <row r="12">
@@ -3514,7 +3514,7 @@
         <v>26.0</v>
       </c>
       <c r="G17" t="n">
-        <v>91.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="18">
@@ -3675,7 +3675,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="25">
@@ -4783,13 +4783,13 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1031.0</v>
+        <v>1037.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
       </c>
       <c r="G41" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -871,7 +871,7 @@
         <v>37</v>
       </c>
       <c r="F27" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1367.0</v>
+        <v>1369.0</v>
       </c>
       <c r="G56" t="n">
         <v>699.0</v>
@@ -1651,7 +1651,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>244.0</v>
+        <v>252.0</v>
       </c>
       <c r="G57" t="n">
         <v>70.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>144.0</v>
+        <v>146.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1937,7 +1937,7 @@
         <v>36</v>
       </c>
       <c r="F68" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="G68" t="n">
         <v>244.0</v>
@@ -1989,7 +1989,7 @@
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>241.0</v>
+        <v>242.0</v>
       </c>
       <c r="G70" t="n">
         <v>16.0</v>
@@ -2093,7 +2093,7 @@
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G74" t="n">
         <v>0.0</v>
@@ -2717,7 +2717,7 @@
         <v>37</v>
       </c>
       <c r="F98" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="G98" t="n">
         <v>4.0</v>
@@ -2795,7 +2795,7 @@
         <v>37</v>
       </c>
       <c r="F101" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G101" t="n">
         <v>0.0</v>
@@ -3508,13 +3508,13 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>118.0</v>
+        <v>124.0</v>
       </c>
       <c r="F17" t="n">
         <v>26.0</v>
       </c>
       <c r="G17" t="n">
-        <v>92.0</v>
+        <v>93.0</v>
       </c>
     </row>
     <row r="18">
@@ -3577,10 +3577,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>78.0</v>
+        <v>83.0</v>
       </c>
       <c r="F20" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G20" t="n">
         <v>8.0</v>
@@ -4047,7 +4047,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1310.0</v>
+        <v>1313.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4070,7 +4070,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1762.0</v>
+        <v>1763.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4300,7 +4300,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8947.0</v>
+        <v>8970.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4323,7 +4323,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3000.0</v>
+        <v>3012.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6046.0</v>
+        <v>6052.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5666.0</v>
+        <v>5668.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4415,7 +4415,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>1586.0</v>
+        <v>1587.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4438,7 +4438,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4386.0</v>
+        <v>4389.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4461,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>664.0</v>
+        <v>668.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4507,7 +4507,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1852.0</v>
+        <v>1853.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4668,7 +4668,7 @@
         <v>25</v>
       </c>
       <c r="E36" t="n">
-        <v>1693.0</v>
+        <v>1695.0</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
@@ -4691,7 +4691,7 @@
         <v>26</v>
       </c>
       <c r="E37" t="n">
-        <v>595.0</v>
+        <v>597.0</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
@@ -4783,13 +4783,13 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1037.0</v>
+        <v>1038.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
       </c>
       <c r="G41" t="n">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="39">
   <si>
     <t>Area</t>
   </si>
@@ -3666,16 +3666,16 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="25">
@@ -3686,19 +3686,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="26">
@@ -3709,19 +3709,19 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>17.0</v>
+        <v>1.0</v>
       </c>
       <c r="F26" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -3735,16 +3735,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="28">
@@ -3758,16 +3758,16 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29">
@@ -3778,19 +3778,19 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E29" t="n">
         <v>0.0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G29" t="n">
-        <v>99.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -3804,16 +3804,16 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>68.0</v>
+        <v>0.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="31">
@@ -3827,15 +3827,38 @@
         <v>16</v>
       </c>
       <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
         <v>29</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E32" t="n">
         <v>8.0</v>
       </c>
-      <c r="F31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F32" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G32" t="n">
         <v>1.0</v>
       </c>
     </row>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>146.0</v>
+        <v>147.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>164.0</v>
+        <v>175.0</v>
       </c>
       <c r="G62" t="n">
         <v>102.0</v>
@@ -2954,7 +2954,7 @@
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -3003,7 +3003,7 @@
         <v>37</v>
       </c>
       <c r="F109" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
@@ -3058,7 +3058,7 @@
         <v>6.0</v>
       </c>
       <c r="G111" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3370,13 +3370,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>173.0</v>
+        <v>176.0</v>
       </c>
       <c r="F11" t="n">
         <v>94.0</v>
       </c>
       <c r="G11" t="n">
-        <v>269.0</v>
+        <v>272.0</v>
       </c>
     </row>
     <row r="12">
@@ -3508,7 +3508,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="F17" t="n">
         <v>26.0</v>
@@ -3577,13 +3577,13 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>83.0</v>
+        <v>85.0</v>
       </c>
       <c r="F20" t="n">
         <v>31.0</v>
       </c>
       <c r="G20" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="21">
@@ -3600,7 +3600,7 @@
         <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -3629,7 +3629,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>115.0</v>
+        <v>118.0</v>
       </c>
     </row>
     <row r="23">
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>109.0</v>
+        <v>112.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3813,7 +3813,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>99.0</v>
+        <v>102.0</v>
       </c>
     </row>
     <row r="31">
@@ -3830,7 +3830,7 @@
         <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>68.0</v>
+        <v>70.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -3909,7 +3909,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -4001,7 +4001,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>612.0</v>
+        <v>616.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4208,7 +4208,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>289.0</v>
+        <v>291.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4231,7 +4231,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3408.0</v>
+        <v>3415.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3012.0</v>
+        <v>3015.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6052.0</v>
+        <v>6065.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4389.0</v>
+        <v>4393.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>668.0</v>
+        <v>670.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4576,7 +4576,7 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1038.0</v>
+        <v>1039.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1369.0</v>
+        <v>1373.0</v>
       </c>
       <c r="G56" t="n">
         <v>699.0</v>
@@ -4093,7 +4093,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1763.0</v>
+        <v>1764.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8970.0</v>
+        <v>8990.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3015.0</v>
+        <v>3016.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3369.0</v>
+        <v>3372.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="F32" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -3058,7 +3058,7 @@
         <v>6.0</v>
       </c>
       <c r="G111" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3084,7 +3084,7 @@
         <v>24.0</v>
       </c>
       <c r="G112" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3629,7 +3629,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>118.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="23">
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3853,7 +3853,7 @@
         <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -4139,7 +4139,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>601.0</v>
+        <v>604.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>670.0</v>
+        <v>671.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4513,7 +4513,7 @@
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="29">
@@ -4530,7 +4530,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1853.0</v>
+        <v>1856.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1218.0</v>
+        <v>1220.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1039.0</v>
+        <v>1040.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -897,7 +897,7 @@
         <v>38</v>
       </c>
       <c r="F28" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1027,7 +1027,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1131,7 +1131,7 @@
         <v>37</v>
       </c>
       <c r="F37" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1373.0</v>
+        <v>1374.0</v>
       </c>
       <c r="G56" t="n">
         <v>699.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>147.0</v>
+        <v>149.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>160.0</v>
+        <v>162.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -2954,7 +2954,7 @@
         <v>0.0</v>
       </c>
       <c r="G107" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -3058,7 +3058,7 @@
         <v>6.0</v>
       </c>
       <c r="G111" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3084,7 +3084,7 @@
         <v>24.0</v>
       </c>
       <c r="G112" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3508,10 +3508,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>125.0</v>
+        <v>127.0</v>
       </c>
       <c r="F17" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="G17" t="n">
         <v>93.0</v>
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3813,7 +3813,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="31">
@@ -3853,13 +3853,13 @@
         <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
       </c>
       <c r="G32" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -4070,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1313.0</v>
+        <v>1317.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4093,7 +4093,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1764.0</v>
+        <v>1766.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4116,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>439.0</v>
+        <v>443.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8990.0</v>
+        <v>8996.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3016.0</v>
+        <v>3028.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4438,7 +4438,7 @@
         <v>25</v>
       </c>
       <c r="E25" t="n">
-        <v>1587.0</v>
+        <v>1588.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1040.0</v>
+        <v>1041.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1628,7 +1628,7 @@
         <v>1374.0</v>
       </c>
       <c r="G56" t="n">
-        <v>699.0</v>
+        <v>700.0</v>
       </c>
       <c r="H56" t="n">
         <v>92.0</v>
@@ -1963,7 +1963,7 @@
         <v>37</v>
       </c>
       <c r="F69" t="n">
-        <v>164.0</v>
+        <v>166.0</v>
       </c>
       <c r="G69" t="n">
         <v>123.0</v>
@@ -2119,7 +2119,7 @@
         <v>37</v>
       </c>
       <c r="F75" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="G75" t="n">
         <v>1.0</v>
@@ -2171,7 +2171,7 @@
         <v>36</v>
       </c>
       <c r="F77" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G77" t="n">
         <v>138.0</v>
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="F20" t="n">
         <v>31.0</v>
@@ -3606,7 +3606,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>136.0</v>
+        <v>137.0</v>
       </c>
     </row>
     <row r="22">
@@ -4070,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1317.0</v>
+        <v>1318.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4139,7 +4139,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>604.0</v>
+        <v>605.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5668.0</v>
+        <v>5671.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>671.0</v>
+        <v>672.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -4162,7 +4162,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>398.0</v>
+        <v>399.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1220.0</v>
+        <v>1222.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1041.0</v>
+        <v>1043.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -637,7 +637,7 @@
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1469,7 +1469,7 @@
         <v>38</v>
       </c>
       <c r="F50" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G50" t="n">
         <v>3.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>175.0</v>
+        <v>181.0</v>
       </c>
       <c r="G62" t="n">
         <v>102.0</v>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>117.0</v>
+        <v>120.0</v>
       </c>
       <c r="G64" t="n">
         <v>2.0</v>
@@ -3370,10 +3370,10 @@
         <v>19</v>
       </c>
       <c r="E11" t="n">
-        <v>176.0</v>
+        <v>178.0</v>
       </c>
       <c r="F11" t="n">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="G11" t="n">
         <v>272.0</v>
@@ -3442,7 +3442,7 @@
         <v>20.0</v>
       </c>
       <c r="F14" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="G14" t="n">
         <v>0.0</v>
@@ -3909,7 +3909,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>123.0</v>
+        <v>130.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3932,7 +3932,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>446.0</v>
+        <v>451.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3978,7 +3978,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>262.0</v>
+        <v>263.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -4001,7 +4001,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>616.0</v>
+        <v>624.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>443.0</v>
+        <v>448.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4208,7 +4208,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>291.0</v>
+        <v>296.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4231,7 +4231,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3415.0</v>
+        <v>3452.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4254,7 +4254,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1540.0</v>
+        <v>1541.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>587.0</v>
+        <v>592.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3028.0</v>
+        <v>3035.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6065.0</v>
+        <v>6073.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4393.0</v>
+        <v>4394.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4576,7 +4576,7 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>47.0</v>
+        <v>49.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -715,7 +715,7 @@
         <v>37</v>
       </c>
       <c r="F21" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="G21" t="n">
         <v>1.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1374.0</v>
+        <v>1378.0</v>
       </c>
       <c r="G56" t="n">
         <v>700.0</v>
@@ -1651,7 +1651,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G57" t="n">
         <v>70.0</v>
@@ -1885,7 +1885,7 @@
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G66" t="n">
         <v>21.0</v>
@@ -3932,7 +3932,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>451.0</v>
+        <v>453.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -4001,7 +4001,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>624.0</v>
+        <v>627.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4047,7 +4047,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>658.0</v>
+        <v>659.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>448.0</v>
+        <v>449.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4208,7 +4208,7 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>296.0</v>
+        <v>298.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4231,7 +4231,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3452.0</v>
+        <v>3458.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4254,7 +4254,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>1541.0</v>
+        <v>1542.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>592.0</v>
+        <v>593.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>8996.0</v>
+        <v>9012.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3035.0</v>
+        <v>3037.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3372.0</v>
+        <v>3376.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5671.0</v>
+        <v>5674.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4576,7 +4576,7 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>49.0</v>
+        <v>51.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1368,7 +1368,7 @@
         <v>43.0</v>
       </c>
       <c r="G46" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="H46" t="n">
         <v>4.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>150.0</v>
+        <v>151.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>162.0</v>
+        <v>163.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -2223,7 +2223,7 @@
         <v>38</v>
       </c>
       <c r="F79" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2769,7 +2769,7 @@
         <v>36</v>
       </c>
       <c r="F100" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -3081,7 +3081,7 @@
         <v>37</v>
       </c>
       <c r="F112" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G112" t="n">
         <v>9.0</v>
@@ -3606,7 +3606,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.0</v>
+        <v>138.0</v>
       </c>
     </row>
     <row r="22">
@@ -3629,7 +3629,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="23">
@@ -3813,7 +3813,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="31">
@@ -3830,7 +3830,7 @@
         <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>70.0</v>
+        <v>73.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>449.0</v>
+        <v>451.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3037.0</v>
+        <v>3043.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6073.0</v>
+        <v>6080.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5674.0</v>
+        <v>5676.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4394.0</v>
+        <v>4399.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>672.0</v>
+        <v>676.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1856.0</v>
+        <v>1857.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1222.0</v>
+        <v>1224.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1043.0</v>
+        <v>1051.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1131,7 +1131,7 @@
         <v>37</v>
       </c>
       <c r="F37" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1209,7 +1209,7 @@
         <v>37</v>
       </c>
       <c r="F40" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -2096,7 +2096,7 @@
         <v>38.0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -3514,7 +3514,7 @@
         <v>25.0</v>
       </c>
       <c r="G17" t="n">
-        <v>93.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="18">
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3830,7 +3830,7 @@
         <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4116,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>451.0</v>
+        <v>458.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4162,7 +4162,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>399.0</v>
+        <v>400.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4399.0</v>
+        <v>4400.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1051.0</v>
+        <v>1054.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -637,7 +637,7 @@
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1378.0</v>
+        <v>1379.0</v>
       </c>
       <c r="G56" t="n">
         <v>700.0</v>
@@ -1651,7 +1651,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>253.0</v>
+        <v>256.0</v>
       </c>
       <c r="G57" t="n">
         <v>70.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>163.0</v>
+        <v>165.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G62" t="n">
         <v>102.0</v>
@@ -1839,7 +1839,7 @@
         <v>2.0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="65">
@@ -2015,7 +2015,7 @@
         <v>36</v>
       </c>
       <c r="F71" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="G71" t="n">
         <v>2.0</v>
@@ -3255,7 +3255,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3554,7 +3554,7 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="F19" t="n">
         <v>4.0</v>
@@ -4070,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1318.0</v>
+        <v>1319.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4139,7 +4139,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>605.0</v>
+        <v>606.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>9012.0</v>
+        <v>9024.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3043.0</v>
+        <v>3047.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>676.0</v>
+        <v>677.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1054.0</v>
+        <v>1055.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2327,7 +2327,7 @@
         <v>37</v>
       </c>
       <c r="F83" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>115.0</v>
+        <v>118.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1224.0</v>
+        <v>1226.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1055.0</v>
+        <v>1061.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1573,7 +1573,7 @@
         <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="G54" t="n">
         <v>0.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>151.0</v>
+        <v>152.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -3373,7 +3373,7 @@
         <v>178.0</v>
       </c>
       <c r="F11" t="n">
-        <v>95.0</v>
+        <v>100.0</v>
       </c>
       <c r="G11" t="n">
         <v>272.0</v>
@@ -3439,7 +3439,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="F14" t="n">
         <v>19.0</v>
@@ -3909,7 +3909,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3932,7 +3932,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>453.0</v>
+        <v>456.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -4001,7 +4001,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>627.0</v>
+        <v>639.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4231,7 +4231,7 @@
         <v>19</v>
       </c>
       <c r="E16" t="n">
-        <v>3458.0</v>
+        <v>3460.0</v>
       </c>
       <c r="F16" t="n">
         <v>2.0</v>
@@ -4300,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>593.0</v>
+        <v>601.0</v>
       </c>
       <c r="F19" t="n">
         <v>2.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3047.0</v>
+        <v>3055.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4400.0</v>
+        <v>4401.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4576,7 +4576,7 @@
         <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2093,7 +2093,7 @@
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -4093,7 +4093,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1766.0</v>
+        <v>1768.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>9024.0</v>
+        <v>9025.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3055.0</v>
+        <v>3059.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4392,7 +4392,7 @@
         <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>3376.0</v>
+        <v>3378.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4401.0</v>
+        <v>4407.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>677.0</v>
+        <v>678.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -1729,7 +1729,7 @@
         <v>37</v>
       </c>
       <c r="F60" t="n">
-        <v>152.0</v>
+        <v>154.0</v>
       </c>
       <c r="G60" t="n">
         <v>31.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>165.0</v>
+        <v>168.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1781,7 +1781,7 @@
         <v>36</v>
       </c>
       <c r="F62" t="n">
-        <v>182.0</v>
+        <v>192.0</v>
       </c>
       <c r="G62" t="n">
         <v>102.0</v>
@@ -1833,7 +1833,7 @@
         <v>38</v>
       </c>
       <c r="F64" t="n">
-        <v>120.0</v>
+        <v>121.0</v>
       </c>
       <c r="G64" t="n">
         <v>2.0</v>
@@ -1963,7 +1963,7 @@
         <v>37</v>
       </c>
       <c r="F69" t="n">
-        <v>166.0</v>
+        <v>167.0</v>
       </c>
       <c r="G69" t="n">
         <v>123.0</v>
@@ -1989,7 +1989,7 @@
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>242.0</v>
+        <v>243.0</v>
       </c>
       <c r="G70" t="n">
         <v>16.0</v>
@@ -3081,7 +3081,7 @@
         <v>37</v>
       </c>
       <c r="F112" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G112" t="n">
         <v>9.0</v>
@@ -3554,7 +3554,7 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="F19" t="n">
         <v>4.0</v>
@@ -4070,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1319.0</v>
+        <v>1322.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3059.0</v>
+        <v>3065.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6080.0</v>
+        <v>6088.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4415,7 +4415,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>5676.0</v>
+        <v>5681.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -4530,7 +4530,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1857.0</v>
+        <v>1859.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4691,7 +4691,7 @@
         <v>25</v>
       </c>
       <c r="E36" t="n">
-        <v>1695.0</v>
+        <v>1696.0</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
@@ -4783,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1226.0</v>
+        <v>1236.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1061.0</v>
+        <v>1067.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1787,7 +1787,7 @@
         <v>102.0</v>
       </c>
       <c r="H62" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="63">
@@ -1807,7 +1807,7 @@
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>194.0</v>
+        <v>196.0</v>
       </c>
       <c r="G63" t="n">
         <v>53.0</v>
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>118.0</v>
+        <v>119.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3813,7 +3813,7 @@
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="31">
@@ -3830,7 +3830,7 @@
         <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3065.0</v>
+        <v>3069.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1131,7 +1131,7 @@
         <v>37</v>
       </c>
       <c r="F37" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1379.0</v>
+        <v>1382.0</v>
       </c>
       <c r="G56" t="n">
         <v>700.0</v>
@@ -1677,7 +1677,7 @@
         <v>38</v>
       </c>
       <c r="F58" t="n">
-        <v>263.0</v>
+        <v>266.0</v>
       </c>
       <c r="G58" t="n">
         <v>16.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>168.0</v>
+        <v>169.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -3081,7 +3081,7 @@
         <v>37</v>
       </c>
       <c r="F112" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G112" t="n">
         <v>9.0</v>
@@ -4162,7 +4162,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>400.0</v>
+        <v>410.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>9025.0</v>
+        <v>9032.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3069.0</v>
+        <v>3070.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6088.0</v>
+        <v>6100.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1859.0</v>
+        <v>1860.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -2327,7 +2327,7 @@
         <v>37</v>
       </c>
       <c r="F83" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G83" t="n">
         <v>0.0</v>
@@ -4139,7 +4139,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>606.0</v>
+        <v>609.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4162,7 +4162,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>410.0</v>
+        <v>411.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>678.0</v>
+        <v>680.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1067.0</v>
+        <v>1069.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1651,7 +1651,7 @@
         <v>37</v>
       </c>
       <c r="F57" t="n">
-        <v>256.0</v>
+        <v>259.0</v>
       </c>
       <c r="G57" t="n">
         <v>70.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>169.0</v>
+        <v>171.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -4070,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1322.0</v>
+        <v>1323.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>9032.0</v>
+        <v>9036.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3070.0</v>
+        <v>3083.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6100.0</v>
+        <v>6102.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4714,7 +4714,7 @@
         <v>26</v>
       </c>
       <c r="E37" t="n">
-        <v>597.0</v>
+        <v>598.0</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -637,7 +637,7 @@
         <v>37</v>
       </c>
       <c r="F18" t="n">
-        <v>19.0</v>
+        <v>21.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
@@ -1625,7 +1625,7 @@
         <v>36</v>
       </c>
       <c r="F56" t="n">
-        <v>1382.0</v>
+        <v>1383.0</v>
       </c>
       <c r="G56" t="n">
         <v>700.0</v>
@@ -1807,7 +1807,7 @@
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>196.0</v>
+        <v>203.0</v>
       </c>
       <c r="G63" t="n">
         <v>53.0</v>
@@ -1885,7 +1885,7 @@
         <v>37</v>
       </c>
       <c r="F66" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G66" t="n">
         <v>21.0</v>
@@ -1963,7 +1963,7 @@
         <v>37</v>
       </c>
       <c r="F69" t="n">
-        <v>167.0</v>
+        <v>168.0</v>
       </c>
       <c r="G69" t="n">
         <v>123.0</v>
@@ -1989,7 +1989,7 @@
         <v>38</v>
       </c>
       <c r="F70" t="n">
-        <v>243.0</v>
+        <v>245.0</v>
       </c>
       <c r="G70" t="n">
         <v>16.0</v>
@@ -4283,7 +4283,7 @@
         <v>0.0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="19">
@@ -4323,7 +4323,7 @@
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>9036.0</v>
+        <v>9047.0</v>
       </c>
       <c r="F20" t="n">
         <v>18.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3083.0</v>
+        <v>3087.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1209,7 +1209,7 @@
         <v>37</v>
       </c>
       <c r="F40" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1703,7 +1703,7 @@
         <v>36</v>
       </c>
       <c r="F59" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G59" t="n">
         <v>9.0</v>
@@ -1755,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="F61" t="n">
-        <v>171.0</v>
+        <v>173.0</v>
       </c>
       <c r="G61" t="n">
         <v>1.0</v>
@@ -1807,7 +1807,7 @@
         <v>37</v>
       </c>
       <c r="F63" t="n">
-        <v>203.0</v>
+        <v>205.0</v>
       </c>
       <c r="G63" t="n">
         <v>53.0</v>
@@ -2197,7 +2197,7 @@
         <v>37</v>
       </c>
       <c r="F78" t="n">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
       <c r="G78" t="n">
         <v>135.0</v>
@@ -3081,7 +3081,7 @@
         <v>37</v>
       </c>
       <c r="F112" t="n">
-        <v>27.0</v>
+        <v>29.0</v>
       </c>
       <c r="G112" t="n">
         <v>9.0</v>
@@ -3577,13 +3577,13 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>90.0</v>
+        <v>97.0</v>
       </c>
       <c r="F20" t="n">
         <v>31.0</v>
       </c>
       <c r="G20" t="n">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="21">
@@ -3606,7 +3606,7 @@
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="22">
@@ -4070,7 +4070,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1323.0</v>
+        <v>1324.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4346,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="E21" t="n">
-        <v>3087.0</v>
+        <v>3098.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
@@ -4369,7 +4369,7 @@
         <v>22</v>
       </c>
       <c r="E22" t="n">
-        <v>6102.0</v>
+        <v>6104.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4461,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="E26" t="n">
-        <v>4407.0</v>
+        <v>4409.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4484,7 +4484,7 @@
         <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>680.0</v>
+        <v>682.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4530,7 +4530,7 @@
         <v>35</v>
       </c>
       <c r="E29" t="n">
-        <v>1860.0</v>
+        <v>1862.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4783,7 +4783,7 @@
         <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>1236.0</v>
+        <v>1243.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1069.0</v>
+        <v>1086.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -1209,7 +1209,7 @@
         <v>37</v>
       </c>
       <c r="F40" t="n">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -2093,7 +2093,7 @@
         <v>36</v>
       </c>
       <c r="F74" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G74" t="n">
         <v>1.0</v>
@@ -3577,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>97.0</v>
+        <v>102.0</v>
       </c>
       <c r="F20" t="n">
         <v>31.0</v>
@@ -3646,7 +3646,7 @@
         <v>35</v>
       </c>
       <c r="E23" t="n">
-        <v>119.0</v>
+        <v>124.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3830,7 +3830,7 @@
         <v>35</v>
       </c>
       <c r="E31" t="n">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4806,7 +4806,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>1086.0</v>
+        <v>1089.0</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>

--- a/Download/Cinghiali_ZR.xlsx
+++ b/Download/Cinghiali_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="40">
   <si>
     <t>Area</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>Cuneo</t>
+  </si>
+  <si>
+    <t>Firenze</t>
   </si>
   <si>
     <t>Lucca</t>
@@ -218,7 +221,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>6.0</v>
@@ -244,7 +247,7 @@
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" t="n">
         <v>10.0</v>
@@ -270,7 +273,7 @@
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" t="n">
         <v>10.0</v>
@@ -296,10 +299,10 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G5" t="n">
         <v>0.0</v>
@@ -322,10 +325,10 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -348,10 +351,10 @@
         <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -374,7 +377,7 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>5.0</v>
@@ -400,7 +403,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
         <v>7.0</v>
@@ -426,7 +429,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" t="n">
         <v>27.0</v>
@@ -452,7 +455,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
         <v>10.0</v>
@@ -478,7 +481,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
         <v>9.0</v>
@@ -504,7 +507,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
         <v>33.0</v>
@@ -530,7 +533,7 @@
         <v>21</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
         <v>8.0</v>
@@ -556,7 +559,7 @@
         <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
         <v>27.0</v>
@@ -582,7 +585,7 @@
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" t="n">
         <v>79.0</v>
@@ -608,10 +611,10 @@
         <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>23.0</v>
+        <v>29.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -634,7 +637,7 @@
         <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F18" t="n">
         <v>21.0</v>
@@ -660,7 +663,7 @@
         <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F19" t="n">
         <v>4.0</v>
@@ -686,7 +689,7 @@
         <v>23</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
         <v>14.0</v>
@@ -712,7 +715,7 @@
         <v>23</v>
       </c>
       <c r="E21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F21" t="n">
         <v>42.0</v>
@@ -738,7 +741,7 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F22" t="n">
         <v>47.0</v>
@@ -764,7 +767,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F23" t="n">
         <v>19.0</v>
@@ -790,7 +793,7 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F24" t="n">
         <v>15.0</v>
@@ -816,7 +819,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F25" t="n">
         <v>72.0</v>
@@ -842,7 +845,7 @@
         <v>25</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
         <v>54.0</v>
@@ -868,7 +871,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" t="n">
         <v>25.0</v>
@@ -894,7 +897,7 @@
         <v>25</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F28" t="n">
         <v>23.0</v>
@@ -920,7 +923,7 @@
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F29" t="n">
         <v>11.0</v>
@@ -946,7 +949,7 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="n">
         <v>27.0</v>
@@ -972,7 +975,7 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F31" t="n">
         <v>48.0</v>
@@ -998,10 +1001,10 @@
         <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F32" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1021,13 +1024,13 @@
         <v>16</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>53.0</v>
+        <v>6.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1047,13 +1050,13 @@
         <v>16</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
         <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>76.0</v>
+        <v>31.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1076,10 +1079,10 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0</v>
+        <v>38.0</v>
       </c>
       <c r="G35" t="n">
         <v>0.0</v>
@@ -1102,10 +1105,10 @@
         <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1128,16 +1131,16 @@
         <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F37" t="n">
-        <v>25.0</v>
+        <v>17.0</v>
       </c>
       <c r="G37" t="n">
         <v>0.0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="38">
@@ -1154,16 +1157,16 @@
         <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>33.0</v>
+        <v>23.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="39">
@@ -1180,10 +1183,10 @@
         <v>30</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1206,10 +1209,10 @@
         <v>30</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F40" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1232,10 +1235,10 @@
         <v>30</v>
       </c>
       <c r="E41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>16.0</v>
+        <v>32.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1249,22 +1252,22 @@
         <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F42" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G42" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
         <v>0.0</v>
@@ -1275,19 +1278,19 @@
         <v>8</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F43" t="n">
-        <v>10.0</v>
+        <v>17.0</v>
       </c>
       <c r="G43" t="n">
         <v>0.0</v>
@@ -1301,19 +1304,19 @@
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F44" t="n">
-        <v>5.0</v>
+        <v>17.0</v>
       </c>
       <c r="G44" t="n">
         <v>0.0</v>
@@ -1333,19 +1336,19 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F45" t="n">
-        <v>56.0</v>
+        <v>8.0</v>
       </c>
       <c r="G45" t="n">
-        <v>69.0</v>
+        <v>1.0</v>
       </c>
       <c r="H45" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1359,19 +1362,19 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F46" t="n">
-        <v>43.0</v>
+        <v>13.0</v>
       </c>
       <c r="G46" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="H46" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1385,16 +1388,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F47" t="n">
-        <v>114.0</v>
+        <v>6.0</v>
       </c>
       <c r="G47" t="n">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
       <c r="H47" t="n">
         <v>0.0</v>
@@ -1411,16 +1414,16 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F48" t="n">
-        <v>32.0</v>
+        <v>56.0</v>
       </c>
       <c r="G48" t="n">
-        <v>144.0</v>
+        <v>69.0</v>
       </c>
       <c r="H48" t="n">
         <v>4.0</v>
@@ -1437,19 +1440,19 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F49" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G49" t="n">
-        <v>27.0</v>
+        <v>35.0</v>
       </c>
       <c r="H49" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="50">
@@ -1463,16 +1466,16 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F50" t="n">
-        <v>86.0</v>
+        <v>114.0</v>
       </c>
       <c r="G50" t="n">
-        <v>3.0</v>
+        <v>7.0</v>
       </c>
       <c r="H50" t="n">
         <v>0.0</v>
@@ -1489,19 +1492,19 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0</v>
+        <v>32.0</v>
       </c>
       <c r="G51" t="n">
-        <v>46.0</v>
+        <v>144.0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="52">
@@ -1515,19 +1518,19 @@
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0</v>
+        <v>42.0</v>
       </c>
       <c r="G52" t="n">
-        <v>7.0</v>
+        <v>27.0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="53">
@@ -1541,16 +1544,16 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>4.0</v>
+        <v>86.0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H53" t="n">
         <v>0.0</v>
@@ -1567,16 +1570,16 @@
         <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E54" t="s">
         <v>37</v>
       </c>
       <c r="F54" t="n">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0</v>
+        <v>46.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1593,16 +1596,16 @@
         <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E55" t="s">
         <v>38</v>
       </c>
       <c r="F55" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H55" t="n">
         <v>0.0</v>
@@ -1616,22 +1619,22 @@
         <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E56" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F56" t="n">
-        <v>1383.0</v>
+        <v>4.0</v>
       </c>
       <c r="G56" t="n">
-        <v>700.0</v>
+        <v>0.0</v>
       </c>
       <c r="H56" t="n">
-        <v>92.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -1642,22 +1645,22 @@
         <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F57" t="n">
-        <v>259.0</v>
+        <v>14.0</v>
       </c>
       <c r="G57" t="n">
-        <v>70.0</v>
+        <v>0.0</v>
       </c>
       <c r="H57" t="n">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1668,22 +1671,22 @@
         <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F58" t="n">
-        <v>266.0</v>
+        <v>16.0</v>
       </c>
       <c r="G58" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="H58" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1700,16 +1703,16 @@
         <v>33</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>84.0</v>
+        <v>1384.0</v>
       </c>
       <c r="G59" t="n">
-        <v>9.0</v>
+        <v>700.0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.0</v>
+        <v>92.0</v>
       </c>
     </row>
     <row r="60">
@@ -1726,16 +1729,16 @@
         <v>33</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F60" t="n">
-        <v>154.0</v>
+        <v>259.0</v>
       </c>
       <c r="G60" t="n">
-        <v>31.0</v>
+        <v>70.0</v>
       </c>
       <c r="H60" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="61">
@@ -1752,16 +1755,16 @@
         <v>33</v>
       </c>
       <c r="E61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>173.0</v>
+        <v>267.0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="H61" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="62">
@@ -1775,19 +1778,19 @@
         <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F62" t="n">
-        <v>192.0</v>
+        <v>84.0</v>
       </c>
       <c r="G62" t="n">
-        <v>102.0</v>
+        <v>9.0</v>
       </c>
       <c r="H62" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="63">
@@ -1801,19 +1804,19 @@
         <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E63" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>205.0</v>
+        <v>154.0</v>
       </c>
       <c r="G63" t="n">
-        <v>53.0</v>
+        <v>31.0</v>
       </c>
       <c r="H63" t="n">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="64">
@@ -1827,19 +1830,19 @@
         <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>121.0</v>
+        <v>173.0</v>
       </c>
       <c r="G64" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="65">
@@ -1850,22 +1853,22 @@
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>43.0</v>
+        <v>215.0</v>
       </c>
       <c r="G65" t="n">
-        <v>97.0</v>
+        <v>102.0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="66">
@@ -1876,22 +1879,22 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E66" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F66" t="n">
-        <v>82.0</v>
+        <v>205.0</v>
       </c>
       <c r="G66" t="n">
-        <v>21.0</v>
+        <v>53.0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="67">
@@ -1902,22 +1905,22 @@
         <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F67" t="n">
-        <v>128.0</v>
+        <v>121.0</v>
       </c>
       <c r="G67" t="n">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="68">
@@ -1928,19 +1931,19 @@
         <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F68" t="n">
-        <v>132.0</v>
+        <v>43.0</v>
       </c>
       <c r="G68" t="n">
-        <v>244.0</v>
+        <v>97.0</v>
       </c>
       <c r="H68" t="n">
         <v>0.0</v>
@@ -1954,22 +1957,22 @@
         <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D69" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F69" t="n">
-        <v>168.0</v>
+        <v>82.0</v>
       </c>
       <c r="G69" t="n">
-        <v>123.0</v>
+        <v>21.0</v>
       </c>
       <c r="H69" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1980,19 +1983,19 @@
         <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>245.0</v>
+        <v>128.0</v>
       </c>
       <c r="G70" t="n">
-        <v>16.0</v>
+        <v>8.0</v>
       </c>
       <c r="H70" t="n">
         <v>0.0</v>
@@ -2009,16 +2012,16 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F71" t="n">
-        <v>76.0</v>
+        <v>132.0</v>
       </c>
       <c r="G71" t="n">
-        <v>2.0</v>
+        <v>244.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2035,19 +2038,19 @@
         <v>15</v>
       </c>
       <c r="D72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F72" t="n">
-        <v>50.0</v>
+        <v>168.0</v>
       </c>
       <c r="G72" t="n">
-        <v>5.0</v>
+        <v>123.0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="73">
@@ -2061,16 +2064,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>41.0</v>
+        <v>245.0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0</v>
+        <v>16.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2087,16 +2090,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F74" t="n">
-        <v>40.0</v>
+        <v>76.0</v>
       </c>
       <c r="G74" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2113,19 +2116,19 @@
         <v>15</v>
       </c>
       <c r="D75" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F75" t="n">
-        <v>57.0</v>
+        <v>50.0</v>
       </c>
       <c r="G75" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="H75" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -2139,19 +2142,19 @@
         <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>63.0</v>
+        <v>41.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
       </c>
       <c r="H76" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -2162,22 +2165,22 @@
         <v>10</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F77" t="n">
-        <v>53.0</v>
+        <v>40.0</v>
       </c>
       <c r="G77" t="n">
-        <v>138.0</v>
+        <v>1.0</v>
       </c>
       <c r="H77" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2188,22 +2191,22 @@
         <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78" t="n">
-        <v>61.0</v>
+        <v>57.0</v>
       </c>
       <c r="G78" t="n">
-        <v>135.0</v>
+        <v>1.0</v>
       </c>
       <c r="H78" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="79">
@@ -2214,22 +2217,22 @@
         <v>10</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D79" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F79" t="n">
-        <v>38.0</v>
+        <v>63.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
       </c>
       <c r="H79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
@@ -2243,19 +2246,19 @@
         <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="G80" t="n">
-        <v>15.0</v>
+        <v>138.0</v>
       </c>
       <c r="H80" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -2269,16 +2272,16 @@
         <v>16</v>
       </c>
       <c r="D81" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0</v>
+        <v>100.0</v>
       </c>
       <c r="G81" t="n">
-        <v>27.0</v>
+        <v>135.0</v>
       </c>
       <c r="H81" t="n">
         <v>0.0</v>
@@ -2295,13 +2298,13 @@
         <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E82" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F82" t="n">
-        <v>9.0</v>
+        <v>93.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2327,13 +2330,13 @@
         <v>37</v>
       </c>
       <c r="F83" t="n">
-        <v>82.0</v>
+        <v>0.0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H83" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -2353,10 +2356,10 @@
         <v>38</v>
       </c>
       <c r="F84" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.0</v>
+        <v>27.0</v>
       </c>
       <c r="H84" t="n">
         <v>0.0</v>
@@ -2367,19 +2370,19 @@
         <v>8</v>
       </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C85" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D85" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E85" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F85" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G85" t="n">
         <v>0.0</v>
@@ -2393,25 +2396,25 @@
         <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>3.0</v>
+        <v>82.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
       </c>
       <c r="H86" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="87">
@@ -2419,19 +2422,19 @@
         <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D87" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E87" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F87" t="n">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="G87" t="n">
         <v>0.0</v>
@@ -2445,22 +2448,22 @@
         <v>8</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F88" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G88" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H88" t="n">
         <v>0.0</v>
@@ -2471,22 +2474,22 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F89" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G89" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="H89" t="n">
         <v>0.0</v>
@@ -2503,13 +2506,13 @@
         <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E90" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F90" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2529,13 +2532,13 @@
         <v>12</v>
       </c>
       <c r="D91" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E91" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F91" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2555,10 +2558,10 @@
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F92" t="n">
         <v>1.0</v>
@@ -2578,19 +2581,19 @@
         <v>11</v>
       </c>
       <c r="C93" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E93" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F93" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G93" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2604,19 +2607,19 @@
         <v>11</v>
       </c>
       <c r="C94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D94" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F94" t="n">
-        <v>24.0</v>
+        <v>2.0</v>
       </c>
       <c r="G94" t="n">
-        <v>61.0</v>
+        <v>2.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -2630,19 +2633,19 @@
         <v>11</v>
       </c>
       <c r="C95" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D95" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F95" t="n">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
       <c r="G95" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H95" t="n">
         <v>0.0</v>
@@ -2656,19 +2659,19 @@
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F96" t="n">
-        <v>46.0</v>
+        <v>1.0</v>
       </c>
       <c r="G96" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H96" t="n">
         <v>0.0</v>
@@ -2682,19 +2685,19 @@
         <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F97" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H97" t="n">
         <v>0.0</v>
@@ -2708,22 +2711,22 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E98" t="s">
         <v>37</v>
       </c>
       <c r="F98" t="n">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="G98" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="H98" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="99">
@@ -2737,16 +2740,16 @@
         <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F99" t="n">
-        <v>10.0</v>
+        <v>24.0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0</v>
+        <v>61.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2763,16 +2766,16 @@
         <v>15</v>
       </c>
       <c r="D100" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F100" t="n">
-        <v>5.0</v>
+        <v>31.0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2789,19 +2792,19 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E101" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F101" t="n">
-        <v>22.0</v>
+        <v>46.0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H101" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="102">
@@ -2815,16 +2818,16 @@
         <v>15</v>
       </c>
       <c r="D102" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F102" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2838,22 +2841,22 @@
         <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F103" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H103" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2864,16 +2867,16 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D104" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E104" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F104" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -2890,16 +2893,16 @@
         <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D105" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F105" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2916,22 +2919,22 @@
         <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D106" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E106" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="G106" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="107">
@@ -2942,19 +2945,19 @@
         <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D107" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E107" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G107" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2971,13 +2974,13 @@
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E108" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F108" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -2997,19 +3000,19 @@
         <v>16</v>
       </c>
       <c r="D109" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E109" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F109" t="n">
-        <v>58.0</v>
+        <v>2.0</v>
       </c>
       <c r="G109" t="n">
         <v>0.0</v>
       </c>
       <c r="H109" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="110">
@@ -3023,13 +3026,13 @@
         <v>16</v>
       </c>
       <c r="D110" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F110" t="n">
-        <v>15.0</v>
+        <v>4.0</v>
       </c>
       <c r="G110" t="n">
         <v>0.0</v>
@@ -3049,16 +3052,16 @@
         <v>16</v>
       </c>
       <c r="D111" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E111" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F111" t="n">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G111" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="H111" t="n">
         <v>0.0</v>
@@ -3075,16 +3078,16 @@
         <v>16</v>
       </c>
       <c r="D112" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E112" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F112" t="n">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="G112" t="n">
-        <v>9.0</v>
+        <v>19.0</v>
       </c>
       <c r="H112" t="n">
         <v>0.0</v>
@@ -3101,18 +3104,148 @@
         <v>16</v>
       </c>
       <c r="D113" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E113" t="s">
+        <v>37</v>
+      </c>
+      <c r="F113" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>8</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" t="s">
+        <v>16</v>
+      </c>
+      <c r="D114" t="s">
+        <v>36</v>
+      </c>
+      <c r="E114" t="s">
         <v>38</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F114" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>8</v>
+      </c>
+      <c r="B115" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" t="s">
+        <v>16</v>
+      </c>
+      <c r="D115" t="s">
+        <v>36</v>
+      </c>
+      <c r="E115" t="s">
+        <v>39</v>
+      </c>
+      <c r="F115" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>8</v>
+      </c>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" t="s">
+        <v>16</v>
+      </c>
+      <c r="D116" t="s">
+        <v>30</v>
+      </c>
+      <c r="E116" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>8</v>
+      </c>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>16</v>
+      </c>
+      <c r="D117" t="s">
+        <v>30</v>
+      </c>
+      <c r="E117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F117" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>8</v>
+      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" t="s">
+        <v>30</v>
+      </c>
+      <c r="E118" t="s">
+        <v>39</v>
+      </c>
+      <c r="F118" t="n">
         <v>35.0</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H113" t="n">
+      <c r="G118" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H118" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3315,22 +3448,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="10">
@@ -3344,16 +3477,16 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>24.0</v>
+        <v>178.0</v>
       </c>
       <c r="F10" t="n">
-        <v>15.0</v>
+        <v>100.0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0</v>
+        <v>272.0</v>
       </c>
     </row>
     <row r="11">
@@ -3367,16 +3500,16 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>178.0</v>
+        <v>44.0</v>
       </c>
       <c r="F11" t="n">
-        <v>100.0</v>
+        <v>49.0</v>
       </c>
       <c r="G11" t="n">
-        <v>272.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="12">
@@ -3390,16 +3523,16 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
       <c r="F12" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
       <c r="G12" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13">
@@ -3413,16 +3546,16 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0</v>
+        <v>21.0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -3433,19 +3566,19 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E14" t="n">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="F14" t="n">
-        <v>19.0</v>
+        <v>4.0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="15">
@@ -3459,16 +3592,16 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E15" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G15" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="16">
@@ -3482,16 +3615,16 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>17.0</v>
+        <v>127.0</v>
       </c>
       <c r="F16" t="n">
-        <v>6.0</v>
+        <v>25.0</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="17">
@@ -3502,19 +3635,19 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E17" t="n">
-        <v>127.0</v>
+        <v>19.0</v>
       </c>
       <c r="F17" t="n">
-        <v>25.0</v>
+        <v>7.0</v>
       </c>
       <c r="G17" t="n">
-        <v>99.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -3525,19 +3658,19 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>19.0</v>
+        <v>36.0</v>
       </c>
       <c r="F18" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="19">
@@ -3551,16 +3684,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>36.0</v>
+        <v>104.0</v>
       </c>
       <c r="F19" t="n">
-        <v>4.0</v>
+        <v>32.0</v>
       </c>
       <c r="G19" t="n">
-        <v>25.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="20">
@@ -3571,19 +3704,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>102.0</v>
+        <v>191.0</v>
       </c>
       <c r="F20" t="n">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="21">
@@ -3597,16 +3730,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>190.0</v>
+        <v>0.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>139.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="22">
@@ -3620,16 +3753,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0</v>
+        <v>124.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>122.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -3637,22 +3770,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>124.0</v>
+        <v>0.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -3666,16 +3799,16 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="25">
@@ -3686,19 +3819,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E25" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3709,19 +3842,19 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0</v>
+        <v>11.0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="27">
@@ -3735,16 +3868,16 @@
         <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>17.0</v>
+        <v>4.0</v>
       </c>
       <c r="F27" t="n">
-        <v>11.0</v>
+        <v>5.0</v>
       </c>
       <c r="G27" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28">
@@ -3758,16 +3891,16 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="F28" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -3778,19 +3911,19 @@
         <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E29" t="n">
         <v>0.0</v>
       </c>
       <c r="F29" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>105.0</v>
       </c>
     </row>
     <row r="30">
@@ -3804,16 +3937,16 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0</v>
+        <v>76.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>105.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -3827,38 +3960,15 @@
         <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E31" t="n">
-        <v>76.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" t="s">
-        <v>16</v>
-      </c>
-      <c r="D32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G32" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -3932,7 +4042,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>456.0</v>
+        <v>337.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -4070,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1324.0</v>
+        <v>1325.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4116,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>458.0</v>
+        <v>464.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4139,7 +4249,7 @@
         <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>609.0</v>
+        <v>1.0</v>
       </c>
       <c r="F12" t="n">
         <v>0.0</v>
@@ -4159,10 +4269,10 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>411.0</v>
+        <v>100.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4182,10 +4292,10 @@
         <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>59.0</v>
+        <v>180.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -4199,16 +4309,16 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>298.0</v>
+        <v>407.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4222,22 +4332,22 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>3460.0</v>
+        <v>59.0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G16" t="n">
-        <v>39.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -4251,16 +4361,16 @@
         <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>1542.0</v>
+        <v>417.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
       </c>
       <c r="G17" t="n">
-        <v>41.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -4274,16 +4384,16 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0</v>
+        <v>3460.0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0</v>
+        <v>39.0</v>
       </c>
     </row>
     <row r="19">
@@ -4297,16 +4407,16 @@
         <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>601.0</v>
+        <v>1542.0</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="20">
@@ -4317,19 +4427,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
         <v>32</v>
       </c>
       <c r="E20" t="n">
-        <v>9047.0</v>
+        <v>0.0</v>
       </c>
       <c r="F20" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" t="n">
-        <v>187.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="21">
@@ -4340,19 +4450,19 @@
         <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>3098.0</v>
+        <v>601.0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G21" t="n">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
@@ -4366,16 +4476,16 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>6104.0</v>
+        <v>9057.0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="G22" t="n">
-        <v>5.0</v>
+        <v>187.0</v>
       </c>
     </row>
     <row r="23">
@@ -4386,19 +4496,19 @@
         <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3378.0</v>
+        <v>3099.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>83.0</v>
+        <v>30.0</v>
       </c>
     </row>
     <row r="24">
@@ -4409,19 +4519,19 @@
         <v>10</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>5681.0</v>
+        <v>6112.0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>164.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="25">
@@ -4432,19 +4542,19 @@
         <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>1588.0</v>
+        <v>3378.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>12.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="26">
@@ -4458,16 +4568,16 @@
         <v>15</v>
       </c>
       <c r="D26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>4409.0</v>
+        <v>5683.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0</v>
+        <v>164.0</v>
       </c>
     </row>
     <row r="27">
@@ -4478,19 +4588,19 @@
         <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>682.0</v>
+        <v>1588.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="28">
@@ -4501,19 +4611,19 @@
         <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0</v>
+        <v>4410.0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G28" t="n">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -4527,16 +4637,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1862.0</v>
+        <v>1242.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="30">
@@ -4544,22 +4654,22 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E30" t="n">
-        <v>110.0</v>
+        <v>0.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
     </row>
     <row r="31">
@@ -4567,22 +4677,22 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D31" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>52.0</v>
+        <v>1862.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -4590,16 +4700,16 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E32" t="n">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -4619,10 +4729,10 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>2.0</v>
+        <v>110.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
@@ -4639,19 +4749,19 @@
         <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>14.0</v>
+        <v>52.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35">
@@ -4662,19 +4772,19 @@
         <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>2238.0</v>
+        <v>13.0</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G35" t="n">
-        <v>49.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
@@ -4685,19 +4795,19 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E36" t="n">
-        <v>1696.0</v>
+        <v>2.0</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G36" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -4708,13 +4818,13 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E37" t="n">
-        <v>598.0</v>
+        <v>14.0</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
@@ -4731,19 +4841,19 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
-        <v>94.0</v>
+        <v>2238.0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="39">
@@ -4754,19 +4864,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0</v>
+        <v>1696.0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G39" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="40">
@@ -4777,13 +4887,13 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E40" t="n">
-        <v>1243.0</v>
+        <v>598.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>
@@ -4803,15 +4913,84 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E41" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
+        <v>36</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1243.0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" t="n">
         <v>1089.0</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F44" t="n">
         <v>1.0</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G44" t="n">
         <v>10.0</v>
       </c>
     </row>
